--- a/research/traditional_assets/database/data/tunisia/tunisia_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_chemical_basic.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvmt_icf" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.001600000000000001</v>
+        <v>0.078</v>
+      </c>
+      <c r="E2">
+        <v>0.25</v>
       </c>
       <c r="G2">
-        <v>-0.1003290129611166</v>
+        <v>-0.04008730158730159</v>
       </c>
       <c r="H2">
-        <v>-0.1003988035892323</v>
+        <v>-0.04015873015873016</v>
       </c>
       <c r="I2">
-        <v>-0.1436689930209372</v>
+        <v>-0.03166666666666667</v>
       </c>
       <c r="J2">
-        <v>-0.1436689930209372</v>
+        <v>-0.02977783540802213</v>
       </c>
       <c r="K2">
-        <v>-19.12</v>
+        <v>-7.41</v>
       </c>
       <c r="L2">
-        <v>-0.1906281156530409</v>
+        <v>-0.05880952380952381</v>
       </c>
       <c r="M2">
-        <v>6.23</v>
+        <v>2.81</v>
       </c>
       <c r="N2">
-        <v>0.0713631156930126</v>
+        <v>0.03377403846153846</v>
       </c>
       <c r="O2">
-        <v>-0.325836820083682</v>
+        <v>-0.3792172739541161</v>
       </c>
       <c r="P2">
-        <v>6.23</v>
+        <v>2.81</v>
       </c>
       <c r="Q2">
-        <v>0.0713631156930126</v>
+        <v>0.03377403846153846</v>
       </c>
       <c r="R2">
-        <v>-0.325836820083682</v>
+        <v>-0.3792172739541161</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,61 +638,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>12.4</v>
       </c>
       <c r="V2">
-        <v>0.0286368843069874</v>
+        <v>0.1490384615384615</v>
       </c>
       <c r="X2">
-        <v>0.1351734610764323</v>
+        <v>0.2258184007099203</v>
       </c>
       <c r="Z2">
-        <v>2.492544731610339</v>
+        <v>3.69935408103347</v>
       </c>
       <c r="AB2">
-        <v>0.1333124242976306</v>
+        <v>0.2258184007099203</v>
       </c>
       <c r="AD2">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.56</v>
+        <v>-12.4</v>
       </c>
       <c r="AH2">
-        <v>0.04443957968476357</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.1110503282275711</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.0175557056043214</v>
+        <v>-0.1751412429378531</v>
       </c>
       <c r="AK2">
-        <v>0.04580152671755724</v>
+        <v>-0.5438596491228069</v>
       </c>
       <c r="AL2">
-        <v>4.894</v>
+        <v>5.019</v>
       </c>
       <c r="AM2">
-        <v>4.47</v>
+        <v>3.185</v>
       </c>
       <c r="AN2">
-        <v>-0.4031777557100297</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-2.944421740907234</v>
+        <v>-0.794979079497908</v>
       </c>
       <c r="AP2">
-        <v>-0.1549155908639523</v>
+        <v>-22.962962962963</v>
       </c>
       <c r="AQ2">
-        <v>-3.223713646532439</v>
+        <v>-1.252747252747253</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +703,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Industries Chimiques du Fluor (BVMT:ICF)</t>
+          <t>Les industries Chimiques du Fluor SA (BVMT:ICF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -707,43 +712,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0461</v>
+        <v>0.126</v>
+      </c>
+      <c r="E3">
+        <v>0.25</v>
       </c>
       <c r="G3">
-        <v>-0.05389908256880734</v>
+        <v>0.05548387096774193</v>
       </c>
       <c r="H3">
-        <v>-0.05389908256880734</v>
+        <v>0.05548387096774193</v>
       </c>
       <c r="I3">
-        <v>-0.1011467889908257</v>
+        <v>0.1130645161290323</v>
       </c>
       <c r="J3">
-        <v>-0.1011467889908257</v>
+        <v>0.09957652924641949</v>
       </c>
       <c r="K3">
-        <v>-4.22</v>
+        <v>8.49</v>
       </c>
       <c r="L3">
-        <v>-0.09678899082568806</v>
+        <v>0.1369354838709677</v>
       </c>
       <c r="M3">
-        <v>6.23</v>
+        <v>2.81</v>
       </c>
       <c r="N3">
-        <v>0.1052364864864865</v>
+        <v>0.04614121510673235</v>
       </c>
       <c r="O3">
-        <v>-1.476303317535545</v>
+        <v>0.3309776207302709</v>
       </c>
       <c r="P3">
-        <v>6.23</v>
+        <v>2.81</v>
       </c>
       <c r="Q3">
-        <v>0.1052364864864865</v>
+        <v>0.04614121510673235</v>
       </c>
       <c r="R3">
-        <v>-1.476303317535545</v>
+        <v>0.3309776207302709</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,73 +760,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>12.4</v>
       </c>
       <c r="V3">
-        <v>0.04222972972972973</v>
+        <v>0.2036124794745484</v>
       </c>
       <c r="W3">
-        <v>-0.1009569377990431</v>
+        <v>0.2612307692307692</v>
       </c>
       <c r="X3">
-        <v>0.1385741185529796</v>
+        <v>0.2258184007099203</v>
       </c>
       <c r="Y3">
-        <v>-0.2395310563520227</v>
+        <v>0.03541236852084889</v>
       </c>
       <c r="Z3">
-        <v>1.083499005964215</v>
+        <v>1.82031708749266</v>
       </c>
       <c r="AA3">
-        <v>-0.1095924453280318</v>
+        <v>0.18126085770047</v>
       </c>
       <c r="AB3">
-        <v>0.1348520449953762</v>
+        <v>0.2258184007099203</v>
       </c>
       <c r="AC3">
-        <v>-0.244444490323408</v>
+        <v>-0.04455754300945033</v>
       </c>
       <c r="AD3">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.56</v>
+        <v>-12.4</v>
       </c>
       <c r="AH3">
-        <v>0.06417957635156496</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1110503282275711</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.02567478604344963</v>
+        <v>-0.2556701030927835</v>
       </c>
       <c r="AK3">
-        <v>0.04580152671755724</v>
+        <v>-0.5438596491228069</v>
       </c>
       <c r="AL3">
-        <v>0.134</v>
+        <v>0.019</v>
       </c>
       <c r="AM3">
-        <v>-0.237</v>
+        <v>-1.791</v>
       </c>
       <c r="AN3">
-        <v>-1.727659574468085</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-32.91044776119403</v>
+        <v>368.9473684210526</v>
       </c>
       <c r="AP3">
-        <v>-0.6638297872340424</v>
+        <v>-1.371681415929204</v>
       </c>
       <c r="AQ3">
-        <v>18.60759493670886</v>
+        <v>-3.914014517029592</v>
       </c>
     </row>
     <row r="4">
@@ -838,25 +846,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0429</v>
+        <v>0.03</v>
       </c>
       <c r="G4">
-        <v>-0.136031746031746</v>
+        <v>-0.132671875</v>
       </c>
       <c r="H4">
-        <v>-0.1361552028218695</v>
+        <v>-0.1328125</v>
       </c>
       <c r="I4">
-        <v>-0.1763668430335097</v>
+        <v>-0.171875</v>
       </c>
       <c r="J4">
-        <v>-0.1763668430335097</v>
+        <v>-0.171875</v>
       </c>
       <c r="K4">
-        <v>-14.9</v>
+        <v>-15.9</v>
       </c>
       <c r="L4">
-        <v>-0.2627865961199294</v>
+        <v>-0.2484375</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,10 +894,10 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>0.131772803599885</v>
+        <v>0.2258184007099203</v>
       </c>
       <c r="AB4">
-        <v>0.131772803599885</v>
+        <v>0.2258184007099203</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -910,22 +918,8734 @@
         <v>0</v>
       </c>
       <c r="AL4">
-        <v>4.76</v>
+        <v>5</v>
       </c>
       <c r="AM4">
-        <v>4.707</v>
+        <v>4.976</v>
       </c>
       <c r="AN4">
         <v>-0</v>
       </c>
       <c r="AO4">
-        <v>-2.100840336134454</v>
+        <v>-2.2</v>
       </c>
       <c r="AP4">
         <v>-0</v>
       </c>
       <c r="AQ4">
-        <v>-2.12449543233482</v>
+        <v>-2.210610932475884</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Les industries Chimiques du Fluor SA (BVMT:ICF)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVMT:ICF</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chemical (Basic)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.46</v>
+      </c>
+      <c r="G2">
+        <v>60.9</v>
+      </c>
+      <c r="H2">
+        <v>35.4088650754436</v>
+      </c>
+      <c r="I2">
+        <v>48.5</v>
+      </c>
+      <c r="J2">
+        <v>51.0228650754436</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>28.014</v>
+      </c>
+      <c r="M2">
+        <v>0.22581840070992</v>
+      </c>
+      <c r="N2">
+        <v>0.216571131060936</v>
+      </c>
+      <c r="O2">
+        <v>0.127966720183486</v>
+      </c>
+      <c r="P2">
+        <v>0.04675</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.22581840070992</v>
+      </c>
+      <c r="T2">
+        <v>0.36123357603877</v>
+      </c>
+      <c r="U2">
+        <v>0.991793239958831</v>
+      </c>
+      <c r="V2">
+        <v>1.70992501185495</v>
+      </c>
+      <c r="W2">
+        <v>4.549673215340381</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>60.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.1885659159339335</v>
+      </c>
+      <c r="AC2">
+        <v>0.1505490825688073</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="AH2">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>2.584</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0.019</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>12.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2258184007099203</v>
+      </c>
+      <c r="C2">
+        <v>60.9</v>
+      </c>
+      <c r="D2">
+        <v>48.5</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>12.4</v>
+      </c>
+      <c r="H2">
+        <v>60.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K2">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L2">
+        <v>7.01</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>7.01</v>
+      </c>
+      <c r="O2">
+        <v>1.0515</v>
+      </c>
+      <c r="P2">
+        <v>5.9585</v>
+      </c>
+      <c r="Q2">
+        <v>7.988499999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2258184007099203</v>
+      </c>
+      <c r="T2">
+        <v>0.9917932399588305</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2255383231088554</v>
+      </c>
+      <c r="C3">
+        <v>60.36374223858019</v>
+      </c>
+      <c r="D3">
+        <v>48.57274223858019</v>
+      </c>
+      <c r="E3">
+        <v>0.609</v>
+      </c>
+      <c r="F3">
+        <v>0.609</v>
+      </c>
+      <c r="G3">
+        <v>12.4</v>
+      </c>
+      <c r="H3">
+        <v>60.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K3">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L3">
+        <v>7.01</v>
+      </c>
+      <c r="M3">
+        <v>0.0278313</v>
+      </c>
+      <c r="N3">
+        <v>6.9821687</v>
+      </c>
+      <c r="O3">
+        <v>1.047325305</v>
+      </c>
+      <c r="P3">
+        <v>5.934843395</v>
+      </c>
+      <c r="Q3">
+        <v>7.964843394999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2274241142513691</v>
+      </c>
+      <c r="T3">
+        <v>1.000308636463527</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>251.8746878514478</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2252582455077906</v>
+      </c>
+      <c r="C4">
+        <v>59.82770300835614</v>
+      </c>
+      <c r="D4">
+        <v>48.64570300835614</v>
+      </c>
+      <c r="E4">
+        <v>1.218</v>
+      </c>
+      <c r="F4">
+        <v>1.218</v>
+      </c>
+      <c r="G4">
+        <v>12.4</v>
+      </c>
+      <c r="H4">
+        <v>60.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K4">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L4">
+        <v>7.01</v>
+      </c>
+      <c r="M4">
+        <v>0.05566260000000001</v>
+      </c>
+      <c r="N4">
+        <v>6.9543374</v>
+      </c>
+      <c r="O4">
+        <v>1.04315061</v>
+      </c>
+      <c r="P4">
+        <v>5.91118679</v>
+      </c>
+      <c r="Q4">
+        <v>7.94118679</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2290625974569291</v>
+      </c>
+      <c r="T4">
+        <v>1.008997816570361</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>125.9373439257239</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2249781679067257</v>
+      </c>
+      <c r="C5">
+        <v>59.29188329557179</v>
+      </c>
+      <c r="D5">
+        <v>48.71888329557179</v>
+      </c>
+      <c r="E5">
+        <v>1.827</v>
+      </c>
+      <c r="F5">
+        <v>1.827</v>
+      </c>
+      <c r="G5">
+        <v>12.4</v>
+      </c>
+      <c r="H5">
+        <v>60.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K5">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L5">
+        <v>7.01</v>
+      </c>
+      <c r="M5">
+        <v>0.08349390000000001</v>
+      </c>
+      <c r="N5">
+        <v>6.9265061</v>
+      </c>
+      <c r="O5">
+        <v>1.038975915</v>
+      </c>
+      <c r="P5">
+        <v>5.887530185</v>
+      </c>
+      <c r="Q5">
+        <v>7.917530184999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2307348638213667</v>
+      </c>
+      <c r="T5">
+        <v>1.017866155029913</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>83.95822928381594</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2246980903056608</v>
+      </c>
+      <c r="C6">
+        <v>58.75628409241455</v>
+      </c>
+      <c r="D6">
+        <v>48.79228409241455</v>
+      </c>
+      <c r="E6">
+        <v>2.436</v>
+      </c>
+      <c r="F6">
+        <v>2.436</v>
+      </c>
+      <c r="G6">
+        <v>12.4</v>
+      </c>
+      <c r="H6">
+        <v>60.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K6">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L6">
+        <v>7.01</v>
+      </c>
+      <c r="M6">
+        <v>0.1113252</v>
+      </c>
+      <c r="N6">
+        <v>6.8986748</v>
+      </c>
+      <c r="O6">
+        <v>1.03480122</v>
+      </c>
+      <c r="P6">
+        <v>5.86387358</v>
+      </c>
+      <c r="Q6">
+        <v>7.893873579999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2324419690683966</v>
+      </c>
+      <c r="T6">
+        <v>1.026919250540706</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>62.96867196286195</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2244180127045959</v>
+      </c>
+      <c r="C7">
+        <v>58.22090639706031</v>
+      </c>
+      <c r="D7">
+        <v>48.86590639706031</v>
+      </c>
+      <c r="E7">
+        <v>3.045</v>
+      </c>
+      <c r="F7">
+        <v>3.045</v>
+      </c>
+      <c r="G7">
+        <v>12.4</v>
+      </c>
+      <c r="H7">
+        <v>60.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K7">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L7">
+        <v>7.01</v>
+      </c>
+      <c r="M7">
+        <v>0.1391565</v>
+      </c>
+      <c r="N7">
+        <v>6.870843499999999</v>
+      </c>
+      <c r="O7">
+        <v>1.030626525</v>
+      </c>
+      <c r="P7">
+        <v>5.840216975</v>
+      </c>
+      <c r="Q7">
+        <v>7.870216974999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2341850133732589</v>
+      </c>
+      <c r="T7">
+        <v>1.036162937535936</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>50.37493757028955</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.224137935103531</v>
+      </c>
+      <c r="C8">
+        <v>57.68575121371862</v>
+      </c>
+      <c r="D8">
+        <v>48.93975121371862</v>
+      </c>
+      <c r="E8">
+        <v>3.654</v>
+      </c>
+      <c r="F8">
+        <v>3.654</v>
+      </c>
+      <c r="G8">
+        <v>12.4</v>
+      </c>
+      <c r="H8">
+        <v>60.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K8">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L8">
+        <v>7.01</v>
+      </c>
+      <c r="M8">
+        <v>0.1669878</v>
+      </c>
+      <c r="N8">
+        <v>6.8430122</v>
+      </c>
+      <c r="O8">
+        <v>1.02645183</v>
+      </c>
+      <c r="P8">
+        <v>5.816560369999999</v>
+      </c>
+      <c r="Q8">
+        <v>7.846560369999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2359651437271607</v>
+      </c>
+      <c r="T8">
+        <v>1.045603298722554</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>41.97911464190796</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2238578575024661</v>
+      </c>
+      <c r="C9">
+        <v>57.15081955267834</v>
+      </c>
+      <c r="D9">
+        <v>49.01381955267833</v>
+      </c>
+      <c r="E9">
+        <v>4.263</v>
+      </c>
+      <c r="F9">
+        <v>4.263</v>
+      </c>
+      <c r="G9">
+        <v>12.4</v>
+      </c>
+      <c r="H9">
+        <v>60.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K9">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L9">
+        <v>7.01</v>
+      </c>
+      <c r="M9">
+        <v>0.1948191</v>
+      </c>
+      <c r="N9">
+        <v>6.8151809</v>
+      </c>
+      <c r="O9">
+        <v>1.022277135</v>
+      </c>
+      <c r="P9">
+        <v>5.792903764999999</v>
+      </c>
+      <c r="Q9">
+        <v>7.822903764999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2377835564542647</v>
+      </c>
+      <c r="T9">
+        <v>1.055246678429315</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>35.98209826449254</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2235777799014013</v>
+      </c>
+      <c r="C10">
+        <v>56.61611243035369</v>
+      </c>
+      <c r="D10">
+        <v>49.08811243035369</v>
+      </c>
+      <c r="E10">
+        <v>4.872</v>
+      </c>
+      <c r="F10">
+        <v>4.872</v>
+      </c>
+      <c r="G10">
+        <v>12.4</v>
+      </c>
+      <c r="H10">
+        <v>60.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K10">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L10">
+        <v>7.01</v>
+      </c>
+      <c r="M10">
+        <v>0.2226504</v>
+      </c>
+      <c r="N10">
+        <v>6.7873496</v>
+      </c>
+      <c r="O10">
+        <v>1.01810244</v>
+      </c>
+      <c r="P10">
+        <v>5.76924716</v>
+      </c>
+      <c r="Q10">
+        <v>7.799247159999999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2396414998928275</v>
+      </c>
+      <c r="T10">
+        <v>1.065099696825353</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>31.48433598143097</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2232977023003364</v>
+      </c>
+      <c r="C11">
+        <v>56.08163086933087</v>
+      </c>
+      <c r="D11">
+        <v>49.16263086933087</v>
+      </c>
+      <c r="E11">
+        <v>5.481</v>
+      </c>
+      <c r="F11">
+        <v>5.481</v>
+      </c>
+      <c r="G11">
+        <v>12.4</v>
+      </c>
+      <c r="H11">
+        <v>60.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K11">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L11">
+        <v>7.01</v>
+      </c>
+      <c r="M11">
+        <v>0.2504817</v>
+      </c>
+      <c r="N11">
+        <v>6.7595183</v>
+      </c>
+      <c r="O11">
+        <v>1.013927745</v>
+      </c>
+      <c r="P11">
+        <v>5.745590555</v>
+      </c>
+      <c r="Q11">
+        <v>7.775590554999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2415402772531169</v>
+      </c>
+      <c r="T11">
+        <v>1.075169265076249</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>27.98607642793865</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2230176246992716</v>
+      </c>
+      <c r="C12">
+        <v>55.5473758984148</v>
+      </c>
+      <c r="D12">
+        <v>49.2373758984148</v>
+      </c>
+      <c r="E12">
+        <v>6.09</v>
+      </c>
+      <c r="F12">
+        <v>6.09</v>
+      </c>
+      <c r="G12">
+        <v>12.4</v>
+      </c>
+      <c r="H12">
+        <v>60.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K12">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L12">
+        <v>7.01</v>
+      </c>
+      <c r="M12">
+        <v>0.278313</v>
+      </c>
+      <c r="N12">
+        <v>6.731687</v>
+      </c>
+      <c r="O12">
+        <v>1.00975305</v>
+      </c>
+      <c r="P12">
+        <v>5.72193395</v>
+      </c>
+      <c r="Q12">
+        <v>7.75193395</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2434812496658573</v>
+      </c>
+      <c r="T12">
+        <v>1.085462601510498</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>25.18746878514478</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2227375470982066</v>
+      </c>
+      <c r="C13">
+        <v>55.0133485526766</v>
+      </c>
+      <c r="D13">
+        <v>49.3123485526766</v>
+      </c>
+      <c r="E13">
+        <v>6.699</v>
+      </c>
+      <c r="F13">
+        <v>6.699</v>
+      </c>
+      <c r="G13">
+        <v>12.4</v>
+      </c>
+      <c r="H13">
+        <v>60.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K13">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L13">
+        <v>7.01</v>
+      </c>
+      <c r="M13">
+        <v>0.3061443</v>
+      </c>
+      <c r="N13">
+        <v>6.7038557</v>
+      </c>
+      <c r="O13">
+        <v>1.005578355</v>
+      </c>
+      <c r="P13">
+        <v>5.698277345</v>
+      </c>
+      <c r="Q13">
+        <v>7.728277345</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2454658394361872</v>
+      </c>
+      <c r="T13">
+        <v>1.095987248875854</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>22.89769889558616</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2224574694971418</v>
+      </c>
+      <c r="C14">
+        <v>54.47954987350131</v>
+      </c>
+      <c r="D14">
+        <v>49.38754987350131</v>
+      </c>
+      <c r="E14">
+        <v>7.308</v>
+      </c>
+      <c r="F14">
+        <v>7.308</v>
+      </c>
+      <c r="G14">
+        <v>12.4</v>
+      </c>
+      <c r="H14">
+        <v>60.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K14">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L14">
+        <v>7.01</v>
+      </c>
+      <c r="M14">
+        <v>0.3339756</v>
+      </c>
+      <c r="N14">
+        <v>6.676024399999999</v>
+      </c>
+      <c r="O14">
+        <v>1.00140366</v>
+      </c>
+      <c r="P14">
+        <v>5.674620739999999</v>
+      </c>
+      <c r="Q14">
+        <v>7.704620739999998</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2474955335194793</v>
+      </c>
+      <c r="T14">
+        <v>1.10675109277224</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>20.98955732095398</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2221773918960769</v>
+      </c>
+      <c r="C15">
+        <v>53.94598090863612</v>
+      </c>
+      <c r="D15">
+        <v>49.46298090863612</v>
+      </c>
+      <c r="E15">
+        <v>7.917</v>
+      </c>
+      <c r="F15">
+        <v>7.917</v>
+      </c>
+      <c r="G15">
+        <v>12.4</v>
+      </c>
+      <c r="H15">
+        <v>60.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K15">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L15">
+        <v>7.01</v>
+      </c>
+      <c r="M15">
+        <v>0.3618069</v>
+      </c>
+      <c r="N15">
+        <v>6.648193099999999</v>
+      </c>
+      <c r="O15">
+        <v>0.997228965</v>
+      </c>
+      <c r="P15">
+        <v>5.650964135</v>
+      </c>
+      <c r="Q15">
+        <v>7.680964134999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.24957188723687</v>
+      </c>
+      <c r="T15">
+        <v>1.1177623813559</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.038845</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>19.37497598857291</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.221897314295012</v>
+      </c>
+      <c r="C16">
+        <v>53.41264271223903</v>
+      </c>
+      <c r="D16">
+        <v>49.53864271223903</v>
+      </c>
+      <c r="E16">
+        <v>8.526</v>
+      </c>
+      <c r="F16">
+        <v>8.526</v>
+      </c>
+      <c r="G16">
+        <v>12.4</v>
+      </c>
+      <c r="H16">
+        <v>60.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K16">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L16">
+        <v>7.01</v>
+      </c>
+      <c r="M16">
+        <v>0.3896382</v>
+      </c>
+      <c r="N16">
+        <v>6.6203618</v>
+      </c>
+      <c r="O16">
+        <v>0.9930542700000001</v>
+      </c>
+      <c r="P16">
+        <v>5.62730753</v>
+      </c>
+      <c r="Q16">
+        <v>7.657307529999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2516965282500139</v>
+      </c>
+      <c r="T16">
+        <v>1.12902974641825</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.038845</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>17.99104913224627</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2216172366939471</v>
+      </c>
+      <c r="C17">
+        <v>52.87953634492796</v>
+      </c>
+      <c r="D17">
+        <v>49.61453634492796</v>
+      </c>
+      <c r="E17">
+        <v>9.135</v>
+      </c>
+      <c r="F17">
+        <v>9.135</v>
+      </c>
+      <c r="G17">
+        <v>12.4</v>
+      </c>
+      <c r="H17">
+        <v>60.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K17">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L17">
+        <v>7.01</v>
+      </c>
+      <c r="M17">
+        <v>0.4174695</v>
+      </c>
+      <c r="N17">
+        <v>6.5925305</v>
+      </c>
+      <c r="O17">
+        <v>0.9888795750000001</v>
+      </c>
+      <c r="P17">
+        <v>5.603650924999999</v>
+      </c>
+      <c r="Q17">
+        <v>7.633650924999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2538711608164084</v>
+      </c>
+      <c r="T17">
+        <v>1.140562225952655</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.038845</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>16.79164585676319</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2213371590928822</v>
+      </c>
+      <c r="C18">
+        <v>52.34666287383028</v>
+      </c>
+      <c r="D18">
+        <v>49.69066287383028</v>
+      </c>
+      <c r="E18">
+        <v>9.744</v>
+      </c>
+      <c r="F18">
+        <v>9.744</v>
+      </c>
+      <c r="G18">
+        <v>12.4</v>
+      </c>
+      <c r="H18">
+        <v>60.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K18">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L18">
+        <v>7.01</v>
+      </c>
+      <c r="M18">
+        <v>0.4453008000000001</v>
+      </c>
+      <c r="N18">
+        <v>6.5646992</v>
+      </c>
+      <c r="O18">
+        <v>0.9847048800000001</v>
+      </c>
+      <c r="P18">
+        <v>5.57999432</v>
+      </c>
+      <c r="Q18">
+        <v>7.609994319999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2560975703486693</v>
+      </c>
+      <c r="T18">
+        <v>1.152369288333117</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.038845</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>15.74216799071549</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2210570814918173</v>
+      </c>
+      <c r="C19">
+        <v>51.81402337263292</v>
+      </c>
+      <c r="D19">
+        <v>49.76702337263292</v>
+      </c>
+      <c r="E19">
+        <v>10.353</v>
+      </c>
+      <c r="F19">
+        <v>10.353</v>
+      </c>
+      <c r="G19">
+        <v>12.4</v>
+      </c>
+      <c r="H19">
+        <v>60.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K19">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L19">
+        <v>7.01</v>
+      </c>
+      <c r="M19">
+        <v>0.4731321000000001</v>
+      </c>
+      <c r="N19">
+        <v>6.5368679</v>
+      </c>
+      <c r="O19">
+        <v>0.9805301850000001</v>
+      </c>
+      <c r="P19">
+        <v>5.556337715</v>
+      </c>
+      <c r="Q19">
+        <v>7.586337714999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2583776283033944</v>
+      </c>
+      <c r="T19">
+        <v>1.16446085824082</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.038845</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>14.81615810890869</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2207770038907525</v>
+      </c>
+      <c r="C20">
+        <v>51.28161892163268</v>
+      </c>
+      <c r="D20">
+        <v>49.84361892163269</v>
+      </c>
+      <c r="E20">
+        <v>10.962</v>
+      </c>
+      <c r="F20">
+        <v>10.962</v>
+      </c>
+      <c r="G20">
+        <v>12.4</v>
+      </c>
+      <c r="H20">
+        <v>60.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K20">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L20">
+        <v>7.01</v>
+      </c>
+      <c r="M20">
+        <v>0.5009634000000001</v>
+      </c>
+      <c r="N20">
+        <v>6.5090366</v>
+      </c>
+      <c r="O20">
+        <v>0.9763554900000001</v>
+      </c>
+      <c r="P20">
+        <v>5.53268111</v>
+      </c>
+      <c r="Q20">
+        <v>7.562681109999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2607132974277469</v>
+      </c>
+      <c r="T20">
+        <v>1.176847344487734</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.038845</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>13.99303821396932</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2204969262896876</v>
+      </c>
+      <c r="C21">
+        <v>50.74945060778738</v>
+      </c>
+      <c r="D21">
+        <v>49.92045060778738</v>
+      </c>
+      <c r="E21">
+        <v>11.571</v>
+      </c>
+      <c r="F21">
+        <v>11.571</v>
+      </c>
+      <c r="G21">
+        <v>12.4</v>
+      </c>
+      <c r="H21">
+        <v>60.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K21">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L21">
+        <v>7.01</v>
+      </c>
+      <c r="M21">
+        <v>0.5287947000000001</v>
+      </c>
+      <c r="N21">
+        <v>6.4812053</v>
+      </c>
+      <c r="O21">
+        <v>0.9721807950000001</v>
+      </c>
+      <c r="P21">
+        <v>5.509024505</v>
+      </c>
+      <c r="Q21">
+        <v>7.539024505</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.263106637394676</v>
+      </c>
+      <c r="T21">
+        <v>1.189539669901239</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.038845</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>13.25656251849725</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2204888486886227</v>
+      </c>
+      <c r="C22">
+        <v>50.14266999267478</v>
+      </c>
+      <c r="D22">
+        <v>49.92266999267478</v>
+      </c>
+      <c r="E22">
+        <v>12.18</v>
+      </c>
+      <c r="F22">
+        <v>12.18</v>
+      </c>
+      <c r="G22">
+        <v>12.4</v>
+      </c>
+      <c r="H22">
+        <v>60.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K22">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L22">
+        <v>7.01</v>
+      </c>
+      <c r="M22">
+        <v>0.576114</v>
+      </c>
+      <c r="N22">
+        <v>6.433885999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.9650829000000001</v>
+      </c>
+      <c r="P22">
+        <v>5.468803099999999</v>
+      </c>
+      <c r="Q22">
+        <v>7.498803099999998</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2655598108607784</v>
+      </c>
+      <c r="T22">
+        <v>1.202549303450082</v>
+      </c>
+      <c r="U22">
+        <v>0.0473</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.040205</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>12.16773069218939</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2202223710875578</v>
+      </c>
+      <c r="C23">
+        <v>49.60699762729148</v>
+      </c>
+      <c r="D23">
+        <v>49.99599762729148</v>
+      </c>
+      <c r="E23">
+        <v>12.789</v>
+      </c>
+      <c r="F23">
+        <v>12.789</v>
+      </c>
+      <c r="G23">
+        <v>12.4</v>
+      </c>
+      <c r="H23">
+        <v>60.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K23">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L23">
+        <v>7.01</v>
+      </c>
+      <c r="M23">
+        <v>0.6049197000000001</v>
+      </c>
+      <c r="N23">
+        <v>6.4050803</v>
+      </c>
+      <c r="O23">
+        <v>0.9607620450000001</v>
+      </c>
+      <c r="P23">
+        <v>5.444318255</v>
+      </c>
+      <c r="Q23">
+        <v>7.474318254999999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2680750899842504</v>
+      </c>
+      <c r="T23">
+        <v>1.215888294810288</v>
+      </c>
+      <c r="U23">
+        <v>0.0473</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.040205</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>11.58831494494228</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.219955893486493</v>
+      </c>
+      <c r="C24">
+        <v>49.07154098960864</v>
+      </c>
+      <c r="D24">
+        <v>50.06954098960863</v>
+      </c>
+      <c r="E24">
+        <v>13.398</v>
+      </c>
+      <c r="F24">
+        <v>13.398</v>
+      </c>
+      <c r="G24">
+        <v>12.4</v>
+      </c>
+      <c r="H24">
+        <v>60.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K24">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L24">
+        <v>7.01</v>
+      </c>
+      <c r="M24">
+        <v>0.6337254</v>
+      </c>
+      <c r="N24">
+        <v>6.376274599999999</v>
+      </c>
+      <c r="O24">
+        <v>0.9564411900000001</v>
+      </c>
+      <c r="P24">
+        <v>5.419833409999999</v>
+      </c>
+      <c r="Q24">
+        <v>7.449833409999998</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2706548634442217</v>
+      </c>
+      <c r="T24">
+        <v>1.229569311589986</v>
+      </c>
+      <c r="U24">
+        <v>0.0473</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.040205</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>11.06157335653581</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2196894158854281</v>
+      </c>
+      <c r="C25">
+        <v>48.53630103302535</v>
+      </c>
+      <c r="D25">
+        <v>50.14330103302535</v>
+      </c>
+      <c r="E25">
+        <v>14.007</v>
+      </c>
+      <c r="F25">
+        <v>14.007</v>
+      </c>
+      <c r="G25">
+        <v>12.4</v>
+      </c>
+      <c r="H25">
+        <v>60.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K25">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L25">
+        <v>7.01</v>
+      </c>
+      <c r="M25">
+        <v>0.6625311</v>
+      </c>
+      <c r="N25">
+        <v>6.3474689</v>
+      </c>
+      <c r="O25">
+        <v>0.9521203350000002</v>
+      </c>
+      <c r="P25">
+        <v>5.395348565</v>
+      </c>
+      <c r="Q25">
+        <v>7.425348564999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2733016440070494</v>
+      </c>
+      <c r="T25">
+        <v>1.243605679454871</v>
+      </c>
+      <c r="U25">
+        <v>0.0473</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.040205</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>10.58063538451252</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2201981382843632</v>
+      </c>
+      <c r="C26">
+        <v>47.78667654463032</v>
+      </c>
+      <c r="D26">
+        <v>50.00267654463033</v>
+      </c>
+      <c r="E26">
+        <v>14.616</v>
+      </c>
+      <c r="F26">
+        <v>14.616</v>
+      </c>
+      <c r="G26">
+        <v>12.4</v>
+      </c>
+      <c r="H26">
+        <v>60.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K26">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L26">
+        <v>7.01</v>
+      </c>
+      <c r="M26">
+        <v>0.7468776</v>
+      </c>
+      <c r="N26">
+        <v>6.263122399999999</v>
+      </c>
+      <c r="O26">
+        <v>0.93946836</v>
+      </c>
+      <c r="P26">
+        <v>5.323654039999999</v>
+      </c>
+      <c r="Q26">
+        <v>7.353654039999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2760180766899515</v>
+      </c>
+      <c r="T26">
+        <v>1.258011425421464</v>
+      </c>
+      <c r="U26">
+        <v>0.0511</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.043435</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>9.385741385201536</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2199639606832983</v>
+      </c>
+      <c r="C27">
+        <v>47.24231140244576</v>
+      </c>
+      <c r="D27">
+        <v>50.06731140244576</v>
+      </c>
+      <c r="E27">
+        <v>15.225</v>
+      </c>
+      <c r="F27">
+        <v>15.225</v>
+      </c>
+      <c r="G27">
+        <v>12.4</v>
+      </c>
+      <c r="H27">
+        <v>60.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K27">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L27">
+        <v>7.01</v>
+      </c>
+      <c r="M27">
+        <v>0.7779975</v>
+      </c>
+      <c r="N27">
+        <v>6.2320025</v>
+      </c>
+      <c r="O27">
+        <v>0.9348003750000001</v>
+      </c>
+      <c r="P27">
+        <v>5.297202125</v>
+      </c>
+      <c r="Q27">
+        <v>7.327202124999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2788069475777311</v>
+      </c>
+      <c r="T27">
+        <v>1.272801324613832</v>
+      </c>
+      <c r="U27">
+        <v>0.0511</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.043435</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>9.010311729793477</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2197297830822335</v>
+      </c>
+      <c r="C28">
+        <v>46.69811357418473</v>
+      </c>
+      <c r="D28">
+        <v>50.13211357418474</v>
+      </c>
+      <c r="E28">
+        <v>15.834</v>
+      </c>
+      <c r="F28">
+        <v>15.834</v>
+      </c>
+      <c r="G28">
+        <v>12.4</v>
+      </c>
+      <c r="H28">
+        <v>60.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K28">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L28">
+        <v>7.01</v>
+      </c>
+      <c r="M28">
+        <v>0.8091174</v>
+      </c>
+      <c r="N28">
+        <v>6.2008826</v>
+      </c>
+      <c r="O28">
+        <v>0.9301323900000001</v>
+      </c>
+      <c r="P28">
+        <v>5.27075021</v>
+      </c>
+      <c r="Q28">
+        <v>7.300750209999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2816711933543695</v>
+      </c>
+      <c r="T28">
+        <v>1.2879909508114</v>
+      </c>
+      <c r="U28">
+        <v>0.0511</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.043435</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.663761278647574</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2194956054811686</v>
+      </c>
+      <c r="C29">
+        <v>46.15408371035298</v>
+      </c>
+      <c r="D29">
+        <v>50.19708371035298</v>
+      </c>
+      <c r="E29">
+        <v>16.443</v>
+      </c>
+      <c r="F29">
+        <v>16.443</v>
+      </c>
+      <c r="G29">
+        <v>12.4</v>
+      </c>
+      <c r="H29">
+        <v>60.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K29">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L29">
+        <v>7.01</v>
+      </c>
+      <c r="M29">
+        <v>0.8402373000000001</v>
+      </c>
+      <c r="N29">
+        <v>6.1697627</v>
+      </c>
+      <c r="O29">
+        <v>0.925464405</v>
+      </c>
+      <c r="P29">
+        <v>5.244298295</v>
+      </c>
+      <c r="Q29">
+        <v>7.274298294999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2846139116180391</v>
+      </c>
+      <c r="T29">
+        <v>1.303596731151367</v>
+      </c>
+      <c r="U29">
+        <v>0.0511</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.043435</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>8.342881231290255</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2192614278801037</v>
+      </c>
+      <c r="C30">
+        <v>45.6102224648327</v>
+      </c>
+      <c r="D30">
+        <v>50.2622224648327</v>
+      </c>
+      <c r="E30">
+        <v>17.052</v>
+      </c>
+      <c r="F30">
+        <v>17.052</v>
+      </c>
+      <c r="G30">
+        <v>12.4</v>
+      </c>
+      <c r="H30">
+        <v>60.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K30">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L30">
+        <v>7.01</v>
+      </c>
+      <c r="M30">
+        <v>0.8713571999999999</v>
+      </c>
+      <c r="N30">
+        <v>6.1386428</v>
+      </c>
+      <c r="O30">
+        <v>0.9207964200000001</v>
+      </c>
+      <c r="P30">
+        <v>5.217846379999999</v>
+      </c>
+      <c r="Q30">
+        <v>7.247846379999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2876383720556996</v>
+      </c>
+      <c r="T30">
+        <v>1.319636005389666</v>
+      </c>
+      <c r="U30">
+        <v>0.0511</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.043435</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>8.044921187315603</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2194956002790388</v>
+      </c>
+      <c r="C31">
+        <v>44.93608515550019</v>
+      </c>
+      <c r="D31">
+        <v>50.19708515550019</v>
+      </c>
+      <c r="E31">
+        <v>17.661</v>
+      </c>
+      <c r="F31">
+        <v>17.661</v>
+      </c>
+      <c r="G31">
+        <v>12.4</v>
+      </c>
+      <c r="H31">
+        <v>60.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K31">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L31">
+        <v>7.01</v>
+      </c>
+      <c r="M31">
+        <v>0.936033</v>
+      </c>
+      <c r="N31">
+        <v>6.073967</v>
+      </c>
+      <c r="O31">
+        <v>0.9110950500000001</v>
+      </c>
+      <c r="P31">
+        <v>5.16287195</v>
+      </c>
+      <c r="Q31">
+        <v>7.192871949999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2907480285620265</v>
+      </c>
+      <c r="T31">
+        <v>1.336127090169889</v>
+      </c>
+      <c r="U31">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>7.489052202219366</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2192775726779739</v>
+      </c>
+      <c r="C32">
+        <v>44.38772620853803</v>
+      </c>
+      <c r="D32">
+        <v>50.25772620853802</v>
+      </c>
+      <c r="E32">
+        <v>18.27</v>
+      </c>
+      <c r="F32">
+        <v>18.27</v>
+      </c>
+      <c r="G32">
+        <v>12.4</v>
+      </c>
+      <c r="H32">
+        <v>60.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K32">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L32">
+        <v>7.01</v>
+      </c>
+      <c r="M32">
+        <v>0.9683100000000001</v>
+      </c>
+      <c r="N32">
+        <v>6.04169</v>
+      </c>
+      <c r="O32">
+        <v>0.9062535000000002</v>
+      </c>
+      <c r="P32">
+        <v>5.1354365</v>
+      </c>
+      <c r="Q32">
+        <v>7.165436499999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2939465323971056</v>
+      </c>
+      <c r="T32">
+        <v>1.353089348800976</v>
+      </c>
+      <c r="U32">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>7.239417128812053</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.219059545076909</v>
+      </c>
+      <c r="C33">
+        <v>43.83951395476</v>
+      </c>
+      <c r="D33">
+        <v>50.31851395476</v>
+      </c>
+      <c r="E33">
+        <v>18.879</v>
+      </c>
+      <c r="F33">
+        <v>18.879</v>
+      </c>
+      <c r="G33">
+        <v>12.4</v>
+      </c>
+      <c r="H33">
+        <v>60.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K33">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L33">
+        <v>7.01</v>
+      </c>
+      <c r="M33">
+        <v>1.000587</v>
+      </c>
+      <c r="N33">
+        <v>6.009413</v>
+      </c>
+      <c r="O33">
+        <v>0.9014119500000002</v>
+      </c>
+      <c r="P33">
+        <v>5.10800105</v>
+      </c>
+      <c r="Q33">
+        <v>7.13800105</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2972377464882739</v>
+      </c>
+      <c r="T33">
+        <v>1.370543267102529</v>
+      </c>
+      <c r="U33">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>7.005887544011666</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2188415174758441</v>
+      </c>
+      <c r="C34">
+        <v>43.29144892709592</v>
+      </c>
+      <c r="D34">
+        <v>50.37944892709592</v>
+      </c>
+      <c r="E34">
+        <v>19.488</v>
+      </c>
+      <c r="F34">
+        <v>19.488</v>
+      </c>
+      <c r="G34">
+        <v>12.4</v>
+      </c>
+      <c r="H34">
+        <v>60.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K34">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L34">
+        <v>7.01</v>
+      </c>
+      <c r="M34">
+        <v>1.032864</v>
+      </c>
+      <c r="N34">
+        <v>5.977136</v>
+      </c>
+      <c r="O34">
+        <v>0.8965704000000001</v>
+      </c>
+      <c r="P34">
+        <v>5.0805656</v>
+      </c>
+      <c r="Q34">
+        <v>7.110565599999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3006257609938884</v>
+      </c>
+      <c r="T34">
+        <v>1.388510535942363</v>
+      </c>
+      <c r="U34">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.786953558261301</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2186234898747793</v>
+      </c>
+      <c r="C35">
+        <v>42.74353166106015</v>
+      </c>
+      <c r="D35">
+        <v>50.44053166106016</v>
+      </c>
+      <c r="E35">
+        <v>20.097</v>
+      </c>
+      <c r="F35">
+        <v>20.097</v>
+      </c>
+      <c r="G35">
+        <v>12.4</v>
+      </c>
+      <c r="H35">
+        <v>60.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K35">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L35">
+        <v>7.01</v>
+      </c>
+      <c r="M35">
+        <v>1.065141</v>
+      </c>
+      <c r="N35">
+        <v>5.944858999999999</v>
+      </c>
+      <c r="O35">
+        <v>0.89172885</v>
+      </c>
+      <c r="P35">
+        <v>5.053130149999999</v>
+      </c>
+      <c r="Q35">
+        <v>7.083130149999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3041149102608646</v>
+      </c>
+      <c r="T35">
+        <v>1.407014141165475</v>
+      </c>
+      <c r="U35">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>6.581288298920048</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2184054622737144</v>
+      </c>
+      <c r="C36">
+        <v>42.19576269476747</v>
+      </c>
+      <c r="D36">
+        <v>50.50176269476747</v>
+      </c>
+      <c r="E36">
+        <v>20.706</v>
+      </c>
+      <c r="F36">
+        <v>20.706</v>
+      </c>
+      <c r="G36">
+        <v>12.4</v>
+      </c>
+      <c r="H36">
+        <v>60.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K36">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L36">
+        <v>7.01</v>
+      </c>
+      <c r="M36">
+        <v>1.097418</v>
+      </c>
+      <c r="N36">
+        <v>5.912582</v>
+      </c>
+      <c r="O36">
+        <v>0.8868873</v>
+      </c>
+      <c r="P36">
+        <v>5.0256947</v>
+      </c>
+      <c r="Q36">
+        <v>7.055694699999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3077097913238097</v>
+      </c>
+      <c r="T36">
+        <v>1.426078461698379</v>
+      </c>
+      <c r="U36">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>6.387720996010636</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2187824346726495</v>
+      </c>
+      <c r="C37">
+        <v>41.48098698021997</v>
+      </c>
+      <c r="D37">
+        <v>50.39598698021997</v>
+      </c>
+      <c r="E37">
+        <v>21.315</v>
+      </c>
+      <c r="F37">
+        <v>21.315</v>
+      </c>
+      <c r="G37">
+        <v>12.4</v>
+      </c>
+      <c r="H37">
+        <v>60.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K37">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L37">
+        <v>7.01</v>
+      </c>
+      <c r="M37">
+        <v>1.172325</v>
+      </c>
+      <c r="N37">
+        <v>5.837675</v>
+      </c>
+      <c r="O37">
+        <v>0.8756512500000001</v>
+      </c>
+      <c r="P37">
+        <v>4.96202375</v>
+      </c>
+      <c r="Q37">
+        <v>6.99202375</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3114152841117685</v>
+      </c>
+      <c r="T37">
+        <v>1.445729376709219</v>
+      </c>
+      <c r="U37">
+        <v>0.055</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.04675</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.979570511590215</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2185814070715846</v>
+      </c>
+      <c r="C38">
+        <v>40.92833866046851</v>
+      </c>
+      <c r="D38">
+        <v>50.45233866046851</v>
+      </c>
+      <c r="E38">
+        <v>21.924</v>
+      </c>
+      <c r="F38">
+        <v>21.924</v>
+      </c>
+      <c r="G38">
+        <v>12.4</v>
+      </c>
+      <c r="H38">
+        <v>60.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K38">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L38">
+        <v>7.01</v>
+      </c>
+      <c r="M38">
+        <v>1.20582</v>
+      </c>
+      <c r="N38">
+        <v>5.80418</v>
+      </c>
+      <c r="O38">
+        <v>0.870627</v>
+      </c>
+      <c r="P38">
+        <v>4.933553</v>
+      </c>
+      <c r="Q38">
+        <v>6.963552999999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.315236573549351</v>
+      </c>
+      <c r="T38">
+        <v>1.465994382814146</v>
+      </c>
+      <c r="U38">
+        <v>0.055</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.04675</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.81347133071271</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2183803794705197</v>
+      </c>
+      <c r="C39">
+        <v>40.37581650420027</v>
+      </c>
+      <c r="D39">
+        <v>50.50881650420028</v>
+      </c>
+      <c r="E39">
+        <v>22.533</v>
+      </c>
+      <c r="F39">
+        <v>22.533</v>
+      </c>
+      <c r="G39">
+        <v>12.4</v>
+      </c>
+      <c r="H39">
+        <v>60.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K39">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L39">
+        <v>7.01</v>
+      </c>
+      <c r="M39">
+        <v>1.239315</v>
+      </c>
+      <c r="N39">
+        <v>5.770685</v>
+      </c>
+      <c r="O39">
+        <v>0.8656027500000002</v>
+      </c>
+      <c r="P39">
+        <v>4.90508225</v>
+      </c>
+      <c r="Q39">
+        <v>6.93508225</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3191791737627298</v>
+      </c>
+      <c r="T39">
+        <v>1.486902722446215</v>
+      </c>
+      <c r="U39">
+        <v>0.055</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.04675</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.656350483936691</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2181793518694549</v>
+      </c>
+      <c r="C40">
+        <v>39.82342093558351</v>
+      </c>
+      <c r="D40">
+        <v>50.56542093558352</v>
+      </c>
+      <c r="E40">
+        <v>23.142</v>
+      </c>
+      <c r="F40">
+        <v>23.142</v>
+      </c>
+      <c r="G40">
+        <v>12.4</v>
+      </c>
+      <c r="H40">
+        <v>60.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K40">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L40">
+        <v>7.01</v>
+      </c>
+      <c r="M40">
+        <v>1.27281</v>
+      </c>
+      <c r="N40">
+        <v>5.73719</v>
+      </c>
+      <c r="O40">
+        <v>0.8605785000000001</v>
+      </c>
+      <c r="P40">
+        <v>4.8766115</v>
+      </c>
+      <c r="Q40">
+        <v>6.906611499999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.323248954628153</v>
+      </c>
+      <c r="T40">
+        <v>1.50848552464706</v>
+      </c>
+      <c r="U40">
+        <v>0.055</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.04675</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.507499155412041</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.21797832426839</v>
+      </c>
+      <c r="C41">
+        <v>39.27115238069007</v>
+      </c>
+      <c r="D41">
+        <v>50.62215238069007</v>
+      </c>
+      <c r="E41">
+        <v>23.751</v>
+      </c>
+      <c r="F41">
+        <v>23.751</v>
+      </c>
+      <c r="G41">
+        <v>12.4</v>
+      </c>
+      <c r="H41">
+        <v>60.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K41">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L41">
+        <v>7.01</v>
+      </c>
+      <c r="M41">
+        <v>1.306305</v>
+      </c>
+      <c r="N41">
+        <v>5.703695</v>
+      </c>
+      <c r="O41">
+        <v>0.8555542500000001</v>
+      </c>
+      <c r="P41">
+        <v>4.84814075</v>
+      </c>
+      <c r="Q41">
+        <v>6.878140749999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3274521709317869</v>
+      </c>
+      <c r="T41">
+        <v>1.530775959706949</v>
+      </c>
+      <c r="U41">
+        <v>0.055</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.04675</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.366281228350194</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2177772966673251</v>
+      </c>
+      <c r="C42">
+        <v>38.71901126750601</v>
+      </c>
+      <c r="D42">
+        <v>50.67901126750601</v>
+      </c>
+      <c r="E42">
+        <v>24.36</v>
+      </c>
+      <c r="F42">
+        <v>24.36</v>
+      </c>
+      <c r="G42">
+        <v>12.4</v>
+      </c>
+      <c r="H42">
+        <v>60.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K42">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L42">
+        <v>7.01</v>
+      </c>
+      <c r="M42">
+        <v>1.3398</v>
+      </c>
+      <c r="N42">
+        <v>5.670199999999999</v>
+      </c>
+      <c r="O42">
+        <v>0.85053</v>
+      </c>
+      <c r="P42">
+        <v>4.819669999999999</v>
+      </c>
+      <c r="Q42">
+        <v>6.849669999999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3317954944455418</v>
+      </c>
+      <c r="T42">
+        <v>1.553809409268835</v>
+      </c>
+      <c r="U42">
+        <v>0.055</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.04675</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.232124197641439</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2175762690662602</v>
+      </c>
+      <c r="C43">
+        <v>38.16699802594245</v>
+      </c>
+      <c r="D43">
+        <v>50.73599802594246</v>
+      </c>
+      <c r="E43">
+        <v>24.969</v>
+      </c>
+      <c r="F43">
+        <v>24.969</v>
+      </c>
+      <c r="G43">
+        <v>12.4</v>
+      </c>
+      <c r="H43">
+        <v>60.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K43">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L43">
+        <v>7.01</v>
+      </c>
+      <c r="M43">
+        <v>1.373295</v>
+      </c>
+      <c r="N43">
+        <v>5.636704999999999</v>
+      </c>
+      <c r="O43">
+        <v>0.8455057500000001</v>
+      </c>
+      <c r="P43">
+        <v>4.791199249999999</v>
+      </c>
+      <c r="Q43">
+        <v>6.821199249999998</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3362860492648478</v>
+      </c>
+      <c r="T43">
+        <v>1.577623653731123</v>
+      </c>
+      <c r="U43">
+        <v>0.055</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.04675</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.10451141233311</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2173752414651954</v>
+      </c>
+      <c r="C44">
+        <v>37.61511308784634</v>
+      </c>
+      <c r="D44">
+        <v>50.79311308784634</v>
+      </c>
+      <c r="E44">
+        <v>25.578</v>
+      </c>
+      <c r="F44">
+        <v>25.578</v>
+      </c>
+      <c r="G44">
+        <v>12.4</v>
+      </c>
+      <c r="H44">
+        <v>60.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K44">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L44">
+        <v>7.01</v>
+      </c>
+      <c r="M44">
+        <v>1.40679</v>
+      </c>
+      <c r="N44">
+        <v>5.60321</v>
+      </c>
+      <c r="O44">
+        <v>0.8404815000000001</v>
+      </c>
+      <c r="P44">
+        <v>4.7627285</v>
+      </c>
+      <c r="Q44">
+        <v>6.792728499999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3409314508020609</v>
+      </c>
+      <c r="T44">
+        <v>1.602259079036938</v>
+      </c>
+      <c r="U44">
+        <v>0.055</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.04675</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.982975426325179</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2171742138641305</v>
+      </c>
+      <c r="C45">
+        <v>37.06335688701142</v>
+      </c>
+      <c r="D45">
+        <v>50.85035688701142</v>
+      </c>
+      <c r="E45">
+        <v>26.187</v>
+      </c>
+      <c r="F45">
+        <v>26.187</v>
+      </c>
+      <c r="G45">
+        <v>12.4</v>
+      </c>
+      <c r="H45">
+        <v>60.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K45">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L45">
+        <v>7.01</v>
+      </c>
+      <c r="M45">
+        <v>1.440285</v>
+      </c>
+      <c r="N45">
+        <v>5.569715</v>
+      </c>
+      <c r="O45">
+        <v>0.8354572500000002</v>
+      </c>
+      <c r="P45">
+        <v>4.73425775</v>
+      </c>
+      <c r="Q45">
+        <v>6.76425775</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3457398488844394</v>
+      </c>
+      <c r="T45">
+        <v>1.627758905230677</v>
+      </c>
+      <c r="U45">
+        <v>0.055</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.04675</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.867092276875757</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2169731862630656</v>
+      </c>
+      <c r="C46">
+        <v>36.51172985918916</v>
+      </c>
+      <c r="D46">
+        <v>50.90772985918916</v>
+      </c>
+      <c r="E46">
+        <v>26.796</v>
+      </c>
+      <c r="F46">
+        <v>26.796</v>
+      </c>
+      <c r="G46">
+        <v>12.4</v>
+      </c>
+      <c r="H46">
+        <v>60.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K46">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L46">
+        <v>7.01</v>
+      </c>
+      <c r="M46">
+        <v>1.47378</v>
+      </c>
+      <c r="N46">
+        <v>5.53622</v>
+      </c>
+      <c r="O46">
+        <v>0.8304330000000002</v>
+      </c>
+      <c r="P46">
+        <v>4.705787</v>
+      </c>
+      <c r="Q46">
+        <v>6.735786999999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3507199754697599</v>
+      </c>
+      <c r="T46">
+        <v>1.654169439502764</v>
+      </c>
+      <c r="U46">
+        <v>0.055</v>
+      </c>
+      <c r="V46">
+        <v>0.15</v>
+      </c>
+      <c r="W46">
+        <v>0.04675</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.756476543310399</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2167721586620007</v>
+      </c>
+      <c r="C47">
+        <v>35.96023244209982</v>
+      </c>
+      <c r="D47">
+        <v>50.96523244209982</v>
+      </c>
+      <c r="E47">
+        <v>27.405</v>
+      </c>
+      <c r="F47">
+        <v>27.405</v>
+      </c>
+      <c r="G47">
+        <v>12.4</v>
+      </c>
+      <c r="H47">
+        <v>60.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K47">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L47">
+        <v>7.01</v>
+      </c>
+      <c r="M47">
+        <v>1.507275</v>
+      </c>
+      <c r="N47">
+        <v>5.502725</v>
+      </c>
+      <c r="O47">
+        <v>0.8254087500000001</v>
+      </c>
+      <c r="P47">
+        <v>4.67731625</v>
+      </c>
+      <c r="Q47">
+        <v>6.707316249999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.355881197567274</v>
+      </c>
+      <c r="T47">
+        <v>1.68154035683929</v>
+      </c>
+      <c r="U47">
+        <v>0.055</v>
+      </c>
+      <c r="V47">
+        <v>0.15</v>
+      </c>
+      <c r="W47">
+        <v>0.04675</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.650777064570168</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2165711310609358</v>
+      </c>
+      <c r="C48">
+        <v>35.40886507544363</v>
+      </c>
+      <c r="D48">
+        <v>51.02286507544363</v>
+      </c>
+      <c r="E48">
+        <v>28.014</v>
+      </c>
+      <c r="F48">
+        <v>28.014</v>
+      </c>
+      <c r="G48">
+        <v>12.4</v>
+      </c>
+      <c r="H48">
+        <v>60.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K48">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L48">
+        <v>7.01</v>
+      </c>
+      <c r="M48">
+        <v>1.54077</v>
+      </c>
+      <c r="N48">
+        <v>5.46923</v>
+      </c>
+      <c r="O48">
+        <v>0.8203845000000001</v>
+      </c>
+      <c r="P48">
+        <v>4.648845499999999</v>
+      </c>
+      <c r="Q48">
+        <v>6.678845499999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.36123357603877</v>
+      </c>
+      <c r="T48">
+        <v>1.709925011854947</v>
+      </c>
+      <c r="U48">
+        <v>0.055</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.04675</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.549673215340381</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2178882034598709</v>
+      </c>
+      <c r="C49">
+        <v>34.42462647230182</v>
+      </c>
+      <c r="D49">
+        <v>50.64762647230182</v>
+      </c>
+      <c r="E49">
+        <v>28.623</v>
+      </c>
+      <c r="F49">
+        <v>28.623</v>
+      </c>
+      <c r="G49">
+        <v>12.4</v>
+      </c>
+      <c r="H49">
+        <v>60.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K49">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L49">
+        <v>7.01</v>
+      </c>
+      <c r="M49">
+        <v>1.6830324</v>
+      </c>
+      <c r="N49">
+        <v>5.3269676</v>
+      </c>
+      <c r="O49">
+        <v>0.79904514</v>
+      </c>
+      <c r="P49">
+        <v>4.527922459999999</v>
+      </c>
+      <c r="Q49">
+        <v>6.557922459999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3667879310563603</v>
+      </c>
+      <c r="T49">
+        <v>1.739380785927798</v>
+      </c>
+      <c r="U49">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.15</v>
+      </c>
+      <c r="W49">
+        <v>0.04998</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.165101040241411</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2177194758588061</v>
+      </c>
+      <c r="C50">
+        <v>33.8633890340536</v>
+      </c>
+      <c r="D50">
+        <v>50.6953890340536</v>
+      </c>
+      <c r="E50">
+        <v>29.232</v>
+      </c>
+      <c r="F50">
+        <v>29.232</v>
+      </c>
+      <c r="G50">
+        <v>12.4</v>
+      </c>
+      <c r="H50">
+        <v>60.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K50">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L50">
+        <v>7.01</v>
+      </c>
+      <c r="M50">
+        <v>1.7188416</v>
+      </c>
+      <c r="N50">
+        <v>5.2911584</v>
+      </c>
+      <c r="O50">
+        <v>0.79367376</v>
+      </c>
+      <c r="P50">
+        <v>4.49748464</v>
+      </c>
+      <c r="Q50">
+        <v>6.527484639999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3725559151130886</v>
+      </c>
+      <c r="T50">
+        <v>1.769969474388067</v>
+      </c>
+      <c r="U50">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.15</v>
+      </c>
+      <c r="W50">
+        <v>0.04998</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.078328101903049</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2193000482577412</v>
+      </c>
+      <c r="C51">
+        <v>32.81046819617058</v>
+      </c>
+      <c r="D51">
+        <v>50.25146819617058</v>
+      </c>
+      <c r="E51">
+        <v>29.841</v>
+      </c>
+      <c r="F51">
+        <v>29.841</v>
+      </c>
+      <c r="G51">
+        <v>12.4</v>
+      </c>
+      <c r="H51">
+        <v>60.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K51">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L51">
+        <v>7.01</v>
+      </c>
+      <c r="M51">
+        <v>1.879983</v>
+      </c>
+      <c r="N51">
+        <v>5.130017</v>
+      </c>
+      <c r="O51">
+        <v>0.76950255</v>
+      </c>
+      <c r="P51">
+        <v>4.360514449999999</v>
+      </c>
+      <c r="Q51">
+        <v>6.390514449999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3785500946230219</v>
+      </c>
+      <c r="T51">
+        <v>1.801757719258542</v>
+      </c>
+      <c r="U51">
+        <v>0.063</v>
+      </c>
+      <c r="V51">
+        <v>0.15</v>
+      </c>
+      <c r="W51">
+        <v>0.05355</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.72875712173993</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2191670206566763</v>
+      </c>
+      <c r="C52">
+        <v>32.23853058285184</v>
+      </c>
+      <c r="D52">
+        <v>50.28853058285184</v>
+      </c>
+      <c r="E52">
+        <v>30.45</v>
+      </c>
+      <c r="F52">
+        <v>30.45</v>
+      </c>
+      <c r="G52">
+        <v>12.4</v>
+      </c>
+      <c r="H52">
+        <v>60.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K52">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L52">
+        <v>7.01</v>
+      </c>
+      <c r="M52">
+        <v>1.91835</v>
+      </c>
+      <c r="N52">
+        <v>5.09165</v>
+      </c>
+      <c r="O52">
+        <v>0.7637475</v>
+      </c>
+      <c r="P52">
+        <v>4.3279025</v>
+      </c>
+      <c r="Q52">
+        <v>6.357902499999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3847840413133526</v>
+      </c>
+      <c r="T52">
+        <v>1.834817493923836</v>
+      </c>
+      <c r="U52">
+        <v>0.063</v>
+      </c>
+      <c r="V52">
+        <v>0.15</v>
+      </c>
+      <c r="W52">
+        <v>0.05355</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.654181979305132</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2190339930556114</v>
+      </c>
+      <c r="C53">
+        <v>31.6666476797496</v>
+      </c>
+      <c r="D53">
+        <v>50.3256476797496</v>
+      </c>
+      <c r="E53">
+        <v>31.059</v>
+      </c>
+      <c r="F53">
+        <v>31.059</v>
+      </c>
+      <c r="G53">
+        <v>12.4</v>
+      </c>
+      <c r="H53">
+        <v>60.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K53">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L53">
+        <v>7.01</v>
+      </c>
+      <c r="M53">
+        <v>1.956717</v>
+      </c>
+      <c r="N53">
+        <v>5.053283</v>
+      </c>
+      <c r="O53">
+        <v>0.75799245</v>
+      </c>
+      <c r="P53">
+        <v>4.29529055</v>
+      </c>
+      <c r="Q53">
+        <v>6.325290549999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3912724348073702</v>
+      </c>
+      <c r="T53">
+        <v>1.869226647146898</v>
+      </c>
+      <c r="U53">
+        <v>0.063</v>
+      </c>
+      <c r="V53">
+        <v>0.15</v>
+      </c>
+      <c r="W53">
+        <v>0.05355</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>3.582531352259933</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2189009654545465</v>
+      </c>
+      <c r="C54">
+        <v>31.09481960809533</v>
+      </c>
+      <c r="D54">
+        <v>50.36281960809533</v>
+      </c>
+      <c r="E54">
+        <v>31.668</v>
+      </c>
+      <c r="F54">
+        <v>31.668</v>
+      </c>
+      <c r="G54">
+        <v>12.4</v>
+      </c>
+      <c r="H54">
+        <v>60.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K54">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L54">
+        <v>7.01</v>
+      </c>
+      <c r="M54">
+        <v>1.995084</v>
+      </c>
+      <c r="N54">
+        <v>5.014915999999999</v>
+      </c>
+      <c r="O54">
+        <v>0.7522374000000001</v>
+      </c>
+      <c r="P54">
+        <v>4.262678599999999</v>
+      </c>
+      <c r="Q54">
+        <v>6.292678599999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3980311780303053</v>
+      </c>
+      <c r="T54">
+        <v>1.905069515087587</v>
+      </c>
+      <c r="U54">
+        <v>0.063</v>
+      </c>
+      <c r="V54">
+        <v>0.15</v>
+      </c>
+      <c r="W54">
+        <v>0.05355</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.513636518562627</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2219664878534816</v>
+      </c>
+      <c r="C55">
+        <v>29.64293424521365</v>
+      </c>
+      <c r="D55">
+        <v>49.51993424521365</v>
+      </c>
+      <c r="E55">
+        <v>32.277</v>
+      </c>
+      <c r="F55">
+        <v>32.277</v>
+      </c>
+      <c r="G55">
+        <v>12.4</v>
+      </c>
+      <c r="H55">
+        <v>60.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K55">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L55">
+        <v>7.01</v>
+      </c>
+      <c r="M55">
+        <v>2.2626177</v>
+      </c>
+      <c r="N55">
+        <v>4.7473823</v>
+      </c>
+      <c r="O55">
+        <v>0.7121073450000001</v>
+      </c>
+      <c r="P55">
+        <v>4.035274955</v>
+      </c>
+      <c r="Q55">
+        <v>6.065274955</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.4050775273478333</v>
+      </c>
+      <c r="T55">
+        <v>1.942437611451284</v>
+      </c>
+      <c r="U55">
+        <v>0.0701</v>
+      </c>
+      <c r="V55">
+        <v>0.15</v>
+      </c>
+      <c r="W55">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.098181367537256</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2218938102524168</v>
+      </c>
+      <c r="C56">
+        <v>29.05359078095819</v>
+      </c>
+      <c r="D56">
+        <v>49.53959078095819</v>
+      </c>
+      <c r="E56">
+        <v>32.886</v>
+      </c>
+      <c r="F56">
+        <v>32.886</v>
+      </c>
+      <c r="G56">
+        <v>12.4</v>
+      </c>
+      <c r="H56">
+        <v>60.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K56">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L56">
+        <v>7.01</v>
+      </c>
+      <c r="M56">
+        <v>2.3053086</v>
+      </c>
+      <c r="N56">
+        <v>4.7046914</v>
+      </c>
+      <c r="O56">
+        <v>0.7057037100000001</v>
+      </c>
+      <c r="P56">
+        <v>3.99898769</v>
+      </c>
+      <c r="Q56">
+        <v>6.028987689999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.412430239679167</v>
+      </c>
+      <c r="T56">
+        <v>1.981430407656881</v>
+      </c>
+      <c r="U56">
+        <v>0.0701</v>
+      </c>
+      <c r="V56">
+        <v>0.15</v>
+      </c>
+      <c r="W56">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.040807638508788</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2317788826513519</v>
+      </c>
+      <c r="C57">
+        <v>25.90699477690152</v>
+      </c>
+      <c r="D57">
+        <v>47.00199477690153</v>
+      </c>
+      <c r="E57">
+        <v>33.495</v>
+      </c>
+      <c r="F57">
+        <v>33.495</v>
+      </c>
+      <c r="G57">
+        <v>12.4</v>
+      </c>
+      <c r="H57">
+        <v>60.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K57">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L57">
+        <v>7.01</v>
+      </c>
+      <c r="M57">
+        <v>3.061443000000001</v>
+      </c>
+      <c r="N57">
+        <v>3.948556999999999</v>
+      </c>
+      <c r="O57">
+        <v>0.59228355</v>
+      </c>
+      <c r="P57">
+        <v>3.356273449999999</v>
+      </c>
+      <c r="Q57">
+        <v>5.386273449999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.4201097392252265</v>
+      </c>
+      <c r="T57">
+        <v>2.022156217027171</v>
+      </c>
+      <c r="U57">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.15</v>
+      </c>
+      <c r="W57">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.289769889558616</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.231887255050287</v>
+      </c>
+      <c r="C58">
+        <v>25.27161437739053</v>
+      </c>
+      <c r="D58">
+        <v>46.97561437739054</v>
+      </c>
+      <c r="E58">
+        <v>34.104</v>
+      </c>
+      <c r="F58">
+        <v>34.104</v>
+      </c>
+      <c r="G58">
+        <v>12.4</v>
+      </c>
+      <c r="H58">
+        <v>60.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K58">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L58">
+        <v>7.01</v>
+      </c>
+      <c r="M58">
+        <v>3.1171056</v>
+      </c>
+      <c r="N58">
+        <v>3.892894399999999</v>
+      </c>
+      <c r="O58">
+        <v>0.58393416</v>
+      </c>
+      <c r="P58">
+        <v>3.308960239999999</v>
+      </c>
+      <c r="Q58">
+        <v>5.338960239999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4281383069324705</v>
+      </c>
+      <c r="T58">
+        <v>2.064733199550656</v>
+      </c>
+      <c r="U58">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.15</v>
+      </c>
+      <c r="W58">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.248881141530784</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2319956274492221</v>
+      </c>
+      <c r="C59">
+        <v>24.63626357386178</v>
+      </c>
+      <c r="D59">
+        <v>46.94926357386178</v>
+      </c>
+      <c r="E59">
+        <v>34.713</v>
+      </c>
+      <c r="F59">
+        <v>34.713</v>
+      </c>
+      <c r="G59">
+        <v>12.4</v>
+      </c>
+      <c r="H59">
+        <v>60.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K59">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L59">
+        <v>7.01</v>
+      </c>
+      <c r="M59">
+        <v>3.172768200000001</v>
+      </c>
+      <c r="N59">
+        <v>3.837231799999999</v>
+      </c>
+      <c r="O59">
+        <v>0.57558477</v>
+      </c>
+      <c r="P59">
+        <v>3.261647029999999</v>
+      </c>
+      <c r="Q59">
+        <v>5.291647029999998</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4365402963935399</v>
+      </c>
+      <c r="T59">
+        <v>2.109290506842676</v>
+      </c>
+      <c r="U59">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.15</v>
+      </c>
+      <c r="W59">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.209427086416209</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2321039998481572</v>
+      </c>
+      <c r="C60">
+        <v>24.00094231653791</v>
+      </c>
+      <c r="D60">
+        <v>46.92294231653791</v>
+      </c>
+      <c r="E60">
+        <v>35.322</v>
+      </c>
+      <c r="F60">
+        <v>35.322</v>
+      </c>
+      <c r="G60">
+        <v>12.4</v>
+      </c>
+      <c r="H60">
+        <v>60.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K60">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L60">
+        <v>7.01</v>
+      </c>
+      <c r="M60">
+        <v>3.2284308</v>
+      </c>
+      <c r="N60">
+        <v>3.7815692</v>
+      </c>
+      <c r="O60">
+        <v>0.5672353800000001</v>
+      </c>
+      <c r="P60">
+        <v>3.21433382</v>
+      </c>
+      <c r="Q60">
+        <v>5.24433382</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4453423805908506</v>
+      </c>
+      <c r="T60">
+        <v>2.15596959067241</v>
+      </c>
+      <c r="U60">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V60">
+        <v>0.15</v>
+      </c>
+      <c r="W60">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.171333515960757</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2322123722470923</v>
+      </c>
+      <c r="C61">
+        <v>23.36565055575313</v>
+      </c>
+      <c r="D61">
+        <v>46.89665055575313</v>
+      </c>
+      <c r="E61">
+        <v>35.931</v>
+      </c>
+      <c r="F61">
+        <v>35.931</v>
+      </c>
+      <c r="G61">
+        <v>12.4</v>
+      </c>
+      <c r="H61">
+        <v>60.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K61">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L61">
+        <v>7.01</v>
+      </c>
+      <c r="M61">
+        <v>3.2840934</v>
+      </c>
+      <c r="N61">
+        <v>3.7259066</v>
+      </c>
+      <c r="O61">
+        <v>0.5588859900000001</v>
+      </c>
+      <c r="P61">
+        <v>3.16702061</v>
+      </c>
+      <c r="Q61">
+        <v>5.197020609999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4545738347490057</v>
+      </c>
+      <c r="T61">
+        <v>2.204925702981643</v>
+      </c>
+      <c r="U61">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V61">
+        <v>0.15</v>
+      </c>
+      <c r="W61">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.134531252978372</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2323207446460275</v>
+      </c>
+      <c r="C62">
+        <v>22.73038824195289</v>
+      </c>
+      <c r="D62">
+        <v>46.8703882419529</v>
+      </c>
+      <c r="E62">
+        <v>36.54</v>
+      </c>
+      <c r="F62">
+        <v>36.54</v>
+      </c>
+      <c r="G62">
+        <v>12.4</v>
+      </c>
+      <c r="H62">
+        <v>60.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K62">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L62">
+        <v>7.01</v>
+      </c>
+      <c r="M62">
+        <v>3.339756</v>
+      </c>
+      <c r="N62">
+        <v>3.670243999999999</v>
+      </c>
+      <c r="O62">
+        <v>0.5505366</v>
+      </c>
+      <c r="P62">
+        <v>3.119707399999999</v>
+      </c>
+      <c r="Q62">
+        <v>5.149707399999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4642668616150686</v>
+      </c>
+      <c r="T62">
+        <v>2.256329620906339</v>
+      </c>
+      <c r="U62">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V62">
+        <v>0.15</v>
+      </c>
+      <c r="W62">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.098955732095398</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2324291170449626</v>
+      </c>
+      <c r="C63">
+        <v>22.0951553256936</v>
+      </c>
+      <c r="D63">
+        <v>46.84415532569361</v>
+      </c>
+      <c r="E63">
+        <v>37.149</v>
+      </c>
+      <c r="F63">
+        <v>37.149</v>
+      </c>
+      <c r="G63">
+        <v>12.4</v>
+      </c>
+      <c r="H63">
+        <v>60.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K63">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L63">
+        <v>7.01</v>
+      </c>
+      <c r="M63">
+        <v>3.395418600000001</v>
+      </c>
+      <c r="N63">
+        <v>3.614581399999999</v>
+      </c>
+      <c r="O63">
+        <v>0.5421872099999999</v>
+      </c>
+      <c r="P63">
+        <v>3.072394189999999</v>
+      </c>
+      <c r="Q63">
+        <v>5.102394189999998</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4744569667819554</v>
+      </c>
+      <c r="T63">
+        <v>2.310369637186147</v>
+      </c>
+      <c r="U63">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V63">
+        <v>0.15</v>
+      </c>
+      <c r="W63">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.064546621733179</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2325374894438977</v>
+      </c>
+      <c r="C64">
+        <v>21.45995175764229</v>
+      </c>
+      <c r="D64">
+        <v>46.81795175764228</v>
+      </c>
+      <c r="E64">
+        <v>37.758</v>
+      </c>
+      <c r="F64">
+        <v>37.758</v>
+      </c>
+      <c r="G64">
+        <v>12.4</v>
+      </c>
+      <c r="H64">
+        <v>60.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K64">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L64">
+        <v>7.01</v>
+      </c>
+      <c r="M64">
+        <v>3.4510812</v>
+      </c>
+      <c r="N64">
+        <v>3.5589188</v>
+      </c>
+      <c r="O64">
+        <v>0.53383782</v>
+      </c>
+      <c r="P64">
+        <v>3.02508098</v>
+      </c>
+      <c r="Q64">
+        <v>5.05508098</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4851833932734151</v>
+      </c>
+      <c r="T64">
+        <v>2.367253864849103</v>
+      </c>
+      <c r="U64">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V64">
+        <v>0.15</v>
+      </c>
+      <c r="W64">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.031247482672966</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2439449118428328</v>
+      </c>
+      <c r="C65">
+        <v>18.24756205250761</v>
+      </c>
+      <c r="D65">
+        <v>44.21456205250761</v>
+      </c>
+      <c r="E65">
+        <v>38.367</v>
+      </c>
+      <c r="F65">
+        <v>38.367</v>
+      </c>
+      <c r="G65">
+        <v>12.4</v>
+      </c>
+      <c r="H65">
+        <v>60.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K65">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L65">
+        <v>7.01</v>
+      </c>
+      <c r="M65">
+        <v>4.3162875</v>
+      </c>
+      <c r="N65">
+        <v>2.6937125</v>
+      </c>
+      <c r="O65">
+        <v>0.4040568750000001</v>
+      </c>
+      <c r="P65">
+        <v>2.289655625</v>
+      </c>
+      <c r="Q65">
+        <v>4.319655624999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4964896266022509</v>
+      </c>
+      <c r="T65">
+        <v>2.427212915628976</v>
+      </c>
+      <c r="U65">
+        <v>0.1125</v>
+      </c>
+      <c r="V65">
+        <v>0.15</v>
+      </c>
+      <c r="W65">
+        <v>0.095625</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.62408087969117</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.244232634241768</v>
+      </c>
+      <c r="C66">
+        <v>17.57663654632614</v>
+      </c>
+      <c r="D66">
+        <v>44.15263654632614</v>
+      </c>
+      <c r="E66">
+        <v>38.976</v>
+      </c>
+      <c r="F66">
+        <v>38.976</v>
+      </c>
+      <c r="G66">
+        <v>12.4</v>
+      </c>
+      <c r="H66">
+        <v>60.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K66">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L66">
+        <v>7.01</v>
+      </c>
+      <c r="M66">
+        <v>4.3848</v>
+      </c>
+      <c r="N66">
+        <v>2.6252</v>
+      </c>
+      <c r="O66">
+        <v>0.39378</v>
+      </c>
+      <c r="P66">
+        <v>2.23142</v>
+      </c>
+      <c r="Q66">
+        <v>4.261419999999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.5084239840049111</v>
+      </c>
+      <c r="T66">
+        <v>2.490503024785508</v>
+      </c>
+      <c r="U66">
+        <v>0.1125</v>
+      </c>
+      <c r="V66">
+        <v>0.15</v>
+      </c>
+      <c r="W66">
+        <v>0.095625</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>1.598704615945995</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2445203566407031</v>
+      </c>
+      <c r="C67">
+        <v>16.90588425931932</v>
+      </c>
+      <c r="D67">
+        <v>44.09088425931932</v>
+      </c>
+      <c r="E67">
+        <v>39.585</v>
+      </c>
+      <c r="F67">
+        <v>39.585</v>
+      </c>
+      <c r="G67">
+        <v>12.4</v>
+      </c>
+      <c r="H67">
+        <v>60.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K67">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L67">
+        <v>7.01</v>
+      </c>
+      <c r="M67">
+        <v>4.4533125</v>
+      </c>
+      <c r="N67">
+        <v>2.5566875</v>
+      </c>
+      <c r="O67">
+        <v>0.383503125</v>
+      </c>
+      <c r="P67">
+        <v>2.173184375</v>
+      </c>
+      <c r="Q67">
+        <v>4.203184374999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5210403046877232</v>
+      </c>
+      <c r="T67">
+        <v>2.557409711608127</v>
+      </c>
+      <c r="U67">
+        <v>0.1125</v>
+      </c>
+      <c r="V67">
+        <v>0.15</v>
+      </c>
+      <c r="W67">
+        <v>0.095625</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>1.574109160316057</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2448080790396382</v>
+      </c>
+      <c r="C68">
+        <v>16.23530446570442</v>
+      </c>
+      <c r="D68">
+        <v>44.02930446570443</v>
+      </c>
+      <c r="E68">
+        <v>40.194</v>
+      </c>
+      <c r="F68">
+        <v>40.194</v>
+      </c>
+      <c r="G68">
+        <v>12.4</v>
+      </c>
+      <c r="H68">
+        <v>60.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K68">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L68">
+        <v>7.01</v>
+      </c>
+      <c r="M68">
+        <v>4.521825000000001</v>
+      </c>
+      <c r="N68">
+        <v>2.488174999999999</v>
+      </c>
+      <c r="O68">
+        <v>0.3732262499999999</v>
+      </c>
+      <c r="P68">
+        <v>2.114948749999999</v>
+      </c>
+      <c r="Q68">
+        <v>4.144948749999998</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.534398761881289</v>
+      </c>
+      <c r="T68">
+        <v>2.628252085890901</v>
+      </c>
+      <c r="U68">
+        <v>0.1125</v>
+      </c>
+      <c r="V68">
+        <v>0.15</v>
+      </c>
+      <c r="W68">
+        <v>0.095625</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>1.550259021523389</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2450958014385733</v>
+      </c>
+      <c r="C69">
+        <v>15.56489644374773</v>
+      </c>
+      <c r="D69">
+        <v>43.96789644374773</v>
+      </c>
+      <c r="E69">
+        <v>40.803</v>
+      </c>
+      <c r="F69">
+        <v>40.803</v>
+      </c>
+      <c r="G69">
+        <v>12.4</v>
+      </c>
+      <c r="H69">
+        <v>60.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K69">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L69">
+        <v>7.01</v>
+      </c>
+      <c r="M69">
+        <v>4.5903375</v>
+      </c>
+      <c r="N69">
+        <v>2.419662499999999</v>
+      </c>
+      <c r="O69">
+        <v>0.362949375</v>
+      </c>
+      <c r="P69">
+        <v>2.056713124999999</v>
+      </c>
+      <c r="Q69">
+        <v>4.086713124999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5485668225411313</v>
+      </c>
+      <c r="T69">
+        <v>2.703387937402934</v>
+      </c>
+      <c r="U69">
+        <v>0.1125</v>
+      </c>
+      <c r="V69">
+        <v>0.15</v>
+      </c>
+      <c r="W69">
+        <v>0.095625</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>1.527120827172294</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2453835238375085</v>
+      </c>
+      <c r="C70">
+        <v>14.89465947573629</v>
+      </c>
+      <c r="D70">
+        <v>43.90665947573629</v>
+      </c>
+      <c r="E70">
+        <v>41.412</v>
+      </c>
+      <c r="F70">
+        <v>41.412</v>
+      </c>
+      <c r="G70">
+        <v>12.4</v>
+      </c>
+      <c r="H70">
+        <v>60.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K70">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L70">
+        <v>7.01</v>
+      </c>
+      <c r="M70">
+        <v>4.65885</v>
+      </c>
+      <c r="N70">
+        <v>2.35115</v>
+      </c>
+      <c r="O70">
+        <v>0.3526725</v>
+      </c>
+      <c r="P70">
+        <v>1.9984775</v>
+      </c>
+      <c r="Q70">
+        <v>4.028477499999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5636203869922141</v>
+      </c>
+      <c r="T70">
+        <v>2.783219779634468</v>
+      </c>
+      <c r="U70">
+        <v>0.1125</v>
+      </c>
+      <c r="V70">
+        <v>0.15</v>
+      </c>
+      <c r="W70">
+        <v>0.095625</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>1.504663167949172</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3010098661923765</v>
+      </c>
+      <c r="C71">
+        <v>4.971109618699195</v>
+      </c>
+      <c r="D71">
+        <v>34.5921096186992</v>
+      </c>
+      <c r="E71">
+        <v>42.021</v>
+      </c>
+      <c r="F71">
+        <v>42.021</v>
+      </c>
+      <c r="G71">
+        <v>12.4</v>
+      </c>
+      <c r="H71">
+        <v>60.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K71">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L71">
+        <v>7.01</v>
+      </c>
+      <c r="M71">
+        <v>8.261328600000001</v>
+      </c>
+      <c r="N71">
+        <v>-1.251328600000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.1876992900000002</v>
+      </c>
+      <c r="P71">
+        <v>-1.063629310000001</v>
+      </c>
+      <c r="Q71">
+        <v>0.9663706899999986</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.5891028259503008</v>
+      </c>
+      <c r="T71">
+        <v>2.918357876208693</v>
+      </c>
+      <c r="U71">
+        <v>0.1966</v>
+      </c>
+      <c r="V71">
+        <v>0.1272797695034186</v>
+      </c>
+      <c r="W71">
+        <v>0.1715767973156279</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.8485317966894573</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3025878661923765</v>
+      </c>
+      <c r="C72">
+        <v>4.155176867143069</v>
+      </c>
+      <c r="D72">
+        <v>34.38517686714307</v>
+      </c>
+      <c r="E72">
+        <v>42.63</v>
+      </c>
+      <c r="F72">
+        <v>42.63</v>
+      </c>
+      <c r="G72">
+        <v>12.4</v>
+      </c>
+      <c r="H72">
+        <v>60.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K72">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L72">
+        <v>7.01</v>
+      </c>
+      <c r="M72">
+        <v>8.381058000000001</v>
+      </c>
+      <c r="N72">
+        <v>-1.371058000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.2056587000000002</v>
+      </c>
+      <c r="P72">
+        <v>-1.165399300000001</v>
+      </c>
+      <c r="Q72">
+        <v>0.8646006999999982</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.6074462534819776</v>
+      </c>
+      <c r="T72">
+        <v>3.015636472082315</v>
+      </c>
+      <c r="U72">
+        <v>0.1966</v>
+      </c>
+      <c r="V72">
+        <v>0.1254614870819412</v>
+      </c>
+      <c r="W72">
+        <v>0.1719342716396904</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.8364099138796079</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3041658661923765</v>
+      </c>
+      <c r="C73">
+        <v>3.341705169728087</v>
+      </c>
+      <c r="D73">
+        <v>34.18070516972809</v>
+      </c>
+      <c r="E73">
+        <v>43.239</v>
+      </c>
+      <c r="F73">
+        <v>43.239</v>
+      </c>
+      <c r="G73">
+        <v>12.4</v>
+      </c>
+      <c r="H73">
+        <v>60.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K73">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L73">
+        <v>7.01</v>
+      </c>
+      <c r="M73">
+        <v>8.5007874</v>
+      </c>
+      <c r="N73">
+        <v>-1.4907874</v>
+      </c>
+      <c r="O73">
+        <v>-0.2236181100000001</v>
+      </c>
+      <c r="P73">
+        <v>-1.26716929</v>
+      </c>
+      <c r="Q73">
+        <v>0.7628307099999991</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.6270547449813559</v>
+      </c>
+      <c r="T73">
+        <v>3.119623936636878</v>
+      </c>
+      <c r="U73">
+        <v>0.1966</v>
+      </c>
+      <c r="V73">
+        <v>0.123694423883604</v>
+      </c>
+      <c r="W73">
+        <v>0.1722816762644835</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.8246294925573601</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3057438661923765</v>
+      </c>
+      <c r="C74">
+        <v>2.530650881958984</v>
+      </c>
+      <c r="D74">
+        <v>33.97865088195898</v>
+      </c>
+      <c r="E74">
+        <v>43.848</v>
+      </c>
+      <c r="F74">
+        <v>43.848</v>
+      </c>
+      <c r="G74">
+        <v>12.4</v>
+      </c>
+      <c r="H74">
+        <v>60.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K74">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L74">
+        <v>7.01</v>
+      </c>
+      <c r="M74">
+        <v>8.620516799999999</v>
+      </c>
+      <c r="N74">
+        <v>-1.610516799999999</v>
+      </c>
+      <c r="O74">
+        <v>-0.2415775199999999</v>
+      </c>
+      <c r="P74">
+        <v>-1.368939279999999</v>
+      </c>
+      <c r="Q74">
+        <v>0.66106072</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6480638430164045</v>
+      </c>
+      <c r="T74">
+        <v>3.231039077231052</v>
+      </c>
+      <c r="U74">
+        <v>0.1966</v>
+      </c>
+      <c r="V74">
+        <v>0.1219764457741095</v>
+      </c>
+      <c r="W74">
+        <v>0.1726194307608101</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.8131763051607301</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3073218661923764</v>
+      </c>
+      <c r="C75">
+        <v>1.721971385268326</v>
+      </c>
+      <c r="D75">
+        <v>33.77897138526833</v>
+      </c>
+      <c r="E75">
+        <v>44.457</v>
+      </c>
+      <c r="F75">
+        <v>44.457</v>
+      </c>
+      <c r="G75">
+        <v>12.4</v>
+      </c>
+      <c r="H75">
+        <v>60.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K75">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L75">
+        <v>7.01</v>
+      </c>
+      <c r="M75">
+        <v>8.7402462</v>
+      </c>
+      <c r="N75">
+        <v>-1.7302462</v>
+      </c>
+      <c r="O75">
+        <v>-0.25953693</v>
+      </c>
+      <c r="P75">
+        <v>-1.47070927</v>
+      </c>
+      <c r="Q75">
+        <v>0.5592907299999994</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.6706291705355305</v>
+      </c>
+      <c r="T75">
+        <v>3.350707191202572</v>
+      </c>
+      <c r="U75">
+        <v>0.1966</v>
+      </c>
+      <c r="V75">
+        <v>0.1203055355580258</v>
+      </c>
+      <c r="W75">
+        <v>0.1729479317092921</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.8020369037201721</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3229492030691006</v>
+      </c>
+      <c r="C76">
+        <v>-0.7447687015776623</v>
+      </c>
+      <c r="D76">
+        <v>31.92123129842233</v>
+      </c>
+      <c r="E76">
+        <v>45.066</v>
+      </c>
+      <c r="F76">
+        <v>45.066</v>
+      </c>
+      <c r="G76">
+        <v>12.4</v>
+      </c>
+      <c r="H76">
+        <v>60.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K76">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L76">
+        <v>7.01</v>
+      </c>
+      <c r="M76">
+        <v>9.635110799999998</v>
+      </c>
+      <c r="N76">
+        <v>-2.625110799999998</v>
+      </c>
+      <c r="O76">
+        <v>-0.3937666199999998</v>
+      </c>
+      <c r="P76">
+        <v>-2.231344179999998</v>
+      </c>
+      <c r="Q76">
+        <v>-0.2013441799999991</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.7000123573896821</v>
+      </c>
+      <c r="T76">
+        <v>3.506531676813463</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.1091321129384418</v>
+      </c>
+      <c r="W76">
+        <v>0.1904675542537611</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.7275474195896119</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3246992030691006</v>
+      </c>
+      <c r="C77">
+        <v>-1.549159784073055</v>
+      </c>
+      <c r="D77">
+        <v>31.72584021592694</v>
+      </c>
+      <c r="E77">
+        <v>45.675</v>
+      </c>
+      <c r="F77">
+        <v>45.675</v>
+      </c>
+      <c r="G77">
+        <v>12.4</v>
+      </c>
+      <c r="H77">
+        <v>60.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K77">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L77">
+        <v>7.01</v>
+      </c>
+      <c r="M77">
+        <v>9.765314999999999</v>
+      </c>
+      <c r="N77">
+        <v>-2.755315</v>
+      </c>
+      <c r="O77">
+        <v>-0.41329725</v>
+      </c>
+      <c r="P77">
+        <v>-2.34201775</v>
+      </c>
+      <c r="Q77">
+        <v>-0.3120177500000003</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.7264608516852695</v>
+      </c>
+      <c r="T77">
+        <v>3.646792943886002</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.1076770180992626</v>
+      </c>
+      <c r="W77">
+        <v>0.1907786535303777</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.717846787328417</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3264492030691006</v>
+      </c>
+      <c r="C78">
+        <v>-2.351173426334164</v>
+      </c>
+      <c r="D78">
+        <v>31.53282657366583</v>
+      </c>
+      <c r="E78">
+        <v>46.284</v>
+      </c>
+      <c r="F78">
+        <v>46.284</v>
+      </c>
+      <c r="G78">
+        <v>12.4</v>
+      </c>
+      <c r="H78">
+        <v>60.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K78">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L78">
+        <v>7.01</v>
+      </c>
+      <c r="M78">
+        <v>9.895519199999999</v>
+      </c>
+      <c r="N78">
+        <v>-2.885519199999999</v>
+      </c>
+      <c r="O78">
+        <v>-0.4328278799999999</v>
+      </c>
+      <c r="P78">
+        <v>-2.452691319999999</v>
+      </c>
+      <c r="Q78">
+        <v>-0.4226913199999998</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7551133871721558</v>
+      </c>
+      <c r="T78">
+        <v>3.798742649881252</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.1062602152295354</v>
+      </c>
+      <c r="W78">
+        <v>0.1910815659839253</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.7084014348635694</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3281992030691007</v>
+      </c>
+      <c r="C79">
+        <v>-3.150852757578697</v>
+      </c>
+      <c r="D79">
+        <v>31.34214724242131</v>
+      </c>
+      <c r="E79">
+        <v>46.893</v>
+      </c>
+      <c r="F79">
+        <v>46.893</v>
+      </c>
+      <c r="G79">
+        <v>12.4</v>
+      </c>
+      <c r="H79">
+        <v>60.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K79">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L79">
+        <v>7.01</v>
+      </c>
+      <c r="M79">
+        <v>10.0257234</v>
+      </c>
+      <c r="N79">
+        <v>-3.015723400000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.4523585100000002</v>
+      </c>
+      <c r="P79">
+        <v>-2.56336489</v>
+      </c>
+      <c r="Q79">
+        <v>-0.533364890000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7862574474839887</v>
+      </c>
+      <c r="T79">
+        <v>3.963905373789133</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.1048802124343466</v>
+      </c>
+      <c r="W79">
+        <v>0.1913766105815367</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.6992014162289775</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3299492030691007</v>
+      </c>
+      <c r="C80">
+        <v>-3.94823987008342</v>
+      </c>
+      <c r="D80">
+        <v>31.15376012991658</v>
+      </c>
+      <c r="E80">
+        <v>47.502</v>
+      </c>
+      <c r="F80">
+        <v>47.502</v>
+      </c>
+      <c r="G80">
+        <v>12.4</v>
+      </c>
+      <c r="H80">
+        <v>60.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K80">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L80">
+        <v>7.01</v>
+      </c>
+      <c r="M80">
+        <v>10.1559276</v>
+      </c>
+      <c r="N80">
+        <v>-3.1459276</v>
+      </c>
+      <c r="O80">
+        <v>-0.4718891400000001</v>
+      </c>
+      <c r="P80">
+        <v>-2.67403846</v>
+      </c>
+      <c r="Q80">
+        <v>-0.6440384600000009</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.8202327860059884</v>
+      </c>
+      <c r="T80">
+        <v>4.144082890779549</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.103535594326214</v>
+      </c>
+      <c r="W80">
+        <v>0.1916640899330554</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.6902372955080932</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3316992030691007</v>
+      </c>
+      <c r="C81">
+        <v>-4.743375850161506</v>
+      </c>
+      <c r="D81">
+        <v>30.9676241498385</v>
+      </c>
+      <c r="E81">
+        <v>48.111</v>
+      </c>
+      <c r="F81">
+        <v>48.111</v>
+      </c>
+      <c r="G81">
+        <v>12.4</v>
+      </c>
+      <c r="H81">
+        <v>60.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K81">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L81">
+        <v>7.01</v>
+      </c>
+      <c r="M81">
+        <v>10.2861318</v>
+      </c>
+      <c r="N81">
+        <v>-3.2761318</v>
+      </c>
+      <c r="O81">
+        <v>-0.4914197700000001</v>
+      </c>
+      <c r="P81">
+        <v>-2.78471203</v>
+      </c>
+      <c r="Q81">
+        <v>-0.7547120300000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.8574438710538927</v>
+      </c>
+      <c r="T81">
+        <v>4.341420171292861</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.1022250171828442</v>
+      </c>
+      <c r="W81">
+        <v>0.1919442913263079</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.6815001145522945</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3334492030691006</v>
+      </c>
+      <c r="C82">
+        <v>-5.536300808035911</v>
+      </c>
+      <c r="D82">
+        <v>30.78369919196409</v>
+      </c>
+      <c r="E82">
+        <v>48.72</v>
+      </c>
+      <c r="F82">
+        <v>48.72</v>
+      </c>
+      <c r="G82">
+        <v>12.4</v>
+      </c>
+      <c r="H82">
+        <v>60.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K82">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L82">
+        <v>7.01</v>
+      </c>
+      <c r="M82">
+        <v>10.416336</v>
+      </c>
+      <c r="N82">
+        <v>-3.406336</v>
+      </c>
+      <c r="O82">
+        <v>-0.5109504</v>
+      </c>
+      <c r="P82">
+        <v>-2.8953856</v>
+      </c>
+      <c r="Q82">
+        <v>-0.8653856000000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.8983760646065873</v>
+      </c>
+      <c r="T82">
+        <v>4.558491179857504</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.1009472044680586</v>
+      </c>
+      <c r="W82">
+        <v>0.1922174876847291</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.6729813631203909</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3351992030691006</v>
+      </c>
+      <c r="C83">
+        <v>-6.327053906654662</v>
+      </c>
+      <c r="D83">
+        <v>30.60194609334534</v>
+      </c>
+      <c r="E83">
+        <v>49.329</v>
+      </c>
+      <c r="F83">
+        <v>49.329</v>
+      </c>
+      <c r="G83">
+        <v>12.4</v>
+      </c>
+      <c r="H83">
+        <v>60.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K83">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L83">
+        <v>7.01</v>
+      </c>
+      <c r="M83">
+        <v>10.5465402</v>
+      </c>
+      <c r="N83">
+        <v>-3.536540199999999</v>
+      </c>
+      <c r="O83">
+        <v>-0.53048103</v>
+      </c>
+      <c r="P83">
+        <v>-3.006059169999999</v>
+      </c>
+      <c r="Q83">
+        <v>-0.9760591700000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.9436169101121969</v>
+      </c>
+      <c r="T83">
+        <v>4.798411768271056</v>
+      </c>
+      <c r="U83">
+        <v>0.2138</v>
+      </c>
+      <c r="V83">
+        <v>0.09970094268450237</v>
+      </c>
+      <c r="W83">
+        <v>0.1924839384540534</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.6646729512300158</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3369492030691006</v>
+      </c>
+      <c r="C84">
+        <v>-7.115673389491057</v>
+      </c>
+      <c r="D84">
+        <v>30.42232661050894</v>
+      </c>
+      <c r="E84">
+        <v>49.938</v>
+      </c>
+      <c r="F84">
+        <v>49.938</v>
+      </c>
+      <c r="G84">
+        <v>12.4</v>
+      </c>
+      <c r="H84">
+        <v>60.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K84">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L84">
+        <v>7.01</v>
+      </c>
+      <c r="M84">
+        <v>10.6767444</v>
+      </c>
+      <c r="N84">
+        <v>-3.666744400000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.5500116600000002</v>
+      </c>
+      <c r="P84">
+        <v>-3.116732740000001</v>
+      </c>
+      <c r="Q84">
+        <v>-1.086732740000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.9938845162295413</v>
+      </c>
+      <c r="T84">
+        <v>5.064990199841671</v>
+      </c>
+      <c r="U84">
+        <v>0.2138</v>
+      </c>
+      <c r="V84">
+        <v>0.09848507752981331</v>
+      </c>
+      <c r="W84">
+        <v>0.1927438904241259</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.6565671835320886</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3386992030691007</v>
+      </c>
+      <c r="C85">
+        <v>-7.902196607370783</v>
+      </c>
+      <c r="D85">
+        <v>30.24480339262922</v>
+      </c>
+      <c r="E85">
+        <v>50.547</v>
+      </c>
+      <c r="F85">
+        <v>50.547</v>
+      </c>
+      <c r="G85">
+        <v>12.4</v>
+      </c>
+      <c r="H85">
+        <v>60.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K85">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L85">
+        <v>7.01</v>
+      </c>
+      <c r="M85">
+        <v>10.8069486</v>
+      </c>
+      <c r="N85">
+        <v>-3.7969486</v>
+      </c>
+      <c r="O85">
+        <v>-0.5695422900000001</v>
+      </c>
+      <c r="P85">
+        <v>-3.22740631</v>
+      </c>
+      <c r="Q85">
+        <v>-1.197406310000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.050065958360691</v>
+      </c>
+      <c r="T85">
+        <v>5.362930799832359</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.09729851033065894</v>
+      </c>
+      <c r="W85">
+        <v>0.1929975784913051</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.6486567355377262</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3404492030691006</v>
+      </c>
+      <c r="C86">
+        <v>-8.686660044365091</v>
+      </c>
+      <c r="D86">
+        <v>30.06933995563491</v>
+      </c>
+      <c r="E86">
+        <v>51.156</v>
+      </c>
+      <c r="F86">
+        <v>51.156</v>
+      </c>
+      <c r="G86">
+        <v>12.4</v>
+      </c>
+      <c r="H86">
+        <v>60.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K86">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L86">
+        <v>7.01</v>
+      </c>
+      <c r="M86">
+        <v>10.9371528</v>
+      </c>
+      <c r="N86">
+        <v>-3.9271528</v>
+      </c>
+      <c r="O86">
+        <v>-0.5890729200000001</v>
+      </c>
+      <c r="P86">
+        <v>-3.33807988</v>
+      </c>
+      <c r="Q86">
+        <v>-1.308079880000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.113270080758234</v>
+      </c>
+      <c r="T86">
+        <v>5.698113974821879</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.09614019473148443</v>
+      </c>
+      <c r="W86">
+        <v>0.1932452263664086</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.6409346315432294</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3421992030691007</v>
+      </c>
+      <c r="C87">
+        <v>-9.469099342787963</v>
+      </c>
+      <c r="D87">
+        <v>29.89590065721204</v>
+      </c>
+      <c r="E87">
+        <v>51.765</v>
+      </c>
+      <c r="F87">
+        <v>51.765</v>
+      </c>
+      <c r="G87">
+        <v>12.4</v>
+      </c>
+      <c r="H87">
+        <v>60.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K87">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L87">
+        <v>7.01</v>
+      </c>
+      <c r="M87">
+        <v>11.067357</v>
+      </c>
+      <c r="N87">
+        <v>-4.057357</v>
+      </c>
+      <c r="O87">
+        <v>-0.60860355</v>
+      </c>
+      <c r="P87">
+        <v>-3.44875345</v>
+      </c>
+      <c r="Q87">
+        <v>-1.418753450000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.184901419475449</v>
+      </c>
+      <c r="T87">
+        <v>6.077988239810003</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.09500913361699637</v>
+      </c>
+      <c r="W87">
+        <v>0.1934870472326862</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.633394224113309</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3439492030691007</v>
+      </c>
+      <c r="C88">
+        <v>-10.24954932733297</v>
+      </c>
+      <c r="D88">
+        <v>29.72445067266702</v>
+      </c>
+      <c r="E88">
+        <v>52.374</v>
+      </c>
+      <c r="F88">
+        <v>52.374</v>
+      </c>
+      <c r="G88">
+        <v>12.4</v>
+      </c>
+      <c r="H88">
+        <v>60.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K88">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L88">
+        <v>7.01</v>
+      </c>
+      <c r="M88">
+        <v>11.1975612</v>
+      </c>
+      <c r="N88">
+        <v>-4.187561199999999</v>
+      </c>
+      <c r="O88">
+        <v>-0.62813418</v>
+      </c>
+      <c r="P88">
+        <v>-3.559427019999999</v>
+      </c>
+      <c r="Q88">
+        <v>-1.52942702</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.266765806580838</v>
+      </c>
+      <c r="T88">
+        <v>6.512130256939289</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.09390437624935689</v>
+      </c>
+      <c r="W88">
+        <v>0.1937232443578875</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.6260291749957125</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3456992030691006</v>
+      </c>
+      <c r="C89">
+        <v>-11.02804402838456</v>
+      </c>
+      <c r="D89">
+        <v>29.55495597161544</v>
+      </c>
+      <c r="E89">
+        <v>52.983</v>
+      </c>
+      <c r="F89">
+        <v>52.983</v>
+      </c>
+      <c r="G89">
+        <v>12.4</v>
+      </c>
+      <c r="H89">
+        <v>60.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K89">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L89">
+        <v>7.01</v>
+      </c>
+      <c r="M89">
+        <v>11.3277654</v>
+      </c>
+      <c r="N89">
+        <v>-4.317765399999999</v>
+      </c>
+      <c r="O89">
+        <v>-0.64766481</v>
+      </c>
+      <c r="P89">
+        <v>-3.670100589999999</v>
+      </c>
+      <c r="Q89">
+        <v>-1.640100589999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.361224714779364</v>
+      </c>
+      <c r="T89">
+        <v>7.013063353626927</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.09282501560281256</v>
+      </c>
+      <c r="W89">
+        <v>0.1939540116641187</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.6188334373520836</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3474492030691007</v>
+      </c>
+      <c r="C90">
+        <v>-11.80461670453609</v>
+      </c>
+      <c r="D90">
+        <v>29.3873832954639</v>
+      </c>
+      <c r="E90">
+        <v>53.592</v>
+      </c>
+      <c r="F90">
+        <v>53.592</v>
+      </c>
+      <c r="G90">
+        <v>12.4</v>
+      </c>
+      <c r="H90">
+        <v>60.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K90">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L90">
+        <v>7.01</v>
+      </c>
+      <c r="M90">
+        <v>11.4579696</v>
+      </c>
+      <c r="N90">
+        <v>-4.447969599999999</v>
+      </c>
+      <c r="O90">
+        <v>-0.6671954399999999</v>
+      </c>
+      <c r="P90">
+        <v>-3.780774159999999</v>
+      </c>
+      <c r="Q90">
+        <v>-1.750774159999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.471426774344312</v>
+      </c>
+      <c r="T90">
+        <v>7.597485299762504</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.09177018588005333</v>
+      </c>
+      <c r="W90">
+        <v>0.1941795342588446</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.6118012392003555</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3491992030691006</v>
+      </c>
+      <c r="C91">
+        <v>-12.57929986434631</v>
+      </c>
+      <c r="D91">
+        <v>29.22170013565369</v>
+      </c>
+      <c r="E91">
+        <v>54.201</v>
+      </c>
+      <c r="F91">
+        <v>54.201</v>
+      </c>
+      <c r="G91">
+        <v>12.4</v>
+      </c>
+      <c r="H91">
+        <v>60.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K91">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L91">
+        <v>7.01</v>
+      </c>
+      <c r="M91">
+        <v>11.5881738</v>
+      </c>
+      <c r="N91">
+        <v>-4.5781738</v>
+      </c>
+      <c r="O91">
+        <v>-0.6867260700000001</v>
+      </c>
+      <c r="P91">
+        <v>-3.89144773</v>
+      </c>
+      <c r="Q91">
+        <v>-1.861447730000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.601665572011977</v>
+      </c>
+      <c r="T91">
+        <v>8.288165781559098</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.09073906019600776</v>
+      </c>
+      <c r="W91">
+        <v>0.1943999889300935</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.6049270679733851</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3509492030691007</v>
+      </c>
+      <c r="C92">
+        <v>-13.35212528736389</v>
+      </c>
+      <c r="D92">
+        <v>29.05787471263611</v>
+      </c>
+      <c r="E92">
+        <v>54.81</v>
+      </c>
+      <c r="F92">
+        <v>54.81</v>
+      </c>
+      <c r="G92">
+        <v>12.4</v>
+      </c>
+      <c r="H92">
+        <v>60.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K92">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L92">
+        <v>7.01</v>
+      </c>
+      <c r="M92">
+        <v>11.718378</v>
+      </c>
+      <c r="N92">
+        <v>-4.708378</v>
+      </c>
+      <c r="O92">
+        <v>-0.7062567000000001</v>
+      </c>
+      <c r="P92">
+        <v>-4.0021213</v>
+      </c>
+      <c r="Q92">
+        <v>-1.9721213</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.757952129213175</v>
+      </c>
+      <c r="T92">
+        <v>9.116982359715008</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.08973084841605214</v>
+      </c>
+      <c r="W92">
+        <v>0.1946155446086481</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5982056561070141</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3526992030691007</v>
+      </c>
+      <c r="C93">
+        <v>-14.12312404444872</v>
+      </c>
+      <c r="D93">
+        <v>28.89587595555128</v>
+      </c>
+      <c r="E93">
+        <v>55.419</v>
+      </c>
+      <c r="F93">
+        <v>55.419</v>
+      </c>
+      <c r="G93">
+        <v>12.4</v>
+      </c>
+      <c r="H93">
+        <v>60.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K93">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L93">
+        <v>7.01</v>
+      </c>
+      <c r="M93">
+        <v>11.8485822</v>
+      </c>
+      <c r="N93">
+        <v>-4.838582200000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.7257873300000003</v>
+      </c>
+      <c r="P93">
+        <v>-4.112794870000001</v>
+      </c>
+      <c r="Q93">
+        <v>-2.082794870000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.948969032459083</v>
+      </c>
+      <c r="T93">
+        <v>10.12998039968334</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.08874479513675484</v>
+      </c>
+      <c r="W93">
+        <v>0.1948263627997618</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.5916319675783656</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3544492030691007</v>
+      </c>
+      <c r="C94">
+        <v>-14.89232651741725</v>
+      </c>
+      <c r="D94">
+        <v>28.73567348258275</v>
+      </c>
+      <c r="E94">
+        <v>56.028</v>
+      </c>
+      <c r="F94">
+        <v>56.028</v>
+      </c>
+      <c r="G94">
+        <v>12.4</v>
+      </c>
+      <c r="H94">
+        <v>60.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K94">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L94">
+        <v>7.01</v>
+      </c>
+      <c r="M94">
+        <v>11.9787864</v>
+      </c>
+      <c r="N94">
+        <v>-4.968786399999999</v>
+      </c>
+      <c r="O94">
+        <v>-0.7453179599999999</v>
+      </c>
+      <c r="P94">
+        <v>-4.22346844</v>
+      </c>
+      <c r="Q94">
+        <v>-2.19346844</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.187740161516469</v>
+      </c>
+      <c r="T94">
+        <v>11.39622794964376</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.08778017779831188</v>
+      </c>
+      <c r="W94">
+        <v>0.1950325979867209</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5852011853220791</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3561992030691007</v>
+      </c>
+      <c r="C95">
+        <v>-15.65976241803786</v>
+      </c>
+      <c r="D95">
+        <v>28.57723758196213</v>
+      </c>
+      <c r="E95">
+        <v>56.637</v>
+      </c>
+      <c r="F95">
+        <v>56.637</v>
+      </c>
+      <c r="G95">
+        <v>12.4</v>
+      </c>
+      <c r="H95">
+        <v>60.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K95">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L95">
+        <v>7.01</v>
+      </c>
+      <c r="M95">
+        <v>12.1089906</v>
+      </c>
+      <c r="N95">
+        <v>-5.0989906</v>
+      </c>
+      <c r="O95">
+        <v>-0.7648485900000002</v>
+      </c>
+      <c r="P95">
+        <v>-4.334142010000001</v>
+      </c>
+      <c r="Q95">
+        <v>-2.304142010000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.494731613161679</v>
+      </c>
+      <c r="T95">
+        <v>13.02426051387859</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.08683630491876013</v>
+      </c>
+      <c r="W95">
+        <v>0.1952343980083691</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5789086994584007</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3579492030691007</v>
+      </c>
+      <c r="C96">
+        <v>-16.4254608064014</v>
+      </c>
+      <c r="D96">
+        <v>28.42053919359861</v>
+      </c>
+      <c r="E96">
+        <v>57.246</v>
+      </c>
+      <c r="F96">
+        <v>57.246</v>
+      </c>
+      <c r="G96">
+        <v>12.4</v>
+      </c>
+      <c r="H96">
+        <v>60.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K96">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L96">
+        <v>7.01</v>
+      </c>
+      <c r="M96">
+        <v>12.2391948</v>
+      </c>
+      <c r="N96">
+        <v>-5.2291948</v>
+      </c>
+      <c r="O96">
+        <v>-0.7843792200000002</v>
+      </c>
+      <c r="P96">
+        <v>-4.44481558</v>
+      </c>
+      <c r="Q96">
+        <v>-2.414815580000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.904053548688626</v>
+      </c>
+      <c r="T96">
+        <v>15.19497059952502</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.08591251444090096</v>
+      </c>
+      <c r="W96">
+        <v>0.1954319044125354</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.572750096272673</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3596992030691007</v>
+      </c>
+      <c r="C97">
+        <v>-17.18945010869047</v>
+      </c>
+      <c r="D97">
+        <v>28.26554989130954</v>
+      </c>
+      <c r="E97">
+        <v>57.855</v>
+      </c>
+      <c r="F97">
+        <v>57.855</v>
+      </c>
+      <c r="G97">
+        <v>12.4</v>
+      </c>
+      <c r="H97">
+        <v>60.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K97">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L97">
+        <v>7.01</v>
+      </c>
+      <c r="M97">
+        <v>12.369399</v>
+      </c>
+      <c r="N97">
+        <v>-5.359399</v>
+      </c>
+      <c r="O97">
+        <v>-0.80390985</v>
+      </c>
+      <c r="P97">
+        <v>-4.55548915</v>
+      </c>
+      <c r="Q97">
+        <v>-2.52548915</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.477104258426353</v>
+      </c>
+      <c r="T97">
+        <v>18.23396471943004</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.08500817218362834</v>
+      </c>
+      <c r="W97">
+        <v>0.1956252527871402</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.5667211478908555</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3614492030691007</v>
+      </c>
+      <c r="C98">
+        <v>-17.95175813437059</v>
+      </c>
+      <c r="D98">
+        <v>28.1122418656294</v>
+      </c>
+      <c r="E98">
+        <v>58.464</v>
+      </c>
+      <c r="F98">
+        <v>58.464</v>
+      </c>
+      <c r="G98">
+        <v>12.4</v>
+      </c>
+      <c r="H98">
+        <v>60.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K98">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L98">
+        <v>7.01</v>
+      </c>
+      <c r="M98">
+        <v>12.4996032</v>
+      </c>
+      <c r="N98">
+        <v>-5.489603199999999</v>
+      </c>
+      <c r="O98">
+        <v>-0.82344048</v>
+      </c>
+      <c r="P98">
+        <v>-4.666162719999999</v>
+      </c>
+      <c r="Q98">
+        <v>-2.63616272</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>4.336680323032932</v>
+      </c>
+      <c r="T98">
+        <v>22.7924558992875</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.08412267039004888</v>
+      </c>
+      <c r="W98">
+        <v>0.1958145730706075</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.5608178026003258</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3631992030691007</v>
+      </c>
+      <c r="C99">
+        <v>-18.7124120928249</v>
+      </c>
+      <c r="D99">
+        <v>27.9605879071751</v>
+      </c>
+      <c r="E99">
+        <v>59.073</v>
+      </c>
+      <c r="F99">
+        <v>59.073</v>
+      </c>
+      <c r="G99">
+        <v>12.4</v>
+      </c>
+      <c r="H99">
+        <v>60.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K99">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L99">
+        <v>7.01</v>
+      </c>
+      <c r="M99">
+        <v>12.6298074</v>
+      </c>
+      <c r="N99">
+        <v>-5.619807399999999</v>
+      </c>
+      <c r="O99">
+        <v>-0.84297111</v>
+      </c>
+      <c r="P99">
+        <v>-4.776836289999999</v>
+      </c>
+      <c r="Q99">
+        <v>-2.74683629</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.769307097377243</v>
+      </c>
+      <c r="T99">
+        <v>30.38994119905</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.0832554263654092</v>
+      </c>
+      <c r="W99">
+        <v>0.1959999898430755</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5550361757693946</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3649492030691007</v>
+      </c>
+      <c r="C100">
+        <v>-19.47143860945322</v>
+      </c>
+      <c r="D100">
+        <v>27.81056139054678</v>
+      </c>
+      <c r="E100">
+        <v>59.682</v>
+      </c>
+      <c r="F100">
+        <v>59.682</v>
+      </c>
+      <c r="G100">
+        <v>12.4</v>
+      </c>
+      <c r="H100">
+        <v>60.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K100">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L100">
+        <v>7.01</v>
+      </c>
+      <c r="M100">
+        <v>12.7600116</v>
+      </c>
+      <c r="N100">
+        <v>-5.750011599999999</v>
+      </c>
+      <c r="O100">
+        <v>-0.8625017399999999</v>
+      </c>
+      <c r="P100">
+        <v>-4.887509859999999</v>
+      </c>
+      <c r="Q100">
+        <v>-2.85750986</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>8.634560646065864</v>
+      </c>
+      <c r="T100">
+        <v>45.58491179857499</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.08240588119841523</v>
+      </c>
+      <c r="W100">
+        <v>0.1961816225997788</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.5493725413227681</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3666992030691006</v>
+      </c>
+      <c r="C101">
+        <v>-20.22886374125568</v>
+      </c>
+      <c r="D101">
+        <v>27.66213625874432</v>
+      </c>
+      <c r="E101">
+        <v>60.291</v>
+      </c>
+      <c r="F101">
+        <v>60.291</v>
+      </c>
+      <c r="G101">
+        <v>12.4</v>
+      </c>
+      <c r="H101">
+        <v>60.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K101">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="L101">
+        <v>7.01</v>
+      </c>
+      <c r="M101">
+        <v>12.8902158</v>
+      </c>
+      <c r="N101">
+        <v>-5.880215799999998</v>
+      </c>
+      <c r="O101">
+        <v>-0.8820323699999999</v>
+      </c>
+      <c r="P101">
+        <v>-4.998183429999998</v>
+      </c>
+      <c r="Q101">
+        <v>-2.968183429999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>17.23032129213173</v>
+      </c>
+      <c r="T101">
+        <v>91.16982359714999</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.08157349856004741</v>
+      </c>
+      <c r="W101">
+        <v>0.1963595860078619</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.5438233237336493</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_chemical_basic.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1938423591495942</v>
+        <v>0.1935898456108698</v>
       </c>
       <c r="C2">
-        <v>65.3</v>
+        <v>64.73806831094097</v>
       </c>
       <c r="D2">
-        <v>53.3</v>
+        <v>53.39106831094098</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -1576,28 +1576,28 @@
         <v>2.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0328459</v>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>2.1671541</v>
       </c>
       <c r="O2">
-        <v>0.33</v>
+        <v>0.325073115</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.842080985</v>
       </c>
       <c r="Q2">
-        <v>3.8</v>
+        <v>3.772080985</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1938423591495942</v>
+        <v>0.1951134299099695</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9131823500886525</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>66.97944035633064</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1935898456108698</v>
+        <v>0.1933373320721454</v>
       </c>
       <c r="C3">
-        <v>64.73806831094097</v>
+        <v>64.17644835290135</v>
       </c>
       <c r="D3">
-        <v>53.39106831094098</v>
+        <v>53.48244835290134</v>
       </c>
       <c r="E3">
-        <v>0.653</v>
+        <v>1.306</v>
       </c>
       <c r="F3">
-        <v>0.653</v>
+        <v>1.306</v>
       </c>
       <c r="G3">
         <v>12</v>
@@ -1658,28 +1658,28 @@
         <v>2.2</v>
       </c>
       <c r="M3">
-        <v>0.0328459</v>
+        <v>0.06569179999999999</v>
       </c>
       <c r="N3">
-        <v>2.1671541</v>
+        <v>2.1343082</v>
       </c>
       <c r="O3">
-        <v>0.325073115</v>
+        <v>0.32014623</v>
       </c>
       <c r="P3">
-        <v>1.842080985</v>
+        <v>1.81416197</v>
       </c>
       <c r="Q3">
-        <v>3.772080985</v>
+        <v>3.74416197</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1951134299099695</v>
+        <v>0.1964104408899443</v>
       </c>
       <c r="T3">
-        <v>0.9131823500886525</v>
+        <v>0.921114707784128</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>66.97944035633064</v>
+        <v>33.48972017816531</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1933373320721454</v>
+        <v>0.193084818533421</v>
       </c>
       <c r="C4">
-        <v>64.17644835290135</v>
+        <v>63.61514172922966</v>
       </c>
       <c r="D4">
-        <v>53.48244835290134</v>
+        <v>53.57414172922967</v>
       </c>
       <c r="E4">
-        <v>1.306</v>
+        <v>1.959</v>
       </c>
       <c r="F4">
-        <v>1.306</v>
+        <v>1.959</v>
       </c>
       <c r="G4">
         <v>12</v>
@@ -1740,28 +1740,28 @@
         <v>2.2</v>
       </c>
       <c r="M4">
-        <v>0.06569179999999999</v>
+        <v>0.09853769999999999</v>
       </c>
       <c r="N4">
-        <v>2.1343082</v>
+        <v>2.1014623</v>
       </c>
       <c r="O4">
-        <v>0.32014623</v>
+        <v>0.315219345</v>
       </c>
       <c r="P4">
-        <v>1.81416197</v>
+        <v>1.786242955</v>
       </c>
       <c r="Q4">
-        <v>3.74416197</v>
+        <v>3.716242955</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1964104408899443</v>
+        <v>0.1977341943643516</v>
       </c>
       <c r="T4">
-        <v>0.921114707784128</v>
+        <v>0.9292106192465203</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.48972017816531</v>
+        <v>22.32648011877688</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.193084818533421</v>
+        <v>0.1928323049946966</v>
       </c>
       <c r="C5">
-        <v>63.61514172922966</v>
+        <v>63.05415005428896</v>
       </c>
       <c r="D5">
-        <v>53.57414172922967</v>
+        <v>53.66615005428896</v>
       </c>
       <c r="E5">
-        <v>1.959</v>
+        <v>2.612</v>
       </c>
       <c r="F5">
-        <v>1.959</v>
+        <v>2.612</v>
       </c>
       <c r="G5">
         <v>12</v>
@@ -1822,28 +1822,28 @@
         <v>2.2</v>
       </c>
       <c r="M5">
-        <v>0.09853769999999999</v>
+        <v>0.1313836</v>
       </c>
       <c r="N5">
-        <v>2.1014623</v>
+        <v>2.0686164</v>
       </c>
       <c r="O5">
-        <v>0.315219345</v>
+        <v>0.31029246</v>
       </c>
       <c r="P5">
-        <v>1.786242955</v>
+        <v>1.75832394</v>
       </c>
       <c r="Q5">
-        <v>3.716242955</v>
+        <v>3.68832394</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1977341943643516</v>
+        <v>0.1990855260361424</v>
       </c>
       <c r="T5">
-        <v>0.9292106192465203</v>
+        <v>0.937475195531046</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.32648011877688</v>
+        <v>16.74486008908266</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1928323049946966</v>
+        <v>0.1925797914559723</v>
       </c>
       <c r="C6">
-        <v>63.05415005428896</v>
+        <v>62.49347495355131</v>
       </c>
       <c r="D6">
-        <v>53.66615005428896</v>
+        <v>53.75847495355132</v>
       </c>
       <c r="E6">
-        <v>2.612</v>
+        <v>3.265</v>
       </c>
       <c r="F6">
-        <v>2.612</v>
+        <v>3.265</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -1904,28 +1904,28 @@
         <v>2.2</v>
       </c>
       <c r="M6">
-        <v>0.1313836</v>
+        <v>0.1642295</v>
       </c>
       <c r="N6">
-        <v>2.0686164</v>
+        <v>2.0357705</v>
       </c>
       <c r="O6">
-        <v>0.31029246</v>
+        <v>0.3053655750000001</v>
       </c>
       <c r="P6">
-        <v>1.75832394</v>
+        <v>1.730404925</v>
       </c>
       <c r="Q6">
-        <v>3.68832394</v>
+        <v>3.660404925</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1990855260361424</v>
+        <v>0.2004653067957603</v>
       </c>
       <c r="T6">
-        <v>0.937475195531046</v>
+        <v>0.9459137628952458</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.74486008908266</v>
+        <v>13.39588807126613</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1925797914559723</v>
+        <v>0.1924037779172479</v>
       </c>
       <c r="C7">
-        <v>62.49347495355131</v>
+        <v>61.90501776102483</v>
       </c>
       <c r="D7">
-        <v>53.75847495355132</v>
+        <v>53.82301776102483</v>
       </c>
       <c r="E7">
-        <v>3.265</v>
+        <v>3.918</v>
       </c>
       <c r="F7">
-        <v>3.265</v>
+        <v>3.918</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -1986,45 +1986,45 @@
         <v>2.2</v>
       </c>
       <c r="M7">
-        <v>0.1642295</v>
+        <v>0.2029524</v>
       </c>
       <c r="N7">
-        <v>2.0357705</v>
+        <v>1.9970476</v>
       </c>
       <c r="O7">
-        <v>0.3053655750000001</v>
+        <v>0.29955714</v>
       </c>
       <c r="P7">
-        <v>1.730404925</v>
+        <v>1.69749046</v>
       </c>
       <c r="Q7">
-        <v>3.660404925</v>
+        <v>3.62749046</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2004653067957603</v>
+        <v>0.2018744445928169</v>
       </c>
       <c r="T7">
-        <v>0.9459137628952458</v>
+        <v>0.9545318742459179</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.15</v>
       </c>
       <c r="W7">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.39588807126613</v>
+        <v>10.83998021210885</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1924037779172479</v>
+        <v>0.1922651643785235</v>
       </c>
       <c r="C8">
-        <v>61.90501776102483</v>
+        <v>61.30295546343575</v>
       </c>
       <c r="D8">
-        <v>53.82301776102483</v>
+        <v>53.87395546343576</v>
       </c>
       <c r="E8">
-        <v>3.918</v>
+        <v>4.571</v>
       </c>
       <c r="F8">
-        <v>3.918</v>
+        <v>4.571</v>
       </c>
       <c r="G8">
         <v>12</v>
@@ -2068,45 +2068,45 @@
         <v>2.2</v>
       </c>
       <c r="M8">
-        <v>0.2029524</v>
+        <v>0.2445485</v>
       </c>
       <c r="N8">
-        <v>1.9970476</v>
+        <v>1.9554515</v>
       </c>
       <c r="O8">
-        <v>0.29955714</v>
+        <v>0.293317725</v>
       </c>
       <c r="P8">
-        <v>1.69749046</v>
+        <v>1.662133775</v>
       </c>
       <c r="Q8">
-        <v>3.62749046</v>
+        <v>3.592133775</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2018744445928169</v>
+        <v>0.2033138864285199</v>
       </c>
       <c r="T8">
-        <v>0.9545318742459179</v>
+        <v>0.9633353213245615</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.15</v>
       </c>
       <c r="W8">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.83998021210885</v>
+        <v>8.996170493787531</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1922651643785235</v>
+        <v>0.1920398508397991</v>
       </c>
       <c r="C9">
-        <v>61.30295546343575</v>
+        <v>60.73295972992564</v>
       </c>
       <c r="D9">
-        <v>53.87395546343576</v>
+        <v>53.95695972992564</v>
       </c>
       <c r="E9">
-        <v>4.571000000000001</v>
+        <v>5.224</v>
       </c>
       <c r="F9">
-        <v>4.571000000000001</v>
+        <v>5.224</v>
       </c>
       <c r="G9">
         <v>12</v>
@@ -2150,28 +2150,28 @@
         <v>2.2</v>
       </c>
       <c r="M9">
-        <v>0.2445485</v>
+        <v>0.279484</v>
       </c>
       <c r="N9">
-        <v>1.9554515</v>
+        <v>1.920516</v>
       </c>
       <c r="O9">
-        <v>0.293317725</v>
+        <v>0.2880774</v>
       </c>
       <c r="P9">
-        <v>1.662133775</v>
+        <v>1.6324386</v>
       </c>
       <c r="Q9">
-        <v>3.592133775</v>
+        <v>3.5624386</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2033138864285199</v>
+        <v>0.2047846204780425</v>
       </c>
       <c r="T9">
-        <v>0.9633353213245615</v>
+        <v>0.9723301476875235</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.996170493787531</v>
+        <v>7.87164918206409</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1920398508397991</v>
+        <v>0.1918757373010747</v>
       </c>
       <c r="C10">
-        <v>60.73295972992564</v>
+        <v>60.14057943148385</v>
       </c>
       <c r="D10">
-        <v>53.95695972992564</v>
+        <v>54.01757943148385</v>
       </c>
       <c r="E10">
-        <v>5.224</v>
+        <v>5.877</v>
       </c>
       <c r="F10">
-        <v>5.224</v>
+        <v>5.877</v>
       </c>
       <c r="G10">
         <v>12</v>
@@ -2232,45 +2232,45 @@
         <v>2.2</v>
       </c>
       <c r="M10">
-        <v>0.279484</v>
+        <v>0.3191211</v>
       </c>
       <c r="N10">
-        <v>1.920516</v>
+        <v>1.8808789</v>
       </c>
       <c r="O10">
-        <v>0.2880774</v>
+        <v>0.282131835</v>
       </c>
       <c r="P10">
-        <v>1.6324386</v>
+        <v>1.598747065</v>
       </c>
       <c r="Q10">
-        <v>3.5624386</v>
+        <v>3.528747065</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2047846204780425</v>
+        <v>0.2062876783528293</v>
       </c>
       <c r="T10">
-        <v>0.9723301476875235</v>
+        <v>0.981522662541979</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.15</v>
       </c>
       <c r="W10">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.87164918206409</v>
+        <v>6.893934622311092</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1918757373010747</v>
+        <v>0.1916572237623503</v>
       </c>
       <c r="C11">
-        <v>60.14057943148385</v>
+        <v>59.56850495666819</v>
       </c>
       <c r="D11">
-        <v>54.01757943148385</v>
+        <v>54.09850495666819</v>
       </c>
       <c r="E11">
-        <v>5.877</v>
+        <v>6.529999999999999</v>
       </c>
       <c r="F11">
-        <v>5.877</v>
+        <v>6.529999999999999</v>
       </c>
       <c r="G11">
         <v>12</v>
@@ -2314,28 +2314,28 @@
         <v>2.2</v>
       </c>
       <c r="M11">
-        <v>0.3191211</v>
+        <v>0.354579</v>
       </c>
       <c r="N11">
-        <v>1.8808789</v>
+        <v>1.845421</v>
       </c>
       <c r="O11">
-        <v>0.282131835</v>
+        <v>0.27681315</v>
       </c>
       <c r="P11">
-        <v>1.598747065</v>
+        <v>1.56860785</v>
       </c>
       <c r="Q11">
-        <v>3.528747065</v>
+        <v>3.49860785</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2062876783528293</v>
+        <v>0.2078241375137226</v>
       </c>
       <c r="T11">
-        <v>0.981522662541979</v>
+        <v>0.9909194555043116</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>6.893934622311092</v>
+        <v>6.204541160079983</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1916572237623503</v>
+        <v>0.1915322102236259</v>
       </c>
       <c r="C12">
-        <v>59.56850495666819</v>
+        <v>58.96191230569524</v>
       </c>
       <c r="D12">
-        <v>54.09850495666819</v>
+        <v>54.14491230569525</v>
       </c>
       <c r="E12">
-        <v>6.53</v>
+        <v>7.183</v>
       </c>
       <c r="F12">
-        <v>6.53</v>
+        <v>7.183</v>
       </c>
       <c r="G12">
         <v>12</v>
@@ -2396,45 +2396,45 @@
         <v>2.2</v>
       </c>
       <c r="M12">
-        <v>0.354579</v>
+        <v>0.3972199</v>
       </c>
       <c r="N12">
-        <v>1.845421</v>
+        <v>1.8027801</v>
       </c>
       <c r="O12">
-        <v>0.27681315</v>
+        <v>0.270417015</v>
       </c>
       <c r="P12">
-        <v>1.56860785</v>
+        <v>1.532363085</v>
       </c>
       <c r="Q12">
-        <v>3.49860785</v>
+        <v>3.462363085</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2078241375137226</v>
+        <v>0.2093951238467707</v>
       </c>
       <c r="T12">
-        <v>0.9909194555043116</v>
+        <v>1.000527412353438</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.15</v>
       </c>
       <c r="W12">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.204541160079982</v>
+        <v>5.538493917349055</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1915322102236259</v>
+        <v>0.1913221966849016</v>
       </c>
       <c r="C13">
-        <v>58.96191230569524</v>
+        <v>58.38705271929733</v>
       </c>
       <c r="D13">
-        <v>54.14491230569525</v>
+        <v>54.22305271929732</v>
       </c>
       <c r="E13">
-        <v>7.183</v>
+        <v>7.835999999999999</v>
       </c>
       <c r="F13">
-        <v>7.183</v>
+        <v>7.835999999999999</v>
       </c>
       <c r="G13">
         <v>12</v>
@@ -2478,28 +2478,28 @@
         <v>2.2</v>
       </c>
       <c r="M13">
-        <v>0.3972199</v>
+        <v>0.4333308</v>
       </c>
       <c r="N13">
-        <v>1.8027801</v>
+        <v>1.7666692</v>
       </c>
       <c r="O13">
-        <v>0.270417015</v>
+        <v>0.26500038</v>
       </c>
       <c r="P13">
-        <v>1.532363085</v>
+        <v>1.50166882</v>
       </c>
       <c r="Q13">
-        <v>3.462363085</v>
+        <v>3.43166882</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2093951238467707</v>
+        <v>0.2110018144146608</v>
       </c>
       <c r="T13">
-        <v>1.000527412353438</v>
+        <v>1.010353731858226</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.538493917349055</v>
+        <v>5.076952757569968</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1913221966849016</v>
+        <v>0.1911121831461771</v>
       </c>
       <c r="C14">
-        <v>58.38705271929733</v>
+        <v>57.81241899895446</v>
       </c>
       <c r="D14">
-        <v>54.22305271929732</v>
+        <v>54.30141899895445</v>
       </c>
       <c r="E14">
-        <v>7.835999999999999</v>
+        <v>8.489000000000001</v>
       </c>
       <c r="F14">
-        <v>7.835999999999999</v>
+        <v>8.489000000000001</v>
       </c>
       <c r="G14">
         <v>12</v>
@@ -2560,28 +2560,28 @@
         <v>2.2</v>
       </c>
       <c r="M14">
-        <v>0.4333308</v>
+        <v>0.4694417000000001</v>
       </c>
       <c r="N14">
-        <v>1.7666692</v>
+        <v>1.7305583</v>
       </c>
       <c r="O14">
-        <v>0.26500038</v>
+        <v>0.259583745</v>
       </c>
       <c r="P14">
-        <v>1.50166882</v>
+        <v>1.470974555</v>
       </c>
       <c r="Q14">
-        <v>3.43166882</v>
+        <v>3.400974555</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2110018144146608</v>
+        <v>0.2126454403979048</v>
       </c>
       <c r="T14">
-        <v>1.010353731858226</v>
+        <v>1.020405943765423</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.076952757569968</v>
+        <v>4.686417930064585</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1911121831461771</v>
+        <v>0.1911996696074527</v>
       </c>
       <c r="C15">
-        <v>57.81241899895446</v>
+        <v>57.12674602931641</v>
       </c>
       <c r="D15">
-        <v>54.30141899895445</v>
+        <v>54.26874602931642</v>
       </c>
       <c r="E15">
-        <v>8.489000000000001</v>
+        <v>9.142000000000001</v>
       </c>
       <c r="F15">
-        <v>8.489000000000001</v>
+        <v>9.142000000000001</v>
       </c>
       <c r="G15">
         <v>12</v>
@@ -2642,45 +2642,45 @@
         <v>2.2</v>
       </c>
       <c r="M15">
-        <v>0.4694417000000001</v>
+        <v>0.5284076000000001</v>
       </c>
       <c r="N15">
-        <v>1.7305583</v>
+        <v>1.6715924</v>
       </c>
       <c r="O15">
-        <v>0.259583745</v>
+        <v>0.25073886</v>
       </c>
       <c r="P15">
-        <v>1.470974555</v>
+        <v>1.42085354</v>
       </c>
       <c r="Q15">
-        <v>3.400974555</v>
+        <v>3.35085354</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2126454403979048</v>
+        <v>0.2143272902412241</v>
       </c>
       <c r="T15">
-        <v>1.020405943765423</v>
+        <v>1.030691928042555</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.15</v>
       </c>
       <c r="W15">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.686417930064585</v>
+        <v>4.16345260741897</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1911996696074527</v>
+        <v>0.1914571560687283</v>
       </c>
       <c r="C16">
-        <v>57.12674602931641</v>
+        <v>56.37781207213852</v>
       </c>
       <c r="D16">
-        <v>54.26874602931642</v>
+        <v>54.17281207213852</v>
       </c>
       <c r="E16">
-        <v>9.142000000000001</v>
+        <v>9.795000000000002</v>
       </c>
       <c r="F16">
-        <v>9.142000000000001</v>
+        <v>9.795000000000002</v>
       </c>
       <c r="G16">
         <v>12</v>
@@ -2724,45 +2724,45 @@
         <v>2.2</v>
       </c>
       <c r="M16">
-        <v>0.5284076000000001</v>
+        <v>0.6004335000000001</v>
       </c>
       <c r="N16">
-        <v>1.6715924</v>
+        <v>1.5995665</v>
       </c>
       <c r="O16">
-        <v>0.25073886</v>
+        <v>0.239934975</v>
       </c>
       <c r="P16">
-        <v>1.42085354</v>
+        <v>1.359631525</v>
       </c>
       <c r="Q16">
-        <v>3.35085354</v>
+        <v>3.289631525</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2143272902412241</v>
+        <v>0.2160487130220334</v>
       </c>
       <c r="T16">
-        <v>1.030691928042555</v>
+        <v>1.04121993547915</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.16345260741897</v>
+        <v>3.664019412641033</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1914571560687283</v>
+        <v>0.191678942530004</v>
       </c>
       <c r="C17">
-        <v>56.37781207213852</v>
+        <v>55.64245065603243</v>
       </c>
       <c r="D17">
-        <v>54.17281207213852</v>
+        <v>54.09045065603243</v>
       </c>
       <c r="E17">
-        <v>9.795</v>
+        <v>10.448</v>
       </c>
       <c r="F17">
-        <v>9.795</v>
+        <v>10.448</v>
       </c>
       <c r="G17">
         <v>12</v>
@@ -2806,45 +2806,45 @@
         <v>2.2</v>
       </c>
       <c r="M17">
-        <v>0.6004335</v>
+        <v>0.6697168000000001</v>
       </c>
       <c r="N17">
-        <v>1.5995665</v>
+        <v>1.5302832</v>
       </c>
       <c r="O17">
-        <v>0.2399349750000001</v>
+        <v>0.22954248</v>
       </c>
       <c r="P17">
-        <v>1.359631525</v>
+        <v>1.30074072</v>
       </c>
       <c r="Q17">
-        <v>3.289631525</v>
+        <v>3.23074072</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2160487130220334</v>
+        <v>0.2178111220595286</v>
       </c>
       <c r="T17">
-        <v>1.04121993547915</v>
+        <v>1.051998609759472</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.664019412641034</v>
+        <v>3.284970602499444</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.191678942530004</v>
+        <v>0.1915437289912796</v>
       </c>
       <c r="C18">
-        <v>55.64245065603243</v>
+        <v>55.03963299523164</v>
       </c>
       <c r="D18">
-        <v>54.09045065603243</v>
+        <v>54.14063299523165</v>
       </c>
       <c r="E18">
-        <v>10.448</v>
+        <v>11.101</v>
       </c>
       <c r="F18">
-        <v>10.448</v>
+        <v>11.101</v>
       </c>
       <c r="G18">
         <v>12</v>
@@ -2888,28 +2888,28 @@
         <v>2.2</v>
       </c>
       <c r="M18">
-        <v>0.6697168000000001</v>
+        <v>0.7115741000000001</v>
       </c>
       <c r="N18">
-        <v>1.5302832</v>
+        <v>1.4884259</v>
       </c>
       <c r="O18">
-        <v>0.22954248</v>
+        <v>0.223263885</v>
       </c>
       <c r="P18">
-        <v>1.30074072</v>
+        <v>1.265162015</v>
       </c>
       <c r="Q18">
-        <v>3.23074072</v>
+        <v>3.195162015</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2178111220595286</v>
+        <v>0.2196159987846742</v>
       </c>
       <c r="T18">
-        <v>1.051998609759472</v>
+        <v>1.063037011130887</v>
       </c>
       <c r="U18">
         <v>0.0641</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.284970602499444</v>
+        <v>3.091737037646536</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1915437289912796</v>
+        <v>0.1926019154525552</v>
       </c>
       <c r="C19">
-        <v>55.03963299523164</v>
+        <v>53.99637320424847</v>
       </c>
       <c r="D19">
-        <v>54.14063299523165</v>
+        <v>53.75037320424848</v>
       </c>
       <c r="E19">
-        <v>11.101</v>
+        <v>11.754</v>
       </c>
       <c r="F19">
-        <v>11.101</v>
+        <v>11.754</v>
       </c>
       <c r="G19">
         <v>12</v>
@@ -2970,45 +2970,45 @@
         <v>2.2</v>
       </c>
       <c r="M19">
-        <v>0.7115741000000001</v>
+        <v>0.8451126000000002</v>
       </c>
       <c r="N19">
-        <v>1.4884259</v>
+        <v>1.3548874</v>
       </c>
       <c r="O19">
-        <v>0.223263885</v>
+        <v>0.20323311</v>
       </c>
       <c r="P19">
-        <v>1.265162015</v>
+        <v>1.15165429</v>
       </c>
       <c r="Q19">
-        <v>3.195162015</v>
+        <v>3.081654289999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2196159987846742</v>
+        <v>0.22146489689336</v>
       </c>
       <c r="T19">
-        <v>1.063037011130887</v>
+        <v>1.074344641804043</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.15</v>
       </c>
       <c r="W19">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.091737037646536</v>
+        <v>2.603203407451267</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1926019154525552</v>
+        <v>0.1931628519138308</v>
       </c>
       <c r="C20">
-        <v>53.99637320424848</v>
+        <v>53.13877249419255</v>
       </c>
       <c r="D20">
-        <v>53.75037320424848</v>
+        <v>53.54577249419255</v>
       </c>
       <c r="E20">
-        <v>11.754</v>
+        <v>12.407</v>
       </c>
       <c r="F20">
-        <v>11.754</v>
+        <v>12.407</v>
       </c>
       <c r="G20">
         <v>12</v>
@@ -3052,45 +3052,45 @@
         <v>2.2</v>
       </c>
       <c r="M20">
-        <v>0.8451126</v>
+        <v>0.9404506</v>
       </c>
       <c r="N20">
-        <v>1.3548874</v>
+        <v>1.2595494</v>
       </c>
       <c r="O20">
-        <v>0.20323311</v>
+        <v>0.18893241</v>
       </c>
       <c r="P20">
-        <v>1.15165429</v>
+        <v>1.07061699</v>
       </c>
       <c r="Q20">
-        <v>3.08165429</v>
+        <v>3.00061699</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.22146489689336</v>
+        <v>0.2233594468071985</v>
       </c>
       <c r="T20">
-        <v>1.074344641804043</v>
+        <v>1.085931473234561</v>
       </c>
       <c r="U20">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.603203407451268</v>
+        <v>2.339304159091397</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1931628519138308</v>
+        <v>0.1931270883751064</v>
       </c>
       <c r="C21">
-        <v>53.13877249419255</v>
+        <v>52.49877068976707</v>
       </c>
       <c r="D21">
-        <v>53.54577249419255</v>
+        <v>53.55877068976707</v>
       </c>
       <c r="E21">
-        <v>12.407</v>
+        <v>13.06</v>
       </c>
       <c r="F21">
-        <v>12.407</v>
+        <v>13.06</v>
       </c>
       <c r="G21">
         <v>12</v>
@@ -3134,28 +3134,28 @@
         <v>2.2</v>
       </c>
       <c r="M21">
-        <v>0.9404506</v>
+        <v>0.9899480000000002</v>
       </c>
       <c r="N21">
-        <v>1.2595494</v>
+        <v>1.210052</v>
       </c>
       <c r="O21">
-        <v>0.18893241</v>
+        <v>0.1815078</v>
       </c>
       <c r="P21">
-        <v>1.07061699</v>
+        <v>1.0285442</v>
       </c>
       <c r="Q21">
-        <v>3.00061699</v>
+        <v>2.9585442</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2233594468071985</v>
+        <v>0.225301360468883</v>
       </c>
       <c r="T21">
-        <v>1.085931473234561</v>
+        <v>1.097807975450843</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.339304159091397</v>
+        <v>2.222338951136827</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1931270883751064</v>
+        <v>0.193091324836382</v>
       </c>
       <c r="C22">
-        <v>52.49877068976707</v>
+        <v>51.85877519747803</v>
       </c>
       <c r="D22">
-        <v>53.55877068976707</v>
+        <v>53.57177519747803</v>
       </c>
       <c r="E22">
-        <v>13.06</v>
+        <v>13.713</v>
       </c>
       <c r="F22">
-        <v>13.06</v>
+        <v>13.713</v>
       </c>
       <c r="G22">
         <v>12</v>
@@ -3216,28 +3216,28 @@
         <v>2.2</v>
       </c>
       <c r="M22">
-        <v>0.9899480000000002</v>
+        <v>1.0394454</v>
       </c>
       <c r="N22">
-        <v>1.210052</v>
+        <v>1.1605546</v>
       </c>
       <c r="O22">
-        <v>0.1815078</v>
+        <v>0.17408319</v>
       </c>
       <c r="P22">
-        <v>1.0285442</v>
+        <v>0.98647141</v>
       </c>
       <c r="Q22">
-        <v>2.9585442</v>
+        <v>2.91647141</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.225301360468883</v>
+        <v>0.2272924365017494</v>
       </c>
       <c r="T22">
-        <v>1.097807975450843</v>
+        <v>1.109985148609308</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.222338951136827</v>
+        <v>2.116513286796978</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.193091324836382</v>
+        <v>0.1930555612976577</v>
       </c>
       <c r="C23">
-        <v>51.85877519747805</v>
+        <v>51.21878602192449</v>
       </c>
       <c r="D23">
-        <v>53.57177519747804</v>
+        <v>53.58478602192449</v>
       </c>
       <c r="E23">
-        <v>13.713</v>
+        <v>14.366</v>
       </c>
       <c r="F23">
-        <v>13.713</v>
+        <v>14.366</v>
       </c>
       <c r="G23">
         <v>12</v>
@@ -3298,28 +3298,28 @@
         <v>2.2</v>
       </c>
       <c r="M23">
-        <v>1.0394454</v>
+        <v>1.0889428</v>
       </c>
       <c r="N23">
-        <v>1.1605546</v>
+        <v>1.1110572</v>
       </c>
       <c r="O23">
-        <v>0.17408319</v>
+        <v>0.16665858</v>
       </c>
       <c r="P23">
-        <v>0.9864714100000002</v>
+        <v>0.9443986200000001</v>
       </c>
       <c r="Q23">
-        <v>2.91647141</v>
+        <v>2.87439862</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2272924365017494</v>
+        <v>0.2293345657662277</v>
       </c>
       <c r="T23">
-        <v>1.109985148609308</v>
+        <v>1.122474556976965</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.116513286796978</v>
+        <v>2.020308137397116</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1930555612976577</v>
+        <v>0.1957958977589332</v>
       </c>
       <c r="C24">
-        <v>51.21878602192449</v>
+        <v>49.58682362962278</v>
       </c>
       <c r="D24">
-        <v>53.58478602192449</v>
+        <v>52.60582362962278</v>
       </c>
       <c r="E24">
-        <v>14.366</v>
+        <v>15.019</v>
       </c>
       <c r="F24">
-        <v>14.366</v>
+        <v>15.019</v>
       </c>
       <c r="G24">
         <v>12</v>
@@ -3380,45 +3380,45 @@
         <v>2.2</v>
       </c>
       <c r="M24">
-        <v>1.0889428</v>
+        <v>1.35171</v>
       </c>
       <c r="N24">
-        <v>1.1110572</v>
+        <v>0.8482900000000002</v>
       </c>
       <c r="O24">
-        <v>0.16665858</v>
+        <v>0.1272435</v>
       </c>
       <c r="P24">
-        <v>0.9443986200000001</v>
+        <v>0.7210465000000001</v>
       </c>
       <c r="Q24">
-        <v>2.87439862</v>
+        <v>2.6510465</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2293345657662277</v>
+        <v>0.2314297373492639</v>
       </c>
       <c r="T24">
-        <v>1.122474556976965</v>
+        <v>1.135288365561964</v>
       </c>
       <c r="U24">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.020308137397116</v>
+        <v>1.627568043441271</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1957958977589332</v>
+        <v>0.1958808342202089</v>
       </c>
       <c r="C25">
-        <v>49.58682362962278</v>
+        <v>48.90405199006062</v>
       </c>
       <c r="D25">
-        <v>52.60582362962278</v>
+        <v>52.57605199006063</v>
       </c>
       <c r="E25">
-        <v>15.019</v>
+        <v>15.672</v>
       </c>
       <c r="F25">
-        <v>15.019</v>
+        <v>15.672</v>
       </c>
       <c r="G25">
         <v>12</v>
@@ -3462,28 +3462,28 @@
         <v>2.2</v>
       </c>
       <c r="M25">
-        <v>1.35171</v>
+        <v>1.41048</v>
       </c>
       <c r="N25">
-        <v>0.8482900000000002</v>
+        <v>0.7895200000000002</v>
       </c>
       <c r="O25">
-        <v>0.1272435</v>
+        <v>0.118428</v>
       </c>
       <c r="P25">
-        <v>0.7210465000000001</v>
+        <v>0.6710920000000002</v>
       </c>
       <c r="Q25">
-        <v>2.6510465</v>
+        <v>2.601092</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2314297373492639</v>
+        <v>0.2335800450265906</v>
       </c>
       <c r="T25">
-        <v>1.135288365561964</v>
+        <v>1.148439379636041</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.627568043441271</v>
+        <v>1.559752708297885</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1958808342202088</v>
+        <v>0.2089423933118378</v>
       </c>
       <c r="C26">
-        <v>48.90405199006065</v>
+        <v>44.04169110027586</v>
       </c>
       <c r="D26">
-        <v>52.57605199006064</v>
+        <v>48.36669110027586</v>
       </c>
       <c r="E26">
-        <v>15.672</v>
+        <v>16.325</v>
       </c>
       <c r="F26">
-        <v>15.672</v>
+        <v>16.325</v>
       </c>
       <c r="G26">
         <v>12</v>
@@ -3544,45 +3544,45 @@
         <v>2.2</v>
       </c>
       <c r="M26">
-        <v>1.41048</v>
+        <v>2.39651</v>
       </c>
       <c r="N26">
-        <v>0.7895200000000004</v>
+        <v>-0.19651</v>
       </c>
       <c r="O26">
-        <v>0.1184280000000001</v>
+        <v>-0.02947649999999999</v>
       </c>
       <c r="P26">
-        <v>0.6710920000000004</v>
+        <v>-0.1670335</v>
       </c>
       <c r="Q26">
-        <v>2.601092</v>
+        <v>1.7629665</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2335800450265906</v>
+        <v>0.2363946561156307</v>
       </c>
       <c r="T26">
-        <v>1.148439379636041</v>
+        <v>1.165653190680533</v>
       </c>
       <c r="U26">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.15</v>
+        <v>0.1377002390976879</v>
       </c>
       <c r="W26">
-        <v>0.0765</v>
+        <v>0.1265856049004594</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.559752708297885</v>
+        <v>0.9180015939845859</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2089423933118378</v>
+        <v>0.2099523933118378</v>
       </c>
       <c r="C27">
-        <v>44.04169110027586</v>
+        <v>43.0910995938366</v>
       </c>
       <c r="D27">
-        <v>48.36669110027586</v>
+        <v>48.0690995938366</v>
       </c>
       <c r="E27">
-        <v>16.325</v>
+        <v>16.978</v>
       </c>
       <c r="F27">
-        <v>16.325</v>
+        <v>16.978</v>
       </c>
       <c r="G27">
         <v>12</v>
@@ -3626,37 +3626,37 @@
         <v>2.2</v>
       </c>
       <c r="M27">
-        <v>2.39651</v>
+        <v>2.4923704</v>
       </c>
       <c r="N27">
-        <v>-0.19651</v>
+        <v>-0.2923704000000003</v>
       </c>
       <c r="O27">
-        <v>-0.02947649999999999</v>
+        <v>-0.04385556000000004</v>
       </c>
       <c r="P27">
-        <v>-0.1670335</v>
+        <v>-0.2485148400000002</v>
       </c>
       <c r="Q27">
-        <v>1.7629665</v>
+        <v>1.68148516</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2363946561156307</v>
+        <v>0.2389702595766527</v>
       </c>
       <c r="T27">
-        <v>1.165653190680533</v>
+        <v>1.181405260824865</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1377002390976879</v>
+        <v>0.1324040760554691</v>
       </c>
       <c r="W27">
-        <v>0.1265856049004594</v>
+        <v>0.1273630816350571</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.9180015939845859</v>
+        <v>0.882693840369794</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2099523933118378</v>
+        <v>0.2109623933118379</v>
       </c>
       <c r="C28">
-        <v>43.0910995938366</v>
+        <v>42.14414774671054</v>
       </c>
       <c r="D28">
-        <v>48.0690995938366</v>
+        <v>47.77514774671054</v>
       </c>
       <c r="E28">
-        <v>16.978</v>
+        <v>17.631</v>
       </c>
       <c r="F28">
-        <v>16.978</v>
+        <v>17.631</v>
       </c>
       <c r="G28">
         <v>12</v>
@@ -3708,37 +3708,37 @@
         <v>2.2</v>
       </c>
       <c r="M28">
-        <v>2.4923704</v>
+        <v>2.5882308</v>
       </c>
       <c r="N28">
-        <v>-0.2923704000000003</v>
+        <v>-0.3882308000000001</v>
       </c>
       <c r="O28">
-        <v>-0.04385556000000004</v>
+        <v>-0.05823462000000001</v>
       </c>
       <c r="P28">
-        <v>-0.2485148400000002</v>
+        <v>-0.3299961800000001</v>
       </c>
       <c r="Q28">
-        <v>1.68148516</v>
+        <v>1.60000382</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2389702595766527</v>
+        <v>0.2416164275160589</v>
       </c>
       <c r="T28">
-        <v>1.181405260824865</v>
+        <v>1.197588894534795</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.1324040760554691</v>
+        <v>0.127500221386748</v>
       </c>
       <c r="W28">
-        <v>0.1273630816350571</v>
+        <v>0.1280829675004254</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.882693840369794</v>
+        <v>0.8500014759116536</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2109623933118379</v>
+        <v>0.2119723933118378</v>
       </c>
       <c r="C29">
-        <v>42.14414774671054</v>
+        <v>41.20076919307422</v>
       </c>
       <c r="D29">
-        <v>47.77514774671054</v>
+        <v>47.48476919307423</v>
       </c>
       <c r="E29">
-        <v>17.631</v>
+        <v>18.284</v>
       </c>
       <c r="F29">
-        <v>17.631</v>
+        <v>18.284</v>
       </c>
       <c r="G29">
         <v>12</v>
@@ -3790,37 +3790,37 @@
         <v>2.2</v>
       </c>
       <c r="M29">
-        <v>2.5882308</v>
+        <v>2.684091200000001</v>
       </c>
       <c r="N29">
-        <v>-0.3882308000000001</v>
+        <v>-0.4840912000000004</v>
       </c>
       <c r="O29">
-        <v>-0.05823462000000001</v>
+        <v>-0.07261368000000006</v>
       </c>
       <c r="P29">
-        <v>-0.3299961800000001</v>
+        <v>-0.4114775200000003</v>
       </c>
       <c r="Q29">
-        <v>1.60000382</v>
+        <v>1.518522479999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2416164275160589</v>
+        <v>0.2443361001204486</v>
       </c>
       <c r="T29">
-        <v>1.197588894534795</v>
+        <v>1.214222073625556</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.127500221386748</v>
+        <v>0.122946642051507</v>
       </c>
       <c r="W29">
-        <v>0.1280829675004254</v>
+        <v>0.1287514329468388</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.8500014759116536</v>
+        <v>0.8196442803433802</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2119723933118378</v>
+        <v>0.2300129302709766</v>
       </c>
       <c r="C30">
-        <v>41.20076919307422</v>
+        <v>35.89744018325013</v>
       </c>
       <c r="D30">
-        <v>47.48476919307423</v>
+        <v>42.83444018325012</v>
       </c>
       <c r="E30">
-        <v>18.284</v>
+        <v>18.937</v>
       </c>
       <c r="F30">
-        <v>18.284</v>
+        <v>18.937</v>
       </c>
       <c r="G30">
         <v>12</v>
@@ -3872,45 +3872,45 @@
         <v>2.2</v>
       </c>
       <c r="M30">
-        <v>2.684091200000001</v>
+        <v>3.8025496</v>
       </c>
       <c r="N30">
-        <v>-0.4840912000000004</v>
+        <v>-1.6025496</v>
       </c>
       <c r="O30">
-        <v>-0.07261368000000006</v>
+        <v>-0.24038244</v>
       </c>
       <c r="P30">
-        <v>-0.4114775200000003</v>
+        <v>-1.36216716</v>
       </c>
       <c r="Q30">
-        <v>1.518522479999999</v>
+        <v>0.5678328399999997</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2443361001204486</v>
+        <v>0.2490627169660024</v>
       </c>
       <c r="T30">
-        <v>1.214222073625556</v>
+        <v>1.243129473861381</v>
       </c>
       <c r="U30">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.122946642051507</v>
+        <v>0.08678387784869394</v>
       </c>
       <c r="W30">
-        <v>0.1287514329468388</v>
+        <v>0.1833737973279823</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y30">
-        <v>0.8196442803433802</v>
+        <v>0.5785591856579596</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2300129302709766</v>
+        <v>0.2315629302709765</v>
       </c>
       <c r="C31">
-        <v>35.89744018325013</v>
+        <v>34.88703097255784</v>
       </c>
       <c r="D31">
-        <v>42.83444018325012</v>
+        <v>42.47703097255784</v>
       </c>
       <c r="E31">
-        <v>18.937</v>
+        <v>19.59</v>
       </c>
       <c r="F31">
-        <v>18.937</v>
+        <v>19.59</v>
       </c>
       <c r="G31">
         <v>12</v>
@@ -3954,37 +3954,37 @@
         <v>2.2</v>
       </c>
       <c r="M31">
-        <v>3.802549599999999</v>
+        <v>3.933672</v>
       </c>
       <c r="N31">
-        <v>-1.602549599999999</v>
+        <v>-1.733672</v>
       </c>
       <c r="O31">
-        <v>-0.2403824399999999</v>
+        <v>-0.2600508</v>
       </c>
       <c r="P31">
-        <v>-1.362167159999999</v>
+        <v>-1.4736212</v>
       </c>
       <c r="Q31">
-        <v>0.5678328400000003</v>
+        <v>0.4563787999999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2490627169660024</v>
+        <v>0.2519664700655167</v>
       </c>
       <c r="T31">
-        <v>1.243129473861381</v>
+        <v>1.260888466345115</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.08678387784869396</v>
+        <v>0.08389108192040415</v>
       </c>
       <c r="W31">
-        <v>0.1833737973279823</v>
+        <v>0.1839546707503829</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5785591856579597</v>
+        <v>0.559273879469361</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2315629302709765</v>
+        <v>0.2331129302709765</v>
       </c>
       <c r="C32">
-        <v>34.88703097255784</v>
+        <v>33.88253682897566</v>
       </c>
       <c r="D32">
-        <v>42.47703097255784</v>
+        <v>42.12553682897566</v>
       </c>
       <c r="E32">
-        <v>19.59</v>
+        <v>20.243</v>
       </c>
       <c r="F32">
-        <v>19.59</v>
+        <v>20.243</v>
       </c>
       <c r="G32">
         <v>12</v>
@@ -4036,37 +4036,37 @@
         <v>2.2</v>
       </c>
       <c r="M32">
-        <v>3.933672</v>
+        <v>4.0647944</v>
       </c>
       <c r="N32">
-        <v>-1.733672</v>
+        <v>-1.8647944</v>
       </c>
       <c r="O32">
-        <v>-0.2600508</v>
+        <v>-0.27971916</v>
       </c>
       <c r="P32">
-        <v>-1.4736212</v>
+        <v>-1.58507524</v>
       </c>
       <c r="Q32">
-        <v>0.4563787999999998</v>
+        <v>0.3449247599999996</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2519664700655167</v>
+        <v>0.2549543899215387</v>
       </c>
       <c r="T32">
-        <v>1.260888466345115</v>
+        <v>1.279162212234175</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.08389108192040415</v>
+        <v>0.08118491798748788</v>
       </c>
       <c r="W32">
-        <v>0.1839546707503829</v>
+        <v>0.1844980684681125</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.559273879469361</v>
+        <v>0.5412327865832525</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2331129302709765</v>
+        <v>0.2346629302709765</v>
       </c>
       <c r="C33">
-        <v>33.88253682897566</v>
+        <v>32.88381211745483</v>
       </c>
       <c r="D33">
-        <v>42.12553682897566</v>
+        <v>41.77981211745483</v>
       </c>
       <c r="E33">
-        <v>20.243</v>
+        <v>20.896</v>
       </c>
       <c r="F33">
-        <v>20.243</v>
+        <v>20.896</v>
       </c>
       <c r="G33">
         <v>12</v>
@@ -4118,37 +4118,37 @@
         <v>2.2</v>
       </c>
       <c r="M33">
-        <v>4.0647944</v>
+        <v>4.1959168</v>
       </c>
       <c r="N33">
-        <v>-1.8647944</v>
+        <v>-1.9959168</v>
       </c>
       <c r="O33">
-        <v>-0.27971916</v>
+        <v>-0.29938752</v>
       </c>
       <c r="P33">
-        <v>-1.58507524</v>
+        <v>-1.69652928</v>
       </c>
       <c r="Q33">
-        <v>0.3449247599999996</v>
+        <v>0.2334707199999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2549543899215387</v>
+        <v>0.258030189773326</v>
       </c>
       <c r="T33">
-        <v>1.279162212234175</v>
+        <v>1.297973421237619</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.08118491798748788</v>
+        <v>0.07864788930037887</v>
       </c>
       <c r="W33">
-        <v>0.1844980684681125</v>
+        <v>0.1850075038284839</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5412327865832525</v>
+        <v>0.5243192620025259</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2346629302709765</v>
+        <v>0.2362129302709765</v>
       </c>
       <c r="C34">
-        <v>32.88381211745483</v>
+        <v>31.89071594494229</v>
       </c>
       <c r="D34">
-        <v>41.77981211745483</v>
+        <v>41.43971594494229</v>
       </c>
       <c r="E34">
-        <v>20.896</v>
+        <v>21.549</v>
       </c>
       <c r="F34">
-        <v>20.896</v>
+        <v>21.549</v>
       </c>
       <c r="G34">
         <v>12</v>
@@ -4200,37 +4200,37 @@
         <v>2.2</v>
       </c>
       <c r="M34">
-        <v>4.1959168</v>
+        <v>4.3270392</v>
       </c>
       <c r="N34">
-        <v>-1.9959168</v>
+        <v>-2.1270392</v>
       </c>
       <c r="O34">
-        <v>-0.29938752</v>
+        <v>-0.3190558799999999</v>
       </c>
       <c r="P34">
-        <v>-1.69652928</v>
+        <v>-1.80798332</v>
       </c>
       <c r="Q34">
-        <v>0.2334707199999999</v>
+        <v>0.12201668</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.258030189773326</v>
+        <v>0.2611978045460622</v>
       </c>
       <c r="T34">
-        <v>1.297973421237619</v>
+        <v>1.317346158868031</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.07864788930037887</v>
+        <v>0.07626461992764014</v>
       </c>
       <c r="W34">
-        <v>0.1850075038284839</v>
+        <v>0.1854860643185299</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5243192620025259</v>
+        <v>0.508430799517601</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2362129302709765</v>
+        <v>0.2502159584882396</v>
       </c>
       <c r="C35">
-        <v>31.89071594494229</v>
+        <v>28.39898693384221</v>
       </c>
       <c r="D35">
-        <v>41.43971594494229</v>
+        <v>38.60098693384221</v>
       </c>
       <c r="E35">
-        <v>21.549</v>
+        <v>22.202</v>
       </c>
       <c r="F35">
-        <v>21.549</v>
+        <v>22.202</v>
       </c>
       <c r="G35">
         <v>12</v>
@@ -4282,45 +4282,45 @@
         <v>2.2</v>
       </c>
       <c r="M35">
-        <v>4.3270392</v>
+        <v>5.235231600000001</v>
       </c>
       <c r="N35">
-        <v>-2.1270392</v>
+        <v>-3.0352316</v>
       </c>
       <c r="O35">
-        <v>-0.3190558799999999</v>
+        <v>-0.45528474</v>
       </c>
       <c r="P35">
-        <v>-1.80798332</v>
+        <v>-2.57994686</v>
       </c>
       <c r="Q35">
-        <v>0.12201668</v>
+        <v>-0.6499468600000005</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2611978045460622</v>
+        <v>0.2652993291865527</v>
       </c>
       <c r="T35">
-        <v>1.317346158868031</v>
+        <v>1.342430572992119</v>
       </c>
       <c r="U35">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07626461992764014</v>
+        <v>0.06303446059578338</v>
       </c>
       <c r="W35">
-        <v>0.1854860643185299</v>
+        <v>0.2209364741915143</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.508430799517601</v>
+        <v>0.4202297373052225</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2502159584882396</v>
+        <v>0.2521159584882396</v>
       </c>
       <c r="C36">
-        <v>28.39898693384221</v>
+        <v>27.39050364640432</v>
       </c>
       <c r="D36">
-        <v>38.60098693384221</v>
+        <v>38.24550364640432</v>
       </c>
       <c r="E36">
-        <v>22.202</v>
+        <v>22.855</v>
       </c>
       <c r="F36">
-        <v>22.202</v>
+        <v>22.855</v>
       </c>
       <c r="G36">
         <v>12</v>
@@ -4364,37 +4364,37 @@
         <v>2.2</v>
       </c>
       <c r="M36">
-        <v>5.235231600000001</v>
+        <v>5.389209</v>
       </c>
       <c r="N36">
-        <v>-3.0352316</v>
+        <v>-3.189209</v>
       </c>
       <c r="O36">
-        <v>-0.45528474</v>
+        <v>-0.47838135</v>
       </c>
       <c r="P36">
-        <v>-2.57994686</v>
+        <v>-2.71082765</v>
       </c>
       <c r="Q36">
-        <v>-0.6499468600000005</v>
+        <v>-0.7808276500000004</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2652993291865527</v>
+        <v>0.2686762419432689</v>
       </c>
       <c r="T36">
-        <v>1.342430572992119</v>
+        <v>1.363083351038151</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.06303446059578338</v>
+        <v>0.06123347600733243</v>
       </c>
       <c r="W36">
-        <v>0.2209364741915143</v>
+        <v>0.221361146357471</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4202297373052225</v>
+        <v>0.4082231733822163</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2521159584882396</v>
+        <v>0.2540159584882397</v>
       </c>
       <c r="C37">
-        <v>27.39050364640432</v>
+        <v>26.38850802927791</v>
       </c>
       <c r="D37">
-        <v>38.24550364640432</v>
+        <v>37.89650802927791</v>
       </c>
       <c r="E37">
-        <v>22.855</v>
+        <v>23.508</v>
       </c>
       <c r="F37">
-        <v>22.855</v>
+        <v>23.508</v>
       </c>
       <c r="G37">
         <v>12</v>
@@ -4446,37 +4446,37 @@
         <v>2.2</v>
       </c>
       <c r="M37">
-        <v>5.389209</v>
+        <v>5.543186400000001</v>
       </c>
       <c r="N37">
-        <v>-3.189209</v>
+        <v>-3.3431864</v>
       </c>
       <c r="O37">
-        <v>-0.47838135</v>
+        <v>-0.50147796</v>
       </c>
       <c r="P37">
-        <v>-2.71082765</v>
+        <v>-2.841708440000001</v>
       </c>
       <c r="Q37">
-        <v>-0.7808276500000004</v>
+        <v>-0.9117084400000008</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2686762419432689</v>
+        <v>0.2721586832236325</v>
       </c>
       <c r="T37">
-        <v>1.363083351038151</v>
+        <v>1.384381528398122</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.06123347600733243</v>
+        <v>0.05953254611823985</v>
       </c>
       <c r="W37">
-        <v>0.221361146357471</v>
+        <v>0.2217622256253191</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4082231733822163</v>
+        <v>0.3968836407882658</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2540159584882397</v>
+        <v>0.2559159584882397</v>
       </c>
       <c r="C38">
-        <v>26.38850802927791</v>
+        <v>25.39282408573701</v>
       </c>
       <c r="D38">
-        <v>37.89650802927791</v>
+        <v>37.55382408573701</v>
       </c>
       <c r="E38">
-        <v>23.508</v>
+        <v>24.161</v>
       </c>
       <c r="F38">
-        <v>23.508</v>
+        <v>24.161</v>
       </c>
       <c r="G38">
         <v>12</v>
@@ -4528,37 +4528,37 @@
         <v>2.2</v>
       </c>
       <c r="M38">
-        <v>5.5431864</v>
+        <v>5.697163799999999</v>
       </c>
       <c r="N38">
-        <v>-3.3431864</v>
+        <v>-3.497163799999999</v>
       </c>
       <c r="O38">
-        <v>-0.5014779599999999</v>
+        <v>-0.5245745699999999</v>
       </c>
       <c r="P38">
-        <v>-2.84170844</v>
+        <v>-2.972589229999999</v>
       </c>
       <c r="Q38">
-        <v>-0.91170844</v>
+        <v>-1.042589229999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2721586832236325</v>
+        <v>0.2757516781954362</v>
       </c>
       <c r="T38">
-        <v>1.384381528398122</v>
+        <v>1.406355838372696</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05953254611823987</v>
+        <v>0.05792355838531447</v>
       </c>
       <c r="W38">
-        <v>0.2217622256253191</v>
+        <v>0.2221416249327429</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3968836407882658</v>
+        <v>0.3861570559020965</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2559159584882397</v>
+        <v>0.2578159584882397</v>
       </c>
       <c r="C39">
-        <v>25.39282408573701</v>
+        <v>24.40328212789727</v>
       </c>
       <c r="D39">
-        <v>37.55382408573701</v>
+        <v>37.21728212789727</v>
       </c>
       <c r="E39">
-        <v>24.161</v>
+        <v>24.814</v>
       </c>
       <c r="F39">
-        <v>24.161</v>
+        <v>24.814</v>
       </c>
       <c r="G39">
         <v>12</v>
@@ -4610,37 +4610,37 @@
         <v>2.2</v>
       </c>
       <c r="M39">
-        <v>5.697163799999999</v>
+        <v>5.8511412</v>
       </c>
       <c r="N39">
-        <v>-3.497163799999999</v>
+        <v>-3.6511412</v>
       </c>
       <c r="O39">
-        <v>-0.5245745699999999</v>
+        <v>-0.5476711799999999</v>
       </c>
       <c r="P39">
-        <v>-2.972589229999999</v>
+        <v>-3.10347002</v>
       </c>
       <c r="Q39">
-        <v>-1.042589229999999</v>
+        <v>-1.17347002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2757516781954362</v>
+        <v>0.2794605762308464</v>
       </c>
       <c r="T39">
-        <v>1.406355838372696</v>
+        <v>1.429038997056126</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05792355838531447</v>
+        <v>0.05639925421727988</v>
       </c>
       <c r="W39">
-        <v>0.2221416249327429</v>
+        <v>0.2225010558555654</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3861570559020965</v>
+        <v>0.3759950281151991</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2578159584882397</v>
+        <v>0.2597159584882396</v>
       </c>
       <c r="C40">
-        <v>24.40328212789727</v>
+        <v>23.41971849654067</v>
       </c>
       <c r="D40">
-        <v>37.21728212789727</v>
+        <v>36.88671849654067</v>
       </c>
       <c r="E40">
-        <v>24.814</v>
+        <v>25.467</v>
       </c>
       <c r="F40">
-        <v>24.814</v>
+        <v>25.467</v>
       </c>
       <c r="G40">
         <v>12</v>
@@ -4692,37 +4692,37 @@
         <v>2.2</v>
       </c>
       <c r="M40">
-        <v>5.8511412</v>
+        <v>6.0051186</v>
       </c>
       <c r="N40">
-        <v>-3.6511412</v>
+        <v>-3.8051186</v>
       </c>
       <c r="O40">
-        <v>-0.5476711799999999</v>
+        <v>-0.57076779</v>
       </c>
       <c r="P40">
-        <v>-3.10347002</v>
+        <v>-3.23435081</v>
       </c>
       <c r="Q40">
-        <v>-1.17347002</v>
+        <v>-1.30435081</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2794605762308464</v>
+        <v>0.2832910774805324</v>
       </c>
       <c r="T40">
-        <v>1.429038997056126</v>
+        <v>1.452465865860325</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05639925421727988</v>
+        <v>0.05495311949375987</v>
       </c>
       <c r="W40">
-        <v>0.2225010558555654</v>
+        <v>0.2228420544233714</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3759950281151991</v>
+        <v>0.3663541299583992</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2597159584882396</v>
+        <v>0.2616159584882396</v>
       </c>
       <c r="C41">
-        <v>23.41971849654067</v>
+        <v>22.44197529573956</v>
       </c>
       <c r="D41">
-        <v>36.88671849654067</v>
+        <v>36.56197529573956</v>
       </c>
       <c r="E41">
-        <v>25.467</v>
+        <v>26.12</v>
       </c>
       <c r="F41">
-        <v>25.467</v>
+        <v>26.12</v>
       </c>
       <c r="G41">
         <v>12</v>
@@ -4774,37 +4774,37 @@
         <v>2.2</v>
       </c>
       <c r="M41">
-        <v>6.0051186</v>
+        <v>6.159096000000001</v>
       </c>
       <c r="N41">
-        <v>-3.8051186</v>
+        <v>-3.959096000000001</v>
       </c>
       <c r="O41">
-        <v>-0.57076779</v>
+        <v>-0.5938644000000001</v>
       </c>
       <c r="P41">
-        <v>-3.23435081</v>
+        <v>-3.3652316</v>
       </c>
       <c r="Q41">
-        <v>-1.30435081</v>
+        <v>-1.435231600000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2832910774805324</v>
+        <v>0.287249262105208</v>
       </c>
       <c r="T41">
-        <v>1.452465865860325</v>
+        <v>1.476673630291331</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05495311949375987</v>
+        <v>0.05357929150641588</v>
       </c>
       <c r="W41">
-        <v>0.2228420544233714</v>
+        <v>0.2231660030627872</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3663541299583992</v>
+        <v>0.3571952767094392</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2616159584882396</v>
+        <v>0.2635159584882397</v>
       </c>
       <c r="C42">
-        <v>22.44197529573956</v>
+        <v>21.46990014137664</v>
       </c>
       <c r="D42">
-        <v>36.56197529573956</v>
+        <v>36.24290014137664</v>
       </c>
       <c r="E42">
-        <v>26.12</v>
+        <v>26.773</v>
       </c>
       <c r="F42">
-        <v>26.12</v>
+        <v>26.773</v>
       </c>
       <c r="G42">
         <v>12</v>
@@ -4856,37 +4856,37 @@
         <v>2.2</v>
       </c>
       <c r="M42">
-        <v>6.159096000000001</v>
+        <v>6.3130734</v>
       </c>
       <c r="N42">
-        <v>-3.959096000000001</v>
+        <v>-4.1130734</v>
       </c>
       <c r="O42">
-        <v>-0.5938644000000001</v>
+        <v>-0.61696101</v>
       </c>
       <c r="P42">
-        <v>-3.3652316</v>
+        <v>-3.49611239</v>
       </c>
       <c r="Q42">
-        <v>-1.435231600000001</v>
+        <v>-1.566112390000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.287249262105208</v>
+        <v>0.2913416224798725</v>
       </c>
       <c r="T42">
-        <v>1.476673630291331</v>
+        <v>1.501701996906438</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05357929150641588</v>
+        <v>0.05227247951845451</v>
       </c>
       <c r="W42">
-        <v>0.2231660030627872</v>
+        <v>0.2234741493295485</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3571952767094392</v>
+        <v>0.3484831967896967</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2635159584882397</v>
+        <v>0.2654159584882396</v>
       </c>
       <c r="C43">
-        <v>21.46990014137664</v>
+        <v>20.50334592271861</v>
       </c>
       <c r="D43">
-        <v>36.24290014137664</v>
+        <v>35.92934592271861</v>
       </c>
       <c r="E43">
-        <v>26.773</v>
+        <v>27.426</v>
       </c>
       <c r="F43">
-        <v>26.773</v>
+        <v>27.426</v>
       </c>
       <c r="G43">
         <v>12</v>
@@ -4938,37 +4938,37 @@
         <v>2.2</v>
       </c>
       <c r="M43">
-        <v>6.3130734</v>
+        <v>6.467050800000001</v>
       </c>
       <c r="N43">
-        <v>-4.1130734</v>
+        <v>-4.267050800000001</v>
       </c>
       <c r="O43">
-        <v>-0.61696101</v>
+        <v>-0.6400576200000001</v>
       </c>
       <c r="P43">
-        <v>-3.49611239</v>
+        <v>-3.62699318</v>
       </c>
       <c r="Q43">
-        <v>-1.566112390000001</v>
+        <v>-1.696993180000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2913416224798725</v>
+        <v>0.2955750987295255</v>
       </c>
       <c r="T43">
-        <v>1.501701996906438</v>
+        <v>1.527593410646204</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05227247951845451</v>
+        <v>0.05102789667277702</v>
       </c>
       <c r="W43">
-        <v>0.2234741493295485</v>
+        <v>0.2237676219645592</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3484831967896967</v>
+        <v>0.3401859778185135</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2654159584882396</v>
+        <v>0.2673159584882396</v>
       </c>
       <c r="C44">
-        <v>20.50334592271861</v>
+        <v>19.54217057626026</v>
       </c>
       <c r="D44">
-        <v>35.92934592271861</v>
+        <v>35.62117057626026</v>
       </c>
       <c r="E44">
-        <v>27.426</v>
+        <v>28.079</v>
       </c>
       <c r="F44">
-        <v>27.426</v>
+        <v>28.079</v>
       </c>
       <c r="G44">
         <v>12</v>
@@ -5020,37 +5020,37 @@
         <v>2.2</v>
       </c>
       <c r="M44">
-        <v>6.4670508</v>
+        <v>6.6210282</v>
       </c>
       <c r="N44">
-        <v>-4.2670508</v>
+        <v>-4.421028199999999</v>
       </c>
       <c r="O44">
-        <v>-0.64005762</v>
+        <v>-0.6631542299999998</v>
       </c>
       <c r="P44">
-        <v>-3.62699318</v>
+        <v>-3.757873969999999</v>
       </c>
       <c r="Q44">
-        <v>-1.69699318</v>
+        <v>-1.82787397</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2955750987295255</v>
+        <v>0.2999571180054821</v>
       </c>
       <c r="T44">
-        <v>1.527593410646204</v>
+        <v>1.554393295043506</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05102789667277702</v>
+        <v>0.0498412014013171</v>
       </c>
       <c r="W44">
-        <v>0.2237676219645592</v>
+        <v>0.2240474447095694</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3401859778185136</v>
+        <v>0.3322746760087807</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2673159584882396</v>
+        <v>0.2692159584882396</v>
       </c>
       <c r="C45">
-        <v>19.54217057626026</v>
+        <v>18.58623687110841</v>
       </c>
       <c r="D45">
-        <v>35.62117057626026</v>
+        <v>35.31823687110841</v>
       </c>
       <c r="E45">
-        <v>28.079</v>
+        <v>28.732</v>
       </c>
       <c r="F45">
-        <v>28.079</v>
+        <v>28.732</v>
       </c>
       <c r="G45">
         <v>12</v>
@@ -5102,37 +5102,37 @@
         <v>2.2</v>
       </c>
       <c r="M45">
-        <v>6.6210282</v>
+        <v>6.7750056</v>
       </c>
       <c r="N45">
-        <v>-4.421028199999999</v>
+        <v>-4.5750056</v>
       </c>
       <c r="O45">
-        <v>-0.6631542299999998</v>
+        <v>-0.6862508399999999</v>
       </c>
       <c r="P45">
-        <v>-3.757873969999999</v>
+        <v>-3.88875476</v>
       </c>
       <c r="Q45">
-        <v>-1.82787397</v>
+        <v>-1.95875476</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2999571180054821</v>
+        <v>0.3044956379698657</v>
       </c>
       <c r="T45">
-        <v>1.554393295043506</v>
+        <v>1.582150318169283</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.0498412014013171</v>
+        <v>0.04870844682401444</v>
       </c>
       <c r="W45">
-        <v>0.2240474447095694</v>
+        <v>0.2243145482388974</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3322746760087807</v>
+        <v>0.3247229788267629</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2692159584882396</v>
+        <v>0.2711159584882397</v>
       </c>
       <c r="C46">
-        <v>18.58623687110841</v>
+        <v>17.63541220522435</v>
       </c>
       <c r="D46">
-        <v>35.31823687110841</v>
+        <v>35.02041220522435</v>
       </c>
       <c r="E46">
-        <v>28.732</v>
+        <v>29.385</v>
       </c>
       <c r="F46">
-        <v>28.732</v>
+        <v>29.385</v>
       </c>
       <c r="G46">
         <v>12</v>
@@ -5184,37 +5184,37 @@
         <v>2.2</v>
       </c>
       <c r="M46">
-        <v>6.7750056</v>
+        <v>6.928983</v>
       </c>
       <c r="N46">
-        <v>-4.5750056</v>
+        <v>-4.728982999999999</v>
       </c>
       <c r="O46">
-        <v>-0.6862508399999999</v>
+        <v>-0.7093474499999999</v>
       </c>
       <c r="P46">
-        <v>-3.88875476</v>
+        <v>-4.019635549999999</v>
       </c>
       <c r="Q46">
-        <v>-1.95875476</v>
+        <v>-2.08963555</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3044956379698657</v>
+        <v>0.3091991950238633</v>
       </c>
       <c r="T46">
-        <v>1.582150318169283</v>
+        <v>1.610916687590543</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04870844682401444</v>
+        <v>0.0476260368945919</v>
       </c>
       <c r="W46">
-        <v>0.2243145482388974</v>
+        <v>0.2245697805002553</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3247229788267629</v>
+        <v>0.3175069126306126</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2711159584882397</v>
+        <v>0.2730159584882397</v>
       </c>
       <c r="C47">
-        <v>17.63541220522435</v>
+        <v>16.68956841188943</v>
       </c>
       <c r="D47">
-        <v>35.02041220522435</v>
+        <v>34.72756841188943</v>
       </c>
       <c r="E47">
-        <v>29.385</v>
+        <v>30.038</v>
       </c>
       <c r="F47">
-        <v>29.385</v>
+        <v>30.038</v>
       </c>
       <c r="G47">
         <v>12</v>
@@ -5266,37 +5266,37 @@
         <v>2.2</v>
       </c>
       <c r="M47">
-        <v>6.928983</v>
+        <v>7.0829604</v>
       </c>
       <c r="N47">
-        <v>-4.728982999999999</v>
+        <v>-4.8829604</v>
       </c>
       <c r="O47">
-        <v>-0.7093474499999999</v>
+        <v>-0.73244406</v>
       </c>
       <c r="P47">
-        <v>-4.019635549999999</v>
+        <v>-4.15051634</v>
       </c>
       <c r="Q47">
-        <v>-2.08963555</v>
+        <v>-2.220516340000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3091991950238633</v>
+        <v>0.3140769578946755</v>
       </c>
       <c r="T47">
-        <v>1.610916687590543</v>
+        <v>1.640748478101478</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0476260368945919</v>
+        <v>0.04659068826644859</v>
       </c>
       <c r="W47">
-        <v>0.2245697805002553</v>
+        <v>0.2248139157067714</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3175069126306126</v>
+        <v>0.3106045884429907</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2730159584882397</v>
+        <v>0.2749159584882397</v>
       </c>
       <c r="C48">
-        <v>16.68956841188943</v>
+        <v>15.74858157580015</v>
       </c>
       <c r="D48">
-        <v>34.72756841188943</v>
+        <v>34.43958157580015</v>
       </c>
       <c r="E48">
-        <v>30.038</v>
+        <v>30.691</v>
       </c>
       <c r="F48">
-        <v>30.038</v>
+        <v>30.691</v>
       </c>
       <c r="G48">
         <v>12</v>
@@ -5348,37 +5348,37 @@
         <v>2.2</v>
       </c>
       <c r="M48">
-        <v>7.0829604</v>
+        <v>7.2369378</v>
       </c>
       <c r="N48">
-        <v>-4.8829604</v>
+        <v>-5.0369378</v>
       </c>
       <c r="O48">
-        <v>-0.73244406</v>
+        <v>-0.7555406699999999</v>
       </c>
       <c r="P48">
-        <v>-4.15051634</v>
+        <v>-4.281397129999999</v>
       </c>
       <c r="Q48">
-        <v>-2.220516340000001</v>
+        <v>-2.35139713</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3140769578946755</v>
+        <v>0.3191387872889147</v>
       </c>
       <c r="T48">
-        <v>1.640748478101478</v>
+        <v>1.671705996556223</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04659068826644859</v>
+        <v>0.04559939702673692</v>
       </c>
       <c r="W48">
-        <v>0.2248139157067714</v>
+        <v>0.2250476621810955</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3106045884429907</v>
+        <v>0.3039959801782461</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2749159584882397</v>
+        <v>0.2768159584882397</v>
       </c>
       <c r="C49">
-        <v>15.74858157580015</v>
+        <v>14.81233185823853</v>
       </c>
       <c r="D49">
-        <v>34.43958157580015</v>
+        <v>34.15633185823853</v>
       </c>
       <c r="E49">
-        <v>30.691</v>
+        <v>31.344</v>
       </c>
       <c r="F49">
-        <v>30.691</v>
+        <v>31.344</v>
       </c>
       <c r="G49">
         <v>12</v>
@@ -5430,37 +5430,37 @@
         <v>2.2</v>
       </c>
       <c r="M49">
-        <v>7.2369378</v>
+        <v>7.3909152</v>
       </c>
       <c r="N49">
-        <v>-5.0369378</v>
+        <v>-5.1909152</v>
       </c>
       <c r="O49">
-        <v>-0.7555406699999999</v>
+        <v>-0.77863728</v>
       </c>
       <c r="P49">
-        <v>-4.281397129999999</v>
+        <v>-4.41227792</v>
       </c>
       <c r="Q49">
-        <v>-2.35139713</v>
+        <v>-2.48227792</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3191387872889147</v>
+        <v>0.3243953024290862</v>
       </c>
       <c r="T49">
-        <v>1.671705996556223</v>
+        <v>1.703854188797689</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04559939702673692</v>
+        <v>0.0446494095886799</v>
       </c>
       <c r="W49">
-        <v>0.2250476621810955</v>
+        <v>0.2252716692189893</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3039959801782461</v>
+        <v>0.2976627305911993</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2768159584882396</v>
+        <v>0.2787159584882397</v>
       </c>
       <c r="C50">
-        <v>14.81233185823854</v>
+        <v>13.8807033307994</v>
       </c>
       <c r="D50">
-        <v>34.15633185823854</v>
+        <v>33.8777033307994</v>
       </c>
       <c r="E50">
-        <v>31.344</v>
+        <v>31.997</v>
       </c>
       <c r="F50">
-        <v>31.344</v>
+        <v>31.997</v>
       </c>
       <c r="G50">
         <v>12</v>
@@ -5512,37 +5512,37 @@
         <v>2.2</v>
       </c>
       <c r="M50">
-        <v>7.390915199999999</v>
+        <v>7.5448926</v>
       </c>
       <c r="N50">
-        <v>-5.190915199999999</v>
+        <v>-5.3448926</v>
       </c>
       <c r="O50">
-        <v>-0.7786372799999999</v>
+        <v>-0.8017338899999999</v>
       </c>
       <c r="P50">
-        <v>-4.412277919999999</v>
+        <v>-4.54315871</v>
       </c>
       <c r="Q50">
-        <v>-2.48227792</v>
+        <v>-2.61315871</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3243953024290861</v>
+        <v>0.3298579554178917</v>
       </c>
       <c r="T50">
-        <v>1.703854188797689</v>
+        <v>1.737263094460389</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0446494095886799</v>
+        <v>0.0437381971480946</v>
       </c>
       <c r="W50">
-        <v>0.2252716692189893</v>
+        <v>0.2254865331124793</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2976627305911994</v>
+        <v>0.2915879809872973</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2787159584882397</v>
+        <v>0.2806159584882396</v>
       </c>
       <c r="C51">
-        <v>13.8807033307994</v>
+        <v>12.95358381719002</v>
       </c>
       <c r="D51">
-        <v>33.8777033307994</v>
+        <v>33.60358381719001</v>
       </c>
       <c r="E51">
-        <v>31.997</v>
+        <v>32.65</v>
       </c>
       <c r="F51">
-        <v>31.997</v>
+        <v>32.65</v>
       </c>
       <c r="G51">
         <v>12</v>
@@ -5594,37 +5594,37 @@
         <v>2.2</v>
       </c>
       <c r="M51">
-        <v>7.5448926</v>
+        <v>7.69887</v>
       </c>
       <c r="N51">
-        <v>-5.3448926</v>
+        <v>-5.49887</v>
       </c>
       <c r="O51">
-        <v>-0.8017338899999999</v>
+        <v>-0.8248305</v>
       </c>
       <c r="P51">
-        <v>-4.54315871</v>
+        <v>-4.6740395</v>
       </c>
       <c r="Q51">
-        <v>-2.61315871</v>
+        <v>-2.7440395</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3298579554178917</v>
+        <v>0.3355391145262495</v>
       </c>
       <c r="T51">
-        <v>1.737263094460389</v>
+        <v>1.772008356349597</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0437381971480946</v>
+        <v>0.0428634332051327</v>
       </c>
       <c r="W51">
-        <v>0.2254865331124793</v>
+        <v>0.2256928024502297</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2915879809872973</v>
+        <v>0.2857562213675513</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2806159584882396</v>
+        <v>0.2825159584882396</v>
       </c>
       <c r="C52">
-        <v>12.95358381719002</v>
+        <v>12.03086474264848</v>
       </c>
       <c r="D52">
-        <v>33.60358381719001</v>
+        <v>33.33386474264848</v>
       </c>
       <c r="E52">
-        <v>32.65</v>
+        <v>33.303</v>
       </c>
       <c r="F52">
-        <v>32.65</v>
+        <v>33.303</v>
       </c>
       <c r="G52">
         <v>12</v>
@@ -5676,37 +5676,37 @@
         <v>2.2</v>
       </c>
       <c r="M52">
-        <v>7.69887</v>
+        <v>7.8528474</v>
       </c>
       <c r="N52">
-        <v>-5.49887</v>
+        <v>-5.6528474</v>
       </c>
       <c r="O52">
-        <v>-0.8248305</v>
+        <v>-0.84792711</v>
       </c>
       <c r="P52">
-        <v>-4.6740395</v>
+        <v>-4.80492029</v>
       </c>
       <c r="Q52">
-        <v>-2.7440395</v>
+        <v>-2.87492029</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3355391145262495</v>
+        <v>0.3414521576798465</v>
       </c>
       <c r="T52">
-        <v>1.772008356349597</v>
+        <v>1.808171792193466</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0428634332051327</v>
+        <v>0.04202297373052226</v>
       </c>
       <c r="W52">
-        <v>0.2256928024502297</v>
+        <v>0.2258909827943429</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2857562213675513</v>
+        <v>0.2801531582034817</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2825159584882396</v>
+        <v>0.2844159584882396</v>
       </c>
       <c r="C53">
-        <v>12.03086474264848</v>
+        <v>11.11244099055624</v>
       </c>
       <c r="D53">
-        <v>33.33386474264848</v>
+        <v>33.06844099055624</v>
       </c>
       <c r="E53">
-        <v>33.303</v>
+        <v>33.956</v>
       </c>
       <c r="F53">
-        <v>33.303</v>
+        <v>33.956</v>
       </c>
       <c r="G53">
         <v>12</v>
@@ -5758,37 +5758,37 @@
         <v>2.2</v>
       </c>
       <c r="M53">
-        <v>7.8528474</v>
+        <v>8.0068248</v>
       </c>
       <c r="N53">
-        <v>-5.6528474</v>
+        <v>-5.8068248</v>
       </c>
       <c r="O53">
-        <v>-0.84792711</v>
+        <v>-0.8710237200000001</v>
       </c>
       <c r="P53">
-        <v>-4.80492029</v>
+        <v>-4.93580108</v>
       </c>
       <c r="Q53">
-        <v>-2.87492029</v>
+        <v>-3.00580108</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3414521576798465</v>
+        <v>0.34761157763151</v>
       </c>
       <c r="T53">
-        <v>1.808171792193466</v>
+        <v>1.845842037864164</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04202297373052226</v>
+        <v>0.0412148396203199</v>
       </c>
       <c r="W53">
-        <v>0.2258909827943429</v>
+        <v>0.2260815408175286</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2801531582034817</v>
+        <v>0.2747655974687994</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2844159584882396</v>
+        <v>0.2863159584882397</v>
       </c>
       <c r="C54">
-        <v>11.11244099055624</v>
+        <v>10.19821076584694</v>
       </c>
       <c r="D54">
-        <v>33.06844099055624</v>
+        <v>32.80721076584694</v>
       </c>
       <c r="E54">
-        <v>33.956</v>
+        <v>34.609</v>
       </c>
       <c r="F54">
-        <v>33.956</v>
+        <v>34.609</v>
       </c>
       <c r="G54">
         <v>12</v>
@@ -5840,37 +5840,37 @@
         <v>2.2</v>
       </c>
       <c r="M54">
-        <v>8.0068248</v>
+        <v>8.160802200000001</v>
       </c>
       <c r="N54">
-        <v>-5.8068248</v>
+        <v>-5.960802200000001</v>
       </c>
       <c r="O54">
-        <v>-0.8710237200000001</v>
+        <v>-0.8941203300000001</v>
       </c>
       <c r="P54">
-        <v>-4.93580108</v>
+        <v>-5.066681870000001</v>
       </c>
       <c r="Q54">
-        <v>-3.00580108</v>
+        <v>-3.136681870000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.34761157763151</v>
+        <v>0.3540331005598399</v>
       </c>
       <c r="T54">
-        <v>1.845842037864164</v>
+        <v>1.885115272712337</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0412148396203199</v>
+        <v>0.04043720113691764</v>
       </c>
       <c r="W54">
-        <v>0.2260815408175286</v>
+        <v>0.2262649079719148</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2747655974687994</v>
+        <v>0.2695813409127843</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2863159584882397</v>
+        <v>0.2882159584882396</v>
       </c>
       <c r="C55">
-        <v>10.19821076584694</v>
+        <v>9.288075464838556</v>
       </c>
       <c r="D55">
-        <v>32.80721076584694</v>
+        <v>32.55007546483856</v>
       </c>
       <c r="E55">
-        <v>34.609</v>
+        <v>35.262</v>
       </c>
       <c r="F55">
-        <v>34.609</v>
+        <v>35.262</v>
       </c>
       <c r="G55">
         <v>12</v>
@@ -5922,37 +5922,37 @@
         <v>2.2</v>
       </c>
       <c r="M55">
-        <v>8.160802200000001</v>
+        <v>8.3147796</v>
       </c>
       <c r="N55">
-        <v>-5.960802200000001</v>
+        <v>-6.114779599999999</v>
       </c>
       <c r="O55">
-        <v>-0.8941203300000001</v>
+        <v>-0.9172169399999999</v>
       </c>
       <c r="P55">
-        <v>-5.066681870000001</v>
+        <v>-5.197562659999999</v>
       </c>
       <c r="Q55">
-        <v>-3.136681870000001</v>
+        <v>-3.267562659999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3540331005598399</v>
+        <v>0.3607338201372278</v>
       </c>
       <c r="T55">
-        <v>1.885115272712337</v>
+        <v>1.926096039510431</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04043720113691764</v>
+        <v>0.03968836407882658</v>
       </c>
       <c r="W55">
-        <v>0.2262649079719148</v>
+        <v>0.2264414837502127</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2695813409127843</v>
+        <v>0.2645890938588439</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2882159584882396</v>
+        <v>0.2901159584882397</v>
       </c>
       <c r="C56">
-        <v>9.288075464838556</v>
+        <v>8.381939551139446</v>
       </c>
       <c r="D56">
-        <v>32.55007546483856</v>
+        <v>32.29693955113945</v>
       </c>
       <c r="E56">
-        <v>35.262</v>
+        <v>35.915</v>
       </c>
       <c r="F56">
-        <v>35.262</v>
+        <v>35.915</v>
       </c>
       <c r="G56">
         <v>12</v>
@@ -6004,37 +6004,37 @@
         <v>2.2</v>
       </c>
       <c r="M56">
-        <v>8.3147796</v>
+        <v>8.468757</v>
       </c>
       <c r="N56">
-        <v>-6.114779599999999</v>
+        <v>-6.268757</v>
       </c>
       <c r="O56">
-        <v>-0.9172169399999999</v>
+        <v>-0.9403135499999999</v>
       </c>
       <c r="P56">
-        <v>-5.197562659999999</v>
+        <v>-5.32844345</v>
       </c>
       <c r="Q56">
-        <v>-3.267562659999999</v>
+        <v>-3.39844345</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3607338201372278</v>
+        <v>0.3677323494736107</v>
       </c>
       <c r="T56">
-        <v>1.926096039510431</v>
+        <v>1.968898173721774</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03968836407882658</v>
+        <v>0.03896675745921155</v>
       </c>
       <c r="W56">
-        <v>0.2264414837502127</v>
+        <v>0.2266116385911179</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2645890938588439</v>
+        <v>0.2597783830614103</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2901159584882397</v>
+        <v>0.2920159584882397</v>
       </c>
       <c r="C57">
-        <v>8.381939551139446</v>
+        <v>7.47971043729995</v>
       </c>
       <c r="D57">
-        <v>32.29693955113945</v>
+        <v>32.04771043729995</v>
       </c>
       <c r="E57">
-        <v>35.915</v>
+        <v>36.568</v>
       </c>
       <c r="F57">
-        <v>35.915</v>
+        <v>36.568</v>
       </c>
       <c r="G57">
         <v>12</v>
@@ -6086,37 +6086,37 @@
         <v>2.2</v>
       </c>
       <c r="M57">
-        <v>8.468757</v>
+        <v>8.622734400000002</v>
       </c>
       <c r="N57">
-        <v>-6.268757</v>
+        <v>-6.422734400000002</v>
       </c>
       <c r="O57">
-        <v>-0.9403135499999999</v>
+        <v>-0.9634101600000002</v>
       </c>
       <c r="P57">
-        <v>-5.32844345</v>
+        <v>-5.459324240000002</v>
       </c>
       <c r="Q57">
-        <v>-3.39844345</v>
+        <v>-3.529324240000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3677323494736107</v>
+        <v>0.3750489937798291</v>
       </c>
       <c r="T57">
-        <v>1.968898173721774</v>
+        <v>2.013645859488178</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03896675745921155</v>
+        <v>0.03827092250458276</v>
       </c>
       <c r="W57">
-        <v>0.2266116385911179</v>
+        <v>0.2267757164734194</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2597783830614103</v>
+        <v>0.255139483363885</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2920159584882397</v>
+        <v>0.2939159584882396</v>
       </c>
       <c r="C58">
-        <v>7.47971043729995</v>
+        <v>6.581298371901696</v>
       </c>
       <c r="D58">
-        <v>32.04771043729995</v>
+        <v>31.8022983719017</v>
       </c>
       <c r="E58">
-        <v>36.568</v>
+        <v>37.221</v>
       </c>
       <c r="F58">
-        <v>36.568</v>
+        <v>37.221</v>
       </c>
       <c r="G58">
         <v>12</v>
@@ -6168,37 +6168,37 @@
         <v>2.2</v>
       </c>
       <c r="M58">
-        <v>8.622734400000002</v>
+        <v>8.776711800000001</v>
       </c>
       <c r="N58">
-        <v>-6.422734400000002</v>
+        <v>-6.576711800000001</v>
       </c>
       <c r="O58">
-        <v>-0.9634101600000002</v>
+        <v>-0.9865067700000001</v>
       </c>
       <c r="P58">
-        <v>-5.459324240000002</v>
+        <v>-5.590205030000001</v>
       </c>
       <c r="Q58">
-        <v>-3.529324240000002</v>
+        <v>-3.660205030000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3750489937798291</v>
+        <v>0.382705947123546</v>
       </c>
       <c r="T58">
-        <v>2.013645859488178</v>
+        <v>2.060474832964647</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03827092250458276</v>
+        <v>0.03759950281151991</v>
       </c>
       <c r="W58">
-        <v>0.2267757164734194</v>
+        <v>0.2269340372370436</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.255139483363885</v>
+        <v>0.2506633520767995</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2939159584882396</v>
+        <v>0.2958159584882396</v>
       </c>
       <c r="C59">
-        <v>6.581298371901696</v>
+        <v>5.686616331795221</v>
       </c>
       <c r="D59">
-        <v>31.8022983719017</v>
+        <v>31.56061633179522</v>
       </c>
       <c r="E59">
-        <v>37.221</v>
+        <v>37.874</v>
       </c>
       <c r="F59">
-        <v>37.221</v>
+        <v>37.874</v>
       </c>
       <c r="G59">
         <v>12</v>
@@ -6250,37 +6250,37 @@
         <v>2.2</v>
       </c>
       <c r="M59">
-        <v>8.776711800000001</v>
+        <v>8.930689200000002</v>
       </c>
       <c r="N59">
-        <v>-6.576711800000001</v>
+        <v>-6.730689200000001</v>
       </c>
       <c r="O59">
-        <v>-0.9865067700000001</v>
+        <v>-1.00960338</v>
       </c>
       <c r="P59">
-        <v>-5.590205030000001</v>
+        <v>-5.721085820000001</v>
       </c>
       <c r="Q59">
-        <v>-3.660205030000001</v>
+        <v>-3.791085820000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.382705947123546</v>
+        <v>0.3907275172931542</v>
       </c>
       <c r="T59">
-        <v>2.060474832964647</v>
+        <v>2.109533757559044</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03759950281151991</v>
+        <v>0.03695123552166612</v>
       </c>
       <c r="W59">
-        <v>0.2269340372370436</v>
+        <v>0.2270868986639911</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2506633520767995</v>
+        <v>0.2463415701444408</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2958159584882396</v>
+        <v>0.2977159584882396</v>
       </c>
       <c r="C60">
-        <v>5.686616331795229</v>
+        <v>4.795579919214354</v>
       </c>
       <c r="D60">
-        <v>31.56061633179522</v>
+        <v>31.32257991921435</v>
       </c>
       <c r="E60">
-        <v>37.874</v>
+        <v>38.52699999999999</v>
       </c>
       <c r="F60">
-        <v>37.874</v>
+        <v>38.52699999999999</v>
       </c>
       <c r="G60">
         <v>12</v>
@@ -6332,37 +6332,37 @@
         <v>2.2</v>
       </c>
       <c r="M60">
-        <v>8.9306892</v>
+        <v>9.084666599999998</v>
       </c>
       <c r="N60">
-        <v>-6.7306892</v>
+        <v>-6.884666599999998</v>
       </c>
       <c r="O60">
-        <v>-1.00960338</v>
+        <v>-1.03269999</v>
       </c>
       <c r="P60">
-        <v>-5.72108582</v>
+        <v>-5.851966609999998</v>
       </c>
       <c r="Q60">
-        <v>-3.79108582</v>
+        <v>-3.921966609999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3907275172931542</v>
+        <v>0.3991403835685969</v>
       </c>
       <c r="T60">
-        <v>2.109533757559043</v>
+        <v>2.160985800426337</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03695123552166613</v>
+        <v>0.03632494339418026</v>
       </c>
       <c r="W60">
-        <v>0.2270868986639911</v>
+        <v>0.2272345783476523</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2463415701444408</v>
+        <v>0.2421662892945351</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2977159584882396</v>
+        <v>0.2996159584882396</v>
       </c>
       <c r="C61">
-        <v>4.795579919214354</v>
+        <v>3.908107263511482</v>
       </c>
       <c r="D61">
-        <v>31.32257991921435</v>
+        <v>31.08810726351148</v>
       </c>
       <c r="E61">
-        <v>38.52699999999999</v>
+        <v>39.18</v>
       </c>
       <c r="F61">
-        <v>38.52699999999999</v>
+        <v>39.18</v>
       </c>
       <c r="G61">
         <v>12</v>
@@ -6414,37 +6414,37 @@
         <v>2.2</v>
       </c>
       <c r="M61">
-        <v>9.084666599999998</v>
+        <v>9.238644000000001</v>
       </c>
       <c r="N61">
-        <v>-6.884666599999998</v>
+        <v>-7.038644000000001</v>
       </c>
       <c r="O61">
-        <v>-1.03269999</v>
+        <v>-1.0557966</v>
       </c>
       <c r="P61">
-        <v>-5.851966609999998</v>
+        <v>-5.982847400000001</v>
       </c>
       <c r="Q61">
-        <v>-3.921966609999998</v>
+        <v>-4.052847400000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3991403835685969</v>
+        <v>0.4079738931578119</v>
       </c>
       <c r="T61">
-        <v>2.160985800426337</v>
+        <v>2.215010445436996</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03632494339418026</v>
+        <v>0.03571952767094391</v>
       </c>
       <c r="W61">
-        <v>0.2272345783476523</v>
+        <v>0.2273773353751914</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2421662892945351</v>
+        <v>0.2381301844729594</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2996159584882396</v>
+        <v>0.3015159584882396</v>
       </c>
       <c r="C62">
-        <v>3.908107263511482</v>
+        <v>3.024118927273605</v>
       </c>
       <c r="D62">
-        <v>31.08810726351148</v>
+        <v>30.8571189272736</v>
       </c>
       <c r="E62">
-        <v>39.18</v>
+        <v>39.833</v>
       </c>
       <c r="F62">
-        <v>39.18</v>
+        <v>39.833</v>
       </c>
       <c r="G62">
         <v>12</v>
@@ -6496,37 +6496,37 @@
         <v>2.2</v>
       </c>
       <c r="M62">
-        <v>9.238644000000001</v>
+        <v>9.392621399999999</v>
       </c>
       <c r="N62">
-        <v>-7.038644000000001</v>
+        <v>-7.192621399999999</v>
       </c>
       <c r="O62">
-        <v>-1.0557966</v>
+        <v>-1.07889321</v>
       </c>
       <c r="P62">
-        <v>-5.982847400000001</v>
+        <v>-6.11372819</v>
       </c>
       <c r="Q62">
-        <v>-4.052847400000001</v>
+        <v>-4.18372819</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4079738931578119</v>
+        <v>0.4172604032387814</v>
       </c>
       <c r="T62">
-        <v>2.215010445436996</v>
+        <v>2.271805585063585</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03571952767094391</v>
+        <v>0.0351339616435514</v>
       </c>
       <c r="W62">
-        <v>0.2273773353751914</v>
+        <v>0.2275154118444506</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2381301844729594</v>
+        <v>0.2342264109570094</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3015159584882396</v>
+        <v>0.3034159584882397</v>
       </c>
       <c r="C63">
-        <v>3.024118927273605</v>
+        <v>2.143537816592932</v>
       </c>
       <c r="D63">
-        <v>30.8571189272736</v>
+        <v>30.62953781659293</v>
       </c>
       <c r="E63">
-        <v>39.833</v>
+        <v>40.486</v>
       </c>
       <c r="F63">
-        <v>39.833</v>
+        <v>40.486</v>
       </c>
       <c r="G63">
         <v>12</v>
@@ -6578,37 +6578,37 @@
         <v>2.2</v>
       </c>
       <c r="M63">
-        <v>9.392621399999999</v>
+        <v>9.5465988</v>
       </c>
       <c r="N63">
-        <v>-7.192621399999999</v>
+        <v>-7.3465988</v>
       </c>
       <c r="O63">
-        <v>-1.07889321</v>
+        <v>-1.10198982</v>
       </c>
       <c r="P63">
-        <v>-6.11372819</v>
+        <v>-6.24460898</v>
       </c>
       <c r="Q63">
-        <v>-4.18372819</v>
+        <v>-4.31460898</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4172604032387814</v>
+        <v>0.4270356770082231</v>
       </c>
       <c r="T63">
-        <v>2.271805585063585</v>
+        <v>2.331589942565259</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0351339616435514</v>
+        <v>0.03456728484284895</v>
       </c>
       <c r="W63">
-        <v>0.2275154118444506</v>
+        <v>0.2276490342340562</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2342264109570094</v>
+        <v>0.2304485656189931</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3034159584882397</v>
+        <v>0.3053159584882397</v>
       </c>
       <c r="C64">
-        <v>2.143537816592932</v>
+        <v>1.266289095279078</v>
       </c>
       <c r="D64">
-        <v>30.62953781659293</v>
+        <v>30.40528909527908</v>
       </c>
       <c r="E64">
-        <v>40.486</v>
+        <v>41.139</v>
       </c>
       <c r="F64">
-        <v>40.486</v>
+        <v>41.139</v>
       </c>
       <c r="G64">
         <v>12</v>
@@ -6660,37 +6660,37 @@
         <v>2.2</v>
       </c>
       <c r="M64">
-        <v>9.5465988</v>
+        <v>9.700576199999999</v>
       </c>
       <c r="N64">
-        <v>-7.3465988</v>
+        <v>-7.500576199999998</v>
       </c>
       <c r="O64">
-        <v>-1.10198982</v>
+        <v>-1.12508643</v>
       </c>
       <c r="P64">
-        <v>-6.24460898</v>
+        <v>-6.375489769999999</v>
       </c>
       <c r="Q64">
-        <v>-4.31460898</v>
+        <v>-4.445489769999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4270356770082231</v>
+        <v>0.4373393439543913</v>
       </c>
       <c r="T64">
-        <v>2.331589942565259</v>
+        <v>2.394605886958914</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03456728484284895</v>
+        <v>0.03401859778185135</v>
       </c>
       <c r="W64">
-        <v>0.2276490342340562</v>
+        <v>0.2277784146430395</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2304485656189931</v>
+        <v>0.226790651879009</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3053159584882397</v>
+        <v>0.3072159584882397</v>
       </c>
       <c r="C65">
-        <v>1.266289095279078</v>
+        <v>0.3923001028123849</v>
       </c>
       <c r="D65">
-        <v>30.40528909527908</v>
+        <v>30.18430010281238</v>
       </c>
       <c r="E65">
-        <v>41.139</v>
+        <v>41.792</v>
       </c>
       <c r="F65">
-        <v>41.139</v>
+        <v>41.792</v>
       </c>
       <c r="G65">
         <v>12</v>
@@ -6742,37 +6742,37 @@
         <v>2.2</v>
       </c>
       <c r="M65">
-        <v>9.700576199999999</v>
+        <v>9.854553600000001</v>
       </c>
       <c r="N65">
-        <v>-7.500576199999998</v>
+        <v>-7.654553600000001</v>
       </c>
       <c r="O65">
-        <v>-1.12508643</v>
+        <v>-1.14818304</v>
       </c>
       <c r="P65">
-        <v>-6.375489769999999</v>
+        <v>-6.506370560000001</v>
       </c>
       <c r="Q65">
-        <v>-4.445489769999999</v>
+        <v>-4.576370560000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4373393439543913</v>
+        <v>0.4482154368420133</v>
       </c>
       <c r="T65">
-        <v>2.394605886958914</v>
+        <v>2.461122717152218</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03401859778185135</v>
+        <v>0.03348705719150992</v>
       </c>
       <c r="W65">
-        <v>0.2277784146430395</v>
+        <v>0.227903751914242</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.226790651879009</v>
+        <v>0.2232470479433994</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3072159584882397</v>
+        <v>0.3091159584882396</v>
       </c>
       <c r="C66">
-        <v>0.3923001028123849</v>
+        <v>-0.4784997241506446</v>
       </c>
       <c r="D66">
-        <v>30.18430010281238</v>
+        <v>29.96650027584936</v>
       </c>
       <c r="E66">
-        <v>41.792</v>
+        <v>42.445</v>
       </c>
       <c r="F66">
-        <v>41.792</v>
+        <v>42.445</v>
       </c>
       <c r="G66">
         <v>12</v>
@@ -6824,37 +6824,37 @@
         <v>2.2</v>
       </c>
       <c r="M66">
-        <v>9.854553600000001</v>
+        <v>10.008531</v>
       </c>
       <c r="N66">
-        <v>-7.654553600000001</v>
+        <v>-7.808530999999999</v>
       </c>
       <c r="O66">
-        <v>-1.14818304</v>
+        <v>-1.17127965</v>
       </c>
       <c r="P66">
-        <v>-6.506370560000001</v>
+        <v>-6.63725135</v>
       </c>
       <c r="Q66">
-        <v>-4.576370560000001</v>
+        <v>-4.70725135</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4482154368420133</v>
+        <v>0.4597130207517851</v>
       </c>
       <c r="T66">
-        <v>2.461122717152218</v>
+        <v>2.531440509070852</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03348705719150992</v>
+        <v>0.03297187169625593</v>
       </c>
       <c r="W66">
-        <v>0.227903751914242</v>
+        <v>0.2280252326540229</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2232470479433994</v>
+        <v>0.2198124779750396</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3091159584882396</v>
+        <v>0.3110159584882397</v>
       </c>
       <c r="C67">
-        <v>-0.4784997241506446</v>
+        <v>-1.346178926897935</v>
       </c>
       <c r="D67">
-        <v>29.96650027584936</v>
+        <v>29.75182107310206</v>
       </c>
       <c r="E67">
-        <v>42.445</v>
+        <v>43.098</v>
       </c>
       <c r="F67">
-        <v>42.445</v>
+        <v>43.098</v>
       </c>
       <c r="G67">
         <v>12</v>
@@ -6906,37 +6906,37 @@
         <v>2.2</v>
       </c>
       <c r="M67">
-        <v>10.008531</v>
+        <v>10.1625084</v>
       </c>
       <c r="N67">
-        <v>-7.808530999999999</v>
+        <v>-7.9625084</v>
       </c>
       <c r="O67">
-        <v>-1.17127965</v>
+        <v>-1.19437626</v>
       </c>
       <c r="P67">
-        <v>-6.63725135</v>
+        <v>-6.768132140000001</v>
       </c>
       <c r="Q67">
-        <v>-4.70725135</v>
+        <v>-4.838132140000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4597130207517851</v>
+        <v>0.4718869331268376</v>
       </c>
       <c r="T67">
-        <v>2.531440509070852</v>
+        <v>2.605894641690583</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03297187169625593</v>
+        <v>0.03247229788267629</v>
       </c>
       <c r="W67">
-        <v>0.2280252326540229</v>
+        <v>0.228143032159265</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2198124779750396</v>
+        <v>0.2164819858845086</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3110159584882397</v>
+        <v>0.3129159584882397</v>
       </c>
       <c r="C68">
-        <v>-1.346178926897935</v>
+        <v>-2.210804096576375</v>
       </c>
       <c r="D68">
-        <v>29.75182107310206</v>
+        <v>29.54019590342362</v>
       </c>
       <c r="E68">
-        <v>43.098</v>
+        <v>43.751</v>
       </c>
       <c r="F68">
-        <v>43.098</v>
+        <v>43.751</v>
       </c>
       <c r="G68">
         <v>12</v>
@@ -6988,37 +6988,37 @@
         <v>2.2</v>
       </c>
       <c r="M68">
-        <v>10.1625084</v>
+        <v>10.3164858</v>
       </c>
       <c r="N68">
-        <v>-7.9625084</v>
+        <v>-8.1164858</v>
       </c>
       <c r="O68">
-        <v>-1.19437626</v>
+        <v>-1.21747287</v>
       </c>
       <c r="P68">
-        <v>-6.768132140000001</v>
+        <v>-6.89901293</v>
       </c>
       <c r="Q68">
-        <v>-4.838132140000001</v>
+        <v>-4.96901293</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4718869331268376</v>
+        <v>0.4847986583731055</v>
       </c>
       <c r="T68">
-        <v>2.605894641690583</v>
+        <v>2.684861145984238</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03247229788267629</v>
+        <v>0.03198763672024828</v>
       </c>
       <c r="W68">
-        <v>0.228143032159265</v>
+        <v>0.2282573152613655</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2164819858845086</v>
+        <v>0.213250911468322</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3129159584882397</v>
+        <v>0.3148159584882396</v>
       </c>
       <c r="C69">
-        <v>-2.210804096576375</v>
+        <v>-3.07243994305891</v>
       </c>
       <c r="D69">
-        <v>29.54019590342362</v>
+        <v>29.33156005694109</v>
       </c>
       <c r="E69">
-        <v>43.751</v>
+        <v>44.404</v>
       </c>
       <c r="F69">
-        <v>43.751</v>
+        <v>44.404</v>
       </c>
       <c r="G69">
         <v>12</v>
@@ -7070,37 +7070,37 @@
         <v>2.2</v>
       </c>
       <c r="M69">
-        <v>10.3164858</v>
+        <v>10.4704632</v>
       </c>
       <c r="N69">
-        <v>-8.1164858</v>
+        <v>-8.270463200000002</v>
       </c>
       <c r="O69">
-        <v>-1.21747287</v>
+        <v>-1.24056948</v>
       </c>
       <c r="P69">
-        <v>-6.89901293</v>
+        <v>-7.029893720000001</v>
       </c>
       <c r="Q69">
-        <v>-4.96901293</v>
+        <v>-5.099893720000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4847986583731055</v>
+        <v>0.498517366447265</v>
       </c>
       <c r="T69">
-        <v>2.684861145984238</v>
+        <v>2.768763056796245</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03198763672024828</v>
+        <v>0.03151723029789169</v>
       </c>
       <c r="W69">
-        <v>0.2282573152613655</v>
+        <v>0.2283682370957572</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.213250911468322</v>
+        <v>0.2101148686526112</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3148159584882396</v>
+        <v>0.3167159584882396</v>
       </c>
       <c r="C70">
-        <v>-3.07243994305891</v>
+        <v>-3.931149360913707</v>
       </c>
       <c r="D70">
-        <v>29.33156005694109</v>
+        <v>29.12585063908629</v>
       </c>
       <c r="E70">
-        <v>44.404</v>
+        <v>45.057</v>
       </c>
       <c r="F70">
-        <v>44.404</v>
+        <v>45.057</v>
       </c>
       <c r="G70">
         <v>12</v>
@@ -7152,37 +7152,37 @@
         <v>2.2</v>
       </c>
       <c r="M70">
-        <v>10.4704632</v>
+        <v>10.6244406</v>
       </c>
       <c r="N70">
-        <v>-8.270463200000002</v>
+        <v>-8.424440600000001</v>
       </c>
       <c r="O70">
-        <v>-1.24056948</v>
+        <v>-1.26366609</v>
       </c>
       <c r="P70">
-        <v>-7.029893720000001</v>
+        <v>-7.16077451</v>
       </c>
       <c r="Q70">
-        <v>-5.099893720000002</v>
+        <v>-5.230774510000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.498517366447265</v>
+        <v>0.5131211524616929</v>
       </c>
       <c r="T70">
-        <v>2.768763056796245</v>
+        <v>2.858077994112253</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03151723029789169</v>
+        <v>0.03106045884429906</v>
       </c>
       <c r="W70">
-        <v>0.2283682370957572</v>
+        <v>0.2284759438045143</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2101148686526112</v>
+        <v>0.2070697256286604</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3167159584882396</v>
+        <v>0.3186159584882396</v>
       </c>
       <c r="C71">
-        <v>-3.931149360913707</v>
+        <v>-4.786993492616688</v>
       </c>
       <c r="D71">
-        <v>29.12585063908629</v>
+        <v>28.92300650738331</v>
       </c>
       <c r="E71">
-        <v>45.057</v>
+        <v>45.71</v>
       </c>
       <c r="F71">
-        <v>45.057</v>
+        <v>45.71</v>
       </c>
       <c r="G71">
         <v>12</v>
@@ -7234,37 +7234,37 @@
         <v>2.2</v>
       </c>
       <c r="M71">
-        <v>10.6244406</v>
+        <v>10.778418</v>
       </c>
       <c r="N71">
-        <v>-8.424440600000001</v>
+        <v>-8.578417999999999</v>
       </c>
       <c r="O71">
-        <v>-1.26366609</v>
+        <v>-1.2867627</v>
       </c>
       <c r="P71">
-        <v>-7.16077451</v>
+        <v>-7.2916553</v>
       </c>
       <c r="Q71">
-        <v>-5.230774510000001</v>
+        <v>-5.3616553</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5131211524616929</v>
+        <v>0.528698524210416</v>
       </c>
       <c r="T71">
-        <v>2.858077994112253</v>
+        <v>2.953347260582662</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03106045884429906</v>
+        <v>0.03061673800366621</v>
       </c>
       <c r="W71">
-        <v>0.2284759438045143</v>
+        <v>0.2285805731787355</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2070697256286604</v>
+        <v>0.2041115866911082</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3186159584882396</v>
+        <v>0.3205159584882397</v>
       </c>
       <c r="C72">
-        <v>-4.786993492616688</v>
+        <v>-5.640031789140991</v>
       </c>
       <c r="D72">
-        <v>28.92300650738331</v>
+        <v>28.72296821085901</v>
       </c>
       <c r="E72">
-        <v>45.71</v>
+        <v>46.363</v>
       </c>
       <c r="F72">
-        <v>45.71</v>
+        <v>46.363</v>
       </c>
       <c r="G72">
         <v>12</v>
@@ -7316,37 +7316,37 @@
         <v>2.2</v>
       </c>
       <c r="M72">
-        <v>10.778418</v>
+        <v>10.9323954</v>
       </c>
       <c r="N72">
-        <v>-8.578417999999999</v>
+        <v>-8.732395400000001</v>
       </c>
       <c r="O72">
-        <v>-1.2867627</v>
+        <v>-1.30985931</v>
       </c>
       <c r="P72">
-        <v>-7.2916553</v>
+        <v>-7.422536090000001</v>
       </c>
       <c r="Q72">
-        <v>-5.3616553</v>
+        <v>-5.492536090000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.528698524210416</v>
+        <v>0.5453501974590511</v>
       </c>
       <c r="T72">
-        <v>2.953347260582662</v>
+        <v>3.055186821292409</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03061673800366621</v>
+        <v>0.03018551634164275</v>
       </c>
       <c r="W72">
-        <v>0.2285805731787355</v>
+        <v>0.2286822552466406</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2041115866911082</v>
+        <v>0.2012367756109515</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3205159584882396</v>
+        <v>0.3224159584882397</v>
       </c>
       <c r="C73">
-        <v>-5.64003178914097</v>
+        <v>-6.490322068049288</v>
       </c>
       <c r="D73">
-        <v>28.72296821085902</v>
+        <v>28.52567793195071</v>
       </c>
       <c r="E73">
-        <v>46.36299999999999</v>
+        <v>47.016</v>
       </c>
       <c r="F73">
-        <v>46.36299999999999</v>
+        <v>47.016</v>
       </c>
       <c r="G73">
         <v>12</v>
@@ -7398,37 +7398,37 @@
         <v>2.2</v>
       </c>
       <c r="M73">
-        <v>10.9323954</v>
+        <v>11.0863728</v>
       </c>
       <c r="N73">
-        <v>-8.732395399999998</v>
+        <v>-8.8863728</v>
       </c>
       <c r="O73">
-        <v>-1.30985931</v>
+        <v>-1.33295592</v>
       </c>
       <c r="P73">
-        <v>-7.422536089999999</v>
+        <v>-7.55341688</v>
       </c>
       <c r="Q73">
-        <v>-5.492536089999999</v>
+        <v>-5.623416880000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5453501974590509</v>
+        <v>0.5631912759397313</v>
       </c>
       <c r="T73">
-        <v>3.055186821292408</v>
+        <v>3.164300636338565</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03018551634164275</v>
+        <v>0.02976627305911993</v>
       </c>
       <c r="W73">
-        <v>0.2286822552466406</v>
+        <v>0.2287811128126595</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2012367756109518</v>
+        <v>0.1984418203941328</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3224159584882397</v>
+        <v>0.3243159584882396</v>
       </c>
       <c r="C74">
-        <v>-6.490322068049288</v>
+        <v>-7.337920569208407</v>
       </c>
       <c r="D74">
-        <v>28.52567793195071</v>
+        <v>28.33107943079159</v>
       </c>
       <c r="E74">
-        <v>47.016</v>
+        <v>47.669</v>
       </c>
       <c r="F74">
-        <v>47.016</v>
+        <v>47.669</v>
       </c>
       <c r="G74">
         <v>12</v>
@@ -7480,37 +7480,37 @@
         <v>2.2</v>
       </c>
       <c r="M74">
-        <v>11.0863728</v>
+        <v>11.2403502</v>
       </c>
       <c r="N74">
-        <v>-8.8863728</v>
+        <v>-9.040350199999999</v>
       </c>
       <c r="O74">
-        <v>-1.33295592</v>
+        <v>-1.35605253</v>
       </c>
       <c r="P74">
-        <v>-7.55341688</v>
+        <v>-7.684297669999999</v>
       </c>
       <c r="Q74">
-        <v>-5.623416880000001</v>
+        <v>-5.75429767</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5631912759397313</v>
+        <v>0.5823539157893509</v>
       </c>
       <c r="T74">
-        <v>3.164300636338565</v>
+        <v>3.281496956202956</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02976627305911993</v>
+        <v>0.02935851589392651</v>
       </c>
       <c r="W74">
-        <v>0.2287811128126595</v>
+        <v>0.2288772619522121</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1984418203941328</v>
+        <v>0.1957234392928435</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3243159584882396</v>
+        <v>0.3262159584882396</v>
       </c>
       <c r="C75">
-        <v>-7.337920569208407</v>
+        <v>-8.182882008238842</v>
       </c>
       <c r="D75">
-        <v>28.33107943079159</v>
+        <v>28.13911799176115</v>
       </c>
       <c r="E75">
-        <v>47.669</v>
+        <v>48.322</v>
       </c>
       <c r="F75">
-        <v>47.669</v>
+        <v>48.322</v>
       </c>
       <c r="G75">
         <v>12</v>
@@ -7562,37 +7562,37 @@
         <v>2.2</v>
       </c>
       <c r="M75">
-        <v>11.2403502</v>
+        <v>11.3943276</v>
       </c>
       <c r="N75">
-        <v>-9.040350199999999</v>
+        <v>-9.194327599999998</v>
       </c>
       <c r="O75">
-        <v>-1.35605253</v>
+        <v>-1.37914914</v>
       </c>
       <c r="P75">
-        <v>-7.684297669999999</v>
+        <v>-7.815178459999998</v>
       </c>
       <c r="Q75">
-        <v>-5.75429767</v>
+        <v>-5.885178459999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5823539157893509</v>
+        <v>0.6029906048581721</v>
       </c>
       <c r="T75">
-        <v>3.281496956202956</v>
+        <v>3.407708377595378</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02935851589392651</v>
+        <v>0.02896177919265723</v>
       </c>
       <c r="W75">
-        <v>0.2288772619522121</v>
+        <v>0.2289708124663714</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1957234392928435</v>
+        <v>0.1930785279510483</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3262159584882396</v>
+        <v>0.3281159584882396</v>
       </c>
       <c r="C76">
-        <v>-8.182882008238842</v>
+        <v>-9.025259627806079</v>
       </c>
       <c r="D76">
-        <v>28.13911799176115</v>
+        <v>27.94974037219391</v>
       </c>
       <c r="E76">
-        <v>48.322</v>
+        <v>48.97499999999999</v>
       </c>
       <c r="F76">
-        <v>48.322</v>
+        <v>48.97499999999999</v>
       </c>
       <c r="G76">
         <v>12</v>
@@ -7644,37 +7644,37 @@
         <v>2.2</v>
       </c>
       <c r="M76">
-        <v>11.3943276</v>
+        <v>11.548305</v>
       </c>
       <c r="N76">
-        <v>-9.194327599999998</v>
+        <v>-9.348305</v>
       </c>
       <c r="O76">
-        <v>-1.37914914</v>
+        <v>-1.40224575</v>
       </c>
       <c r="P76">
-        <v>-7.815178459999998</v>
+        <v>-7.94605925</v>
       </c>
       <c r="Q76">
-        <v>-5.885178459999999</v>
+        <v>-6.016059250000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6029906048581721</v>
+        <v>0.625278229052499</v>
       </c>
       <c r="T76">
-        <v>3.407708377595378</v>
+        <v>3.544016712699193</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02896177919265723</v>
+        <v>0.02857562213675514</v>
       </c>
       <c r="W76">
-        <v>0.2289708124663714</v>
+        <v>0.2290618683001532</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1930785279510483</v>
+        <v>0.1905041475783675</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3281159584882396</v>
+        <v>0.3300159584882396</v>
       </c>
       <c r="C77">
-        <v>-9.025259627806079</v>
+        <v>-9.865105246854483</v>
       </c>
       <c r="D77">
-        <v>27.94974037219391</v>
+        <v>27.76289475314552</v>
       </c>
       <c r="E77">
-        <v>48.97499999999999</v>
+        <v>49.628</v>
       </c>
       <c r="F77">
-        <v>48.97499999999999</v>
+        <v>49.628</v>
       </c>
       <c r="G77">
         <v>12</v>
@@ -7726,37 +7726,37 @@
         <v>2.2</v>
       </c>
       <c r="M77">
-        <v>11.548305</v>
+        <v>11.7022824</v>
       </c>
       <c r="N77">
-        <v>-9.348305</v>
+        <v>-9.502282399999999</v>
       </c>
       <c r="O77">
-        <v>-1.40224575</v>
+        <v>-1.42534236</v>
       </c>
       <c r="P77">
-        <v>-7.94605925</v>
+        <v>-8.076940039999998</v>
       </c>
       <c r="Q77">
-        <v>-6.016059250000001</v>
+        <v>-6.146940039999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.625278229052499</v>
+        <v>0.6494231552630199</v>
       </c>
       <c r="T77">
-        <v>3.544016712699193</v>
+        <v>3.691684075728326</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02857562213675514</v>
+        <v>0.02819962710863994</v>
       </c>
       <c r="W77">
-        <v>0.2290618683001532</v>
+        <v>0.2291505279277827</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1905041475783675</v>
+        <v>0.1879975140575997</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3300159584882396</v>
+        <v>0.3319159584882396</v>
       </c>
       <c r="C78">
-        <v>-9.865105246854483</v>
+        <v>-10.70246930787956</v>
       </c>
       <c r="D78">
-        <v>27.76289475314552</v>
+        <v>27.57853069212043</v>
       </c>
       <c r="E78">
-        <v>49.628</v>
+        <v>50.281</v>
       </c>
       <c r="F78">
-        <v>49.628</v>
+        <v>50.281</v>
       </c>
       <c r="G78">
         <v>12</v>
@@ -7808,37 +7808,37 @@
         <v>2.2</v>
       </c>
       <c r="M78">
-        <v>11.7022824</v>
+        <v>11.8562598</v>
       </c>
       <c r="N78">
-        <v>-9.502282399999999</v>
+        <v>-9.656259800000001</v>
       </c>
       <c r="O78">
-        <v>-1.42534236</v>
+        <v>-1.44843897</v>
       </c>
       <c r="P78">
-        <v>-8.076940039999998</v>
+        <v>-8.207820830000001</v>
       </c>
       <c r="Q78">
-        <v>-6.146940039999999</v>
+        <v>-6.277820830000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6494231552630199</v>
+        <v>0.6756676402744555</v>
       </c>
       <c r="T78">
-        <v>3.691684075728326</v>
+        <v>3.852192079020862</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02819962710863994</v>
+        <v>0.02783339818515111</v>
       </c>
       <c r="W78">
-        <v>0.2291505279277827</v>
+        <v>0.2292368847079414</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1879975140575997</v>
+        <v>0.1855559879010074</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3319159584882396</v>
+        <v>0.3338159584882396</v>
       </c>
       <c r="C79">
-        <v>-10.70246930787956</v>
+        <v>-11.53740092232923</v>
       </c>
       <c r="D79">
-        <v>27.57853069212043</v>
+        <v>27.39659907767077</v>
       </c>
       <c r="E79">
-        <v>50.281</v>
+        <v>50.934</v>
       </c>
       <c r="F79">
-        <v>50.281</v>
+        <v>50.934</v>
       </c>
       <c r="G79">
         <v>12</v>
@@ -7890,37 +7890,37 @@
         <v>2.2</v>
       </c>
       <c r="M79">
-        <v>11.8562598</v>
+        <v>12.0102372</v>
       </c>
       <c r="N79">
-        <v>-9.656259800000001</v>
+        <v>-9.8102372</v>
       </c>
       <c r="O79">
-        <v>-1.44843897</v>
+        <v>-1.47153558</v>
       </c>
       <c r="P79">
-        <v>-8.207820830000001</v>
+        <v>-8.33870162</v>
       </c>
       <c r="Q79">
-        <v>-6.277820830000001</v>
+        <v>-6.40870162</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6756676402744555</v>
+        <v>0.7042979875596581</v>
       </c>
       <c r="T79">
-        <v>3.852192079020862</v>
+        <v>4.027291718976357</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02783339818515111</v>
+        <v>0.02747655974687994</v>
       </c>
       <c r="W79">
-        <v>0.2292368847079414</v>
+        <v>0.2293210272116857</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1855559879010074</v>
+        <v>0.1831770649791996</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3338159584882396</v>
+        <v>0.3357159584882396</v>
       </c>
       <c r="C80">
-        <v>-11.53740092232923</v>
+        <v>-12.36994791421958</v>
       </c>
       <c r="D80">
-        <v>27.39659907767077</v>
+        <v>27.21705208578042</v>
       </c>
       <c r="E80">
-        <v>50.934</v>
+        <v>51.587</v>
       </c>
       <c r="F80">
-        <v>50.934</v>
+        <v>51.587</v>
       </c>
       <c r="G80">
         <v>12</v>
@@ -7972,37 +7972,37 @@
         <v>2.2</v>
       </c>
       <c r="M80">
-        <v>12.0102372</v>
+        <v>12.1642146</v>
       </c>
       <c r="N80">
-        <v>-9.8102372</v>
+        <v>-9.964214600000002</v>
       </c>
       <c r="O80">
-        <v>-1.47153558</v>
+        <v>-1.49463219</v>
       </c>
       <c r="P80">
-        <v>-8.33870162</v>
+        <v>-8.469582410000001</v>
       </c>
       <c r="Q80">
-        <v>-6.40870162</v>
+        <v>-6.539582410000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7042979875596581</v>
+        <v>0.7356550345863084</v>
       </c>
       <c r="T80">
-        <v>4.027291718976357</v>
+        <v>4.219067515118088</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02747655974687994</v>
+        <v>0.02712875519312196</v>
       </c>
       <c r="W80">
-        <v>0.2293210272116857</v>
+        <v>0.2294030395254618</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1831770649791996</v>
+        <v>0.1808583679541463</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3357159584882396</v>
+        <v>0.3376159584882396</v>
       </c>
       <c r="C81">
-        <v>-12.36994791421958</v>
+        <v>-13.20015686204711</v>
       </c>
       <c r="D81">
-        <v>27.21705208578042</v>
+        <v>27.03984313795289</v>
       </c>
       <c r="E81">
-        <v>51.587</v>
+        <v>52.24</v>
       </c>
       <c r="F81">
-        <v>51.587</v>
+        <v>52.24</v>
       </c>
       <c r="G81">
         <v>12</v>
@@ -8054,37 +8054,37 @@
         <v>2.2</v>
       </c>
       <c r="M81">
-        <v>12.1642146</v>
+        <v>12.318192</v>
       </c>
       <c r="N81">
-        <v>-9.964214600000002</v>
+        <v>-10.118192</v>
       </c>
       <c r="O81">
-        <v>-1.49463219</v>
+        <v>-1.5177288</v>
       </c>
       <c r="P81">
-        <v>-8.469582410000001</v>
+        <v>-8.6004632</v>
       </c>
       <c r="Q81">
-        <v>-6.539582410000001</v>
+        <v>-6.6704632</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7356550345863084</v>
+        <v>0.770147786315624</v>
       </c>
       <c r="T81">
-        <v>4.219067515118088</v>
+        <v>4.430020890873992</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02712875519312196</v>
+        <v>0.02678964575320794</v>
       </c>
       <c r="W81">
-        <v>0.2294030395254618</v>
+        <v>0.2294830015313936</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1808583679541463</v>
+        <v>0.1785976383547196</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3376159584882396</v>
+        <v>0.3395159584882397</v>
       </c>
       <c r="C82">
-        <v>-13.20015686204711</v>
+        <v>-14.02807313907388</v>
       </c>
       <c r="D82">
-        <v>27.03984313795289</v>
+        <v>26.86492686092612</v>
       </c>
       <c r="E82">
-        <v>52.24</v>
+        <v>52.893</v>
       </c>
       <c r="F82">
-        <v>52.24</v>
+        <v>52.893</v>
       </c>
       <c r="G82">
         <v>12</v>
@@ -8136,37 +8136,37 @@
         <v>2.2</v>
       </c>
       <c r="M82">
-        <v>12.318192</v>
+        <v>12.4721694</v>
       </c>
       <c r="N82">
-        <v>-10.118192</v>
+        <v>-10.2721694</v>
       </c>
       <c r="O82">
-        <v>-1.5177288</v>
+        <v>-1.54082541</v>
       </c>
       <c r="P82">
-        <v>-8.6004632</v>
+        <v>-8.731343989999999</v>
       </c>
       <c r="Q82">
-        <v>-6.6704632</v>
+        <v>-6.801343989999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.770147786315624</v>
+        <v>0.8082713540164463</v>
       </c>
       <c r="T82">
-        <v>4.430020890873992</v>
+        <v>4.663179885130519</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02678964575320794</v>
+        <v>0.02645890938588439</v>
       </c>
       <c r="W82">
-        <v>0.2294830015313936</v>
+        <v>0.2295609891668085</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1785976383547196</v>
+        <v>0.1763927292392293</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3395159584882397</v>
+        <v>0.3414159584882396</v>
       </c>
       <c r="C83">
-        <v>-14.02807313907388</v>
+        <v>-14.85374095205932</v>
       </c>
       <c r="D83">
-        <v>26.86492686092612</v>
+        <v>26.69225904794068</v>
       </c>
       <c r="E83">
-        <v>52.893</v>
+        <v>53.546</v>
       </c>
       <c r="F83">
-        <v>52.893</v>
+        <v>53.546</v>
       </c>
       <c r="G83">
         <v>12</v>
@@ -8218,37 +8218,37 @@
         <v>2.2</v>
       </c>
       <c r="M83">
-        <v>12.4721694</v>
+        <v>12.6261468</v>
       </c>
       <c r="N83">
-        <v>-10.2721694</v>
+        <v>-10.4261468</v>
       </c>
       <c r="O83">
-        <v>-1.54082541</v>
+        <v>-1.56392202</v>
       </c>
       <c r="P83">
-        <v>-8.731343989999999</v>
+        <v>-8.862224780000002</v>
       </c>
       <c r="Q83">
-        <v>-6.801343989999999</v>
+        <v>-6.932224780000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8082713540164463</v>
+        <v>0.8506308736840267</v>
       </c>
       <c r="T83">
-        <v>4.663179885130519</v>
+        <v>4.922245434304436</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02645890938588439</v>
+        <v>0.02613623975922726</v>
       </c>
       <c r="W83">
-        <v>0.2295609891668085</v>
+        <v>0.2296370746647742</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1763927292392293</v>
+        <v>0.1742415983948483</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3414159584882396</v>
+        <v>0.3433159584882396</v>
       </c>
       <c r="C84">
-        <v>-14.85374095205932</v>
+        <v>-15.67720337850793</v>
       </c>
       <c r="D84">
-        <v>26.69225904794068</v>
+        <v>26.52179662149208</v>
       </c>
       <c r="E84">
-        <v>53.546</v>
+        <v>54.19900000000001</v>
       </c>
       <c r="F84">
-        <v>53.546</v>
+        <v>54.19900000000001</v>
       </c>
       <c r="G84">
         <v>12</v>
@@ -8300,37 +8300,37 @@
         <v>2.2</v>
       </c>
       <c r="M84">
-        <v>12.6261468</v>
+        <v>12.7801242</v>
       </c>
       <c r="N84">
-        <v>-10.4261468</v>
+        <v>-10.5801242</v>
       </c>
       <c r="O84">
-        <v>-1.56392202</v>
+        <v>-1.58701863</v>
       </c>
       <c r="P84">
-        <v>-8.862224780000002</v>
+        <v>-8.993105570000001</v>
       </c>
       <c r="Q84">
-        <v>-6.932224780000002</v>
+        <v>-7.063105570000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.8506308736840267</v>
+        <v>0.8979738662536755</v>
       </c>
       <c r="T84">
-        <v>4.922245434304436</v>
+        <v>5.211789283381169</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02613623975922726</v>
+        <v>0.02582134530429681</v>
       </c>
       <c r="W84">
-        <v>0.2296370746647742</v>
+        <v>0.2297113267772468</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1742415983948483</v>
+        <v>0.1721423020286454</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3433159584882396</v>
+        <v>0.3452159584882397</v>
       </c>
       <c r="C85">
-        <v>-15.67720337850793</v>
+        <v>-16.49850240249871</v>
       </c>
       <c r="D85">
-        <v>26.52179662149208</v>
+        <v>26.3534975975013</v>
       </c>
       <c r="E85">
-        <v>54.19900000000001</v>
+        <v>54.852</v>
       </c>
       <c r="F85">
-        <v>54.19900000000001</v>
+        <v>54.852</v>
       </c>
       <c r="G85">
         <v>12</v>
@@ -8382,37 +8382,37 @@
         <v>2.2</v>
       </c>
       <c r="M85">
-        <v>12.7801242</v>
+        <v>12.9341016</v>
       </c>
       <c r="N85">
-        <v>-10.5801242</v>
+        <v>-10.7341016</v>
       </c>
       <c r="O85">
-        <v>-1.58701863</v>
+        <v>-1.61011524</v>
       </c>
       <c r="P85">
-        <v>-8.993105570000001</v>
+        <v>-9.123986360000002</v>
       </c>
       <c r="Q85">
-        <v>-7.063105570000001</v>
+        <v>-7.193986360000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.8979738662536755</v>
+        <v>0.9512347328945303</v>
       </c>
       <c r="T85">
-        <v>5.211789283381169</v>
+        <v>5.537526113592492</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02582134530429681</v>
+        <v>0.02551394833638851</v>
       </c>
       <c r="W85">
-        <v>0.2297113267772468</v>
+        <v>0.2297838109822796</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1721423020286454</v>
+        <v>0.1700929889092567</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3452159584882396</v>
+        <v>0.3471159584882396</v>
       </c>
       <c r="C86">
-        <v>-16.49850240249869</v>
+        <v>-17.31767894915913</v>
       </c>
       <c r="D86">
-        <v>26.3534975975013</v>
+        <v>26.18732105084087</v>
       </c>
       <c r="E86">
-        <v>54.852</v>
+        <v>55.505</v>
       </c>
       <c r="F86">
-        <v>54.852</v>
+        <v>55.505</v>
       </c>
       <c r="G86">
         <v>12</v>
@@ -8464,37 +8464,37 @@
         <v>2.2</v>
       </c>
       <c r="M86">
-        <v>12.9341016</v>
+        <v>13.088079</v>
       </c>
       <c r="N86">
-        <v>-10.7341016</v>
+        <v>-10.888079</v>
       </c>
       <c r="O86">
-        <v>-1.61011524</v>
+        <v>-1.63321185</v>
       </c>
       <c r="P86">
-        <v>-9.12398636</v>
+        <v>-9.254867149999997</v>
       </c>
       <c r="Q86">
-        <v>-7.19398636</v>
+        <v>-7.324867149999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.9512347328945295</v>
+        <v>1.011597048420832</v>
       </c>
       <c r="T86">
-        <v>5.537526113592488</v>
+        <v>5.906694521165321</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02551394833638851</v>
+        <v>0.02521378423831336</v>
       </c>
       <c r="W86">
-        <v>0.2297838109822796</v>
+        <v>0.2298545896766057</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1700929889092568</v>
+        <v>0.1680918949220891</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3471159584882396</v>
+        <v>0.3490159584882396</v>
       </c>
       <c r="C87">
-        <v>-17.31767894915913</v>
+        <v>-18.13477291784293</v>
       </c>
       <c r="D87">
-        <v>26.18732105084087</v>
+        <v>26.02322708215707</v>
       </c>
       <c r="E87">
-        <v>55.505</v>
+        <v>56.15799999999999</v>
       </c>
       <c r="F87">
-        <v>55.505</v>
+        <v>56.15799999999999</v>
       </c>
       <c r="G87">
         <v>12</v>
@@ -8546,37 +8546,37 @@
         <v>2.2</v>
       </c>
       <c r="M87">
-        <v>13.088079</v>
+        <v>13.2420564</v>
       </c>
       <c r="N87">
-        <v>-10.888079</v>
+        <v>-11.0420564</v>
       </c>
       <c r="O87">
-        <v>-1.63321185</v>
+        <v>-1.65630846</v>
       </c>
       <c r="P87">
-        <v>-9.254867149999997</v>
+        <v>-9.38574794</v>
       </c>
       <c r="Q87">
-        <v>-7.324867149999998</v>
+        <v>-7.45574794</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.011597048420832</v>
+        <v>1.080582551879463</v>
       </c>
       <c r="T87">
-        <v>5.906694521165321</v>
+        <v>6.328601272677131</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02521378423831336</v>
+        <v>0.02492060070065855</v>
       </c>
       <c r="W87">
-        <v>0.2298545896766057</v>
+        <v>0.2299237223547847</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1680918949220891</v>
+        <v>0.1661373380043902</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3490159584882396</v>
+        <v>0.3509159584882396</v>
       </c>
       <c r="C88">
-        <v>-18.13477291784293</v>
+        <v>-18.94982321406827</v>
       </c>
       <c r="D88">
-        <v>26.02322708215707</v>
+        <v>25.86117678593173</v>
       </c>
       <c r="E88">
-        <v>56.15799999999999</v>
+        <v>56.811</v>
       </c>
       <c r="F88">
-        <v>56.15799999999999</v>
+        <v>56.811</v>
       </c>
       <c r="G88">
         <v>12</v>
@@ -8628,37 +8628,37 @@
         <v>2.2</v>
       </c>
       <c r="M88">
-        <v>13.2420564</v>
+        <v>13.3960338</v>
       </c>
       <c r="N88">
-        <v>-11.0420564</v>
+        <v>-11.1960338</v>
       </c>
       <c r="O88">
-        <v>-1.65630846</v>
+        <v>-1.67940507</v>
       </c>
       <c r="P88">
-        <v>-9.38574794</v>
+        <v>-9.516628729999999</v>
       </c>
       <c r="Q88">
-        <v>-7.45574794</v>
+        <v>-7.586628729999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.080582551879463</v>
+        <v>1.160181209716344</v>
       </c>
       <c r="T88">
-        <v>6.328601272677131</v>
+        <v>6.815416755190756</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02492060070065855</v>
+        <v>0.02463415701444408</v>
       </c>
       <c r="W88">
-        <v>0.2299237223547847</v>
+        <v>0.2299912657759941</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1661373380043902</v>
+        <v>0.1642277134296273</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3509159584882396</v>
+        <v>0.3528159584882397</v>
       </c>
       <c r="C89">
-        <v>-18.94982321406827</v>
+        <v>-19.76286778027004</v>
       </c>
       <c r="D89">
-        <v>25.86117678593173</v>
+        <v>25.70113221972996</v>
       </c>
       <c r="E89">
-        <v>56.811</v>
+        <v>57.464</v>
       </c>
       <c r="F89">
-        <v>56.811</v>
+        <v>57.464</v>
       </c>
       <c r="G89">
         <v>12</v>
@@ -8710,37 +8710,37 @@
         <v>2.2</v>
       </c>
       <c r="M89">
-        <v>13.3960338</v>
+        <v>13.5500112</v>
       </c>
       <c r="N89">
-        <v>-11.1960338</v>
+        <v>-11.3500112</v>
       </c>
       <c r="O89">
-        <v>-1.67940507</v>
+        <v>-1.70250168</v>
       </c>
       <c r="P89">
-        <v>-9.516628729999999</v>
+        <v>-9.64750952</v>
       </c>
       <c r="Q89">
-        <v>-7.586628729999999</v>
+        <v>-7.71750952</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.160181209716344</v>
+        <v>1.25304631052604</v>
       </c>
       <c r="T89">
-        <v>6.815416755190756</v>
+        <v>7.383368151456654</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02463415701444408</v>
+        <v>0.02435422341200722</v>
       </c>
       <c r="W89">
-        <v>0.2299912657759941</v>
+        <v>0.2300572741194487</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1642277134296273</v>
+        <v>0.1623614894133814</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3528159584882397</v>
+        <v>0.3547159584882397</v>
       </c>
       <c r="C90">
-        <v>-19.76286778027004</v>
+        <v>-20.57394362541724</v>
       </c>
       <c r="D90">
-        <v>25.70113221972996</v>
+        <v>25.54305637458275</v>
       </c>
       <c r="E90">
-        <v>57.464</v>
+        <v>58.117</v>
       </c>
       <c r="F90">
-        <v>57.464</v>
+        <v>58.117</v>
       </c>
       <c r="G90">
         <v>12</v>
@@ -8792,37 +8792,37 @@
         <v>2.2</v>
       </c>
       <c r="M90">
-        <v>13.5500112</v>
+        <v>13.7039886</v>
       </c>
       <c r="N90">
-        <v>-11.3500112</v>
+        <v>-11.5039886</v>
       </c>
       <c r="O90">
-        <v>-1.70250168</v>
+        <v>-1.72559829</v>
       </c>
       <c r="P90">
-        <v>-9.64750952</v>
+        <v>-9.778390309999999</v>
       </c>
       <c r="Q90">
-        <v>-7.71750952</v>
+        <v>-7.848390309999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.25304631052604</v>
+        <v>1.362795975119316</v>
       </c>
       <c r="T90">
-        <v>7.383368151456654</v>
+        <v>8.054583437952713</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02435422341200722</v>
+        <v>0.02408058045232174</v>
       </c>
       <c r="W90">
-        <v>0.2300572741194487</v>
+        <v>0.2301217991293426</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1623614894133814</v>
+        <v>0.1605372030154784</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3547159584882397</v>
+        <v>0.3566159584882397</v>
       </c>
       <c r="C91">
-        <v>-20.57394362541724</v>
+        <v>-21.38308685354414</v>
       </c>
       <c r="D91">
-        <v>25.54305637458275</v>
+        <v>25.38691314645586</v>
       </c>
       <c r="E91">
-        <v>58.117</v>
+        <v>58.77</v>
       </c>
       <c r="F91">
-        <v>58.117</v>
+        <v>58.77</v>
       </c>
       <c r="G91">
         <v>12</v>
@@ -8874,37 +8874,37 @@
         <v>2.2</v>
       </c>
       <c r="M91">
-        <v>13.7039886</v>
+        <v>13.857966</v>
       </c>
       <c r="N91">
-        <v>-11.5039886</v>
+        <v>-11.657966</v>
       </c>
       <c r="O91">
-        <v>-1.72559829</v>
+        <v>-1.7486949</v>
       </c>
       <c r="P91">
-        <v>-9.778390309999999</v>
+        <v>-9.909271099999998</v>
       </c>
       <c r="Q91">
-        <v>-7.848390309999999</v>
+        <v>-7.979271099999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.362795975119316</v>
+        <v>1.494495572631248</v>
       </c>
       <c r="T91">
-        <v>8.054583437952713</v>
+        <v>8.860041781747984</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02408058045232174</v>
+        <v>0.02381301844729595</v>
       </c>
       <c r="W91">
-        <v>0.2301217991293426</v>
+        <v>0.2301848902501276</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1605372030154784</v>
+        <v>0.1587534563153064</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3566159584882397</v>
+        <v>0.3585159584882396</v>
       </c>
       <c r="C92">
-        <v>-21.38308685354414</v>
+        <v>-22.19033269124122</v>
       </c>
       <c r="D92">
-        <v>25.38691314645586</v>
+        <v>25.23266730875878</v>
       </c>
       <c r="E92">
-        <v>58.77</v>
+        <v>59.423</v>
       </c>
       <c r="F92">
-        <v>58.77</v>
+        <v>59.423</v>
       </c>
       <c r="G92">
         <v>12</v>
@@ -8956,37 +8956,37 @@
         <v>2.2</v>
       </c>
       <c r="M92">
-        <v>13.857966</v>
+        <v>14.0119434</v>
       </c>
       <c r="N92">
-        <v>-11.657966</v>
+        <v>-11.8119434</v>
       </c>
       <c r="O92">
-        <v>-1.7486949</v>
+        <v>-1.77179151</v>
       </c>
       <c r="P92">
-        <v>-9.909271099999998</v>
+        <v>-10.04015189</v>
       </c>
       <c r="Q92">
-        <v>-7.979271099999998</v>
+        <v>-8.110151890000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.494495572631248</v>
+        <v>1.655461747368054</v>
       </c>
       <c r="T92">
-        <v>8.860041781747984</v>
+        <v>9.844490868608872</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02381301844729595</v>
+        <v>0.02355133692589709</v>
       </c>
       <c r="W92">
-        <v>0.2301848902501276</v>
+        <v>0.2302465947528735</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1587534563153064</v>
+        <v>0.157008912839314</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3585159584882396</v>
+        <v>0.3604159584882396</v>
       </c>
       <c r="C93">
-        <v>-22.19033269124122</v>
+        <v>-22.99571551415016</v>
       </c>
       <c r="D93">
-        <v>25.23266730875878</v>
+        <v>25.08028448584984</v>
       </c>
       <c r="E93">
-        <v>59.423</v>
+        <v>60.076</v>
       </c>
       <c r="F93">
-        <v>59.423</v>
+        <v>60.076</v>
       </c>
       <c r="G93">
         <v>12</v>
@@ -9038,37 +9038,37 @@
         <v>2.2</v>
       </c>
       <c r="M93">
-        <v>14.0119434</v>
+        <v>14.1659208</v>
       </c>
       <c r="N93">
-        <v>-11.8119434</v>
+        <v>-11.9659208</v>
       </c>
       <c r="O93">
-        <v>-1.77179151</v>
+        <v>-1.79488812</v>
       </c>
       <c r="P93">
-        <v>-10.04015189</v>
+        <v>-10.17103268</v>
       </c>
       <c r="Q93">
-        <v>-8.110151890000001</v>
+        <v>-8.24103268</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.655461747368054</v>
+        <v>1.856669465789061</v>
       </c>
       <c r="T93">
-        <v>9.844490868608872</v>
+        <v>11.07505222718498</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02355133692589709</v>
+        <v>0.0232953441332243</v>
       </c>
       <c r="W93">
-        <v>0.2302465947528735</v>
+        <v>0.2303069578533857</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.157008912839314</v>
+        <v>0.1553022942214953</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3604159584882396</v>
+        <v>0.3623159584882396</v>
       </c>
       <c r="C94">
-        <v>-22.99571551415016</v>
+        <v>-23.7992688725044</v>
       </c>
       <c r="D94">
-        <v>25.08028448584984</v>
+        <v>24.9297311274956</v>
       </c>
       <c r="E94">
-        <v>60.076</v>
+        <v>60.729</v>
       </c>
       <c r="F94">
-        <v>60.076</v>
+        <v>60.729</v>
       </c>
       <c r="G94">
         <v>12</v>
@@ -9120,37 +9120,37 @@
         <v>2.2</v>
       </c>
       <c r="M94">
-        <v>14.1659208</v>
+        <v>14.3198982</v>
       </c>
       <c r="N94">
-        <v>-11.9659208</v>
+        <v>-12.1198982</v>
       </c>
       <c r="O94">
-        <v>-1.79488812</v>
+        <v>-1.81798473</v>
       </c>
       <c r="P94">
-        <v>-10.17103268</v>
+        <v>-10.30191347</v>
       </c>
       <c r="Q94">
-        <v>-8.24103268</v>
+        <v>-8.371913470000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.856669465789061</v>
+        <v>2.115365103758927</v>
       </c>
       <c r="T94">
-        <v>11.07505222718498</v>
+        <v>12.65720254535427</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0232953441332243</v>
+        <v>0.0230448565618993</v>
       </c>
       <c r="W94">
-        <v>0.2303069578533857</v>
+        <v>0.2303660228227042</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1553022942214953</v>
+        <v>0.1536323770793286</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3623159584882396</v>
+        <v>0.3642159584882396</v>
       </c>
       <c r="C95">
-        <v>-23.7992688725044</v>
+        <v>-24.60102551575535</v>
       </c>
       <c r="D95">
-        <v>24.9297311274956</v>
+        <v>24.78097448424466</v>
       </c>
       <c r="E95">
-        <v>60.729</v>
+        <v>61.382</v>
       </c>
       <c r="F95">
-        <v>60.729</v>
+        <v>61.382</v>
       </c>
       <c r="G95">
         <v>12</v>
@@ -9202,37 +9202,37 @@
         <v>2.2</v>
       </c>
       <c r="M95">
-        <v>14.3198982</v>
+        <v>14.4738756</v>
       </c>
       <c r="N95">
-        <v>-12.1198982</v>
+        <v>-12.2738756</v>
       </c>
       <c r="O95">
-        <v>-1.81798473</v>
+        <v>-1.84108134</v>
       </c>
       <c r="P95">
-        <v>-10.30191347</v>
+        <v>-10.43279426</v>
       </c>
       <c r="Q95">
-        <v>-8.371913470000003</v>
+        <v>-8.50279426</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.115365103758927</v>
+        <v>2.460292621052081</v>
       </c>
       <c r="T95">
-        <v>12.65720254535427</v>
+        <v>14.76673630291332</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0230448565618993</v>
+        <v>0.02279969851336846</v>
       </c>
       <c r="W95">
-        <v>0.2303660228227042</v>
+        <v>0.2304238310905477</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1536323770793286</v>
+        <v>0.151997990089123</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3642159584882396</v>
+        <v>0.3661159584882396</v>
       </c>
       <c r="C96">
-        <v>-24.60102551575535</v>
+        <v>-25.40101741632215</v>
       </c>
       <c r="D96">
-        <v>24.78097448424466</v>
+        <v>24.63398258367785</v>
       </c>
       <c r="E96">
-        <v>61.382</v>
+        <v>62.035</v>
       </c>
       <c r="F96">
-        <v>61.382</v>
+        <v>62.035</v>
       </c>
       <c r="G96">
         <v>12</v>
@@ -9284,37 +9284,37 @@
         <v>2.2</v>
       </c>
       <c r="M96">
-        <v>14.4738756</v>
+        <v>14.627853</v>
       </c>
       <c r="N96">
-        <v>-12.2738756</v>
+        <v>-12.427853</v>
       </c>
       <c r="O96">
-        <v>-1.84108134</v>
+        <v>-1.86417795</v>
       </c>
       <c r="P96">
-        <v>-10.43279426</v>
+        <v>-10.56367505</v>
       </c>
       <c r="Q96">
-        <v>-8.50279426</v>
+        <v>-8.633675050000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.460292621052081</v>
+        <v>2.943191145262499</v>
       </c>
       <c r="T96">
-        <v>14.76673630291332</v>
+        <v>17.72008356349599</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02279969851336846</v>
+        <v>0.02255970168691195</v>
       </c>
       <c r="W96">
-        <v>0.2304238310905477</v>
+        <v>0.2304804223422262</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.151997990089123</v>
+        <v>0.1503980112460795</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3661159584882396</v>
+        <v>0.3680159584882396</v>
       </c>
       <c r="C97">
-        <v>-25.40101741632215</v>
+        <v>-26.19927579250124</v>
       </c>
       <c r="D97">
-        <v>24.63398258367785</v>
+        <v>24.48872420749877</v>
       </c>
       <c r="E97">
-        <v>62.035</v>
+        <v>62.688</v>
       </c>
       <c r="F97">
-        <v>62.035</v>
+        <v>62.688</v>
       </c>
       <c r="G97">
         <v>12</v>
@@ -9366,37 +9366,37 @@
         <v>2.2</v>
       </c>
       <c r="M97">
-        <v>14.627853</v>
+        <v>14.7818304</v>
       </c>
       <c r="N97">
-        <v>-12.427853</v>
+        <v>-12.5818304</v>
       </c>
       <c r="O97">
-        <v>-1.86417795</v>
+        <v>-1.88727456</v>
       </c>
       <c r="P97">
-        <v>-10.56367505</v>
+        <v>-10.69455584</v>
       </c>
       <c r="Q97">
-        <v>-8.633675050000003</v>
+        <v>-8.764555840000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.943191145262499</v>
+        <v>3.667538931578126</v>
       </c>
       <c r="T97">
-        <v>17.72008356349599</v>
+        <v>22.15010445437</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02255970168691195</v>
+        <v>0.02232470479433995</v>
       </c>
       <c r="W97">
-        <v>0.2304804223422262</v>
+        <v>0.2305358346094947</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1503980112460795</v>
+        <v>0.1488313652955996</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3680159584882396</v>
+        <v>0.3699159584882396</v>
       </c>
       <c r="C98">
-        <v>-26.19927579250123</v>
+        <v>-26.99583113056995</v>
       </c>
       <c r="D98">
-        <v>24.48872420749877</v>
+        <v>24.34516886943004</v>
       </c>
       <c r="E98">
-        <v>62.688</v>
+        <v>63.34099999999999</v>
       </c>
       <c r="F98">
-        <v>62.688</v>
+        <v>63.34099999999999</v>
       </c>
       <c r="G98">
         <v>12</v>
@@ -9448,37 +9448,37 @@
         <v>2.2</v>
       </c>
       <c r="M98">
-        <v>14.7818304</v>
+        <v>14.9358078</v>
       </c>
       <c r="N98">
-        <v>-12.5818304</v>
+        <v>-12.7358078</v>
       </c>
       <c r="O98">
-        <v>-1.88727456</v>
+        <v>-1.91037117</v>
       </c>
       <c r="P98">
-        <v>-10.69455584</v>
+        <v>-10.82543663</v>
       </c>
       <c r="Q98">
-        <v>-8.764555839999998</v>
+        <v>-8.895436630000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.667538931578116</v>
+        <v>4.874785242104155</v>
       </c>
       <c r="T98">
-        <v>22.15010445436994</v>
+        <v>29.53347260582659</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02232470479433995</v>
+        <v>0.02209455319852201</v>
       </c>
       <c r="W98">
-        <v>0.2305358346094947</v>
+        <v>0.2305901043557885</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1488313652955997</v>
+        <v>0.14729702132348</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3699159584882396</v>
+        <v>0.3718159584882397</v>
       </c>
       <c r="C99">
-        <v>-26.99583113056995</v>
+        <v>-27.79071320611745</v>
       </c>
       <c r="D99">
-        <v>24.34516886943004</v>
+        <v>24.20328679388255</v>
       </c>
       <c r="E99">
-        <v>63.34099999999999</v>
+        <v>63.99399999999999</v>
       </c>
       <c r="F99">
-        <v>63.34099999999999</v>
+        <v>63.99399999999999</v>
       </c>
       <c r="G99">
         <v>12</v>
@@ -9530,37 +9530,37 @@
         <v>2.2</v>
       </c>
       <c r="M99">
-        <v>14.9358078</v>
+        <v>15.0897852</v>
       </c>
       <c r="N99">
-        <v>-12.7358078</v>
+        <v>-12.8897852</v>
       </c>
       <c r="O99">
-        <v>-1.91037117</v>
+        <v>-1.93346778</v>
       </c>
       <c r="P99">
-        <v>-10.82543663</v>
+        <v>-10.95631742</v>
       </c>
       <c r="Q99">
-        <v>-8.895436630000001</v>
+        <v>-9.02631742</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.874785242104155</v>
+        <v>7.289277863156233</v>
       </c>
       <c r="T99">
-        <v>29.53347260582659</v>
+        <v>44.30020890873988</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02209455319852201</v>
+        <v>0.0218690985740473</v>
       </c>
       <c r="W99">
-        <v>0.2305901043557885</v>
+        <v>0.2306432665562397</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.14729702132348</v>
+        <v>0.1457939904936487</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3718159584882397</v>
+        <v>0.3737159584882396</v>
       </c>
       <c r="C100">
-        <v>-27.79071320611745</v>
+        <v>-28.58395110463383</v>
       </c>
       <c r="D100">
-        <v>24.20328679388255</v>
+        <v>24.06304889536617</v>
       </c>
       <c r="E100">
-        <v>63.99399999999999</v>
+        <v>64.64699999999999</v>
       </c>
       <c r="F100">
-        <v>63.99399999999999</v>
+        <v>64.64699999999999</v>
       </c>
       <c r="G100">
         <v>12</v>
@@ -9612,37 +9612,37 @@
         <v>2.2</v>
       </c>
       <c r="M100">
-        <v>15.0897852</v>
+        <v>15.2437626</v>
       </c>
       <c r="N100">
-        <v>-12.8897852</v>
+        <v>-13.0437626</v>
       </c>
       <c r="O100">
-        <v>-1.93346778</v>
+        <v>-1.95656439</v>
       </c>
       <c r="P100">
-        <v>-10.95631742</v>
+        <v>-11.08719821</v>
       </c>
       <c r="Q100">
-        <v>-9.02631742</v>
+        <v>-9.157198209999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.289277863156233</v>
+        <v>14.53275572631246</v>
       </c>
       <c r="T100">
-        <v>44.30020890873988</v>
+        <v>88.60041781747975</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0218690985740473</v>
+        <v>0.02164819858845086</v>
       </c>
       <c r="W100">
-        <v>0.2306432665562397</v>
+        <v>0.2306953547728433</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1457939904936487</v>
+        <v>0.1443213239230058</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3737159584882396</v>
-      </c>
-      <c r="C101">
-        <v>-28.58395110463383</v>
-      </c>
-      <c r="D101">
-        <v>24.06304889536617</v>
-      </c>
-      <c r="E101">
-        <v>64.64699999999999</v>
-      </c>
-      <c r="F101">
-        <v>64.64699999999999</v>
-      </c>
-      <c r="G101">
-        <v>12</v>
-      </c>
-      <c r="H101">
-        <v>65.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.13</v>
-      </c>
-      <c r="K101">
-        <v>1.93</v>
-      </c>
-      <c r="L101">
-        <v>2.2</v>
-      </c>
-      <c r="M101">
-        <v>15.2437626</v>
-      </c>
-      <c r="N101">
-        <v>-13.0437626</v>
-      </c>
-      <c r="O101">
-        <v>-1.95656439</v>
-      </c>
-      <c r="P101">
-        <v>-11.08719821</v>
-      </c>
-      <c r="Q101">
-        <v>-9.157198209999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>14.53275572631246</v>
-      </c>
-      <c r="T101">
-        <v>88.60041781747975</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02164819858845086</v>
-      </c>
-      <c r="W101">
-        <v>0.2306953547728433</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1443213239230058</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
